--- a/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
+++ b/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="724" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E0DC221-E27E-42D6-B882-870131AA760C}"/>
+  <xr:revisionPtr revIDLastSave="752" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CACA8D8-015D-4804-A5D7-8D31D52245E8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="116">
   <si>
     <t>GRUPOS</t>
   </si>
@@ -380,17 +380,17 @@
     <t>Ivan</t>
   </si>
   <si>
-    <t>Nancy</t>
+    <t>Armandin</t>
   </si>
   <si>
-    <t>Armandin</t>
+    <t>Brenda</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -445,6 +445,17 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="24">
@@ -733,11 +744,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -829,58 +841,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -888,6 +854,8 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -921,10 +889,56 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CDE2DAD8-18C9-498B-94D4-DF142B136E21}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{E78B5277-1D27-424B-A76E-597236430B2A}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -949,10 +963,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1242,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM124"/>
+  <dimension ref="A1:AK124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
@@ -1258,15 +1268,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1344,17 +1354,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="62" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="64"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="29" t="s">
         <v>102</v>
       </c>
@@ -1377,16 +1387,16 @@
         <v>111</v>
       </c>
       <c r="O2" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="P2" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="P2" s="29" t="s">
-        <v>113</v>
-      </c>
       <c r="Q2" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="R2" s="29" t="s">
         <v>114</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>115</v>
       </c>
       <c r="S2" s="29"/>
       <c r="T2" s="29"/>
@@ -1416,56 +1426,56 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="52"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
         <f t="shared" ref="H3:AF3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" si="0"/>
@@ -1525,7 +1535,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="37" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1537,11 +1547,15 @@
       <c r="D4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
       <c r="G4" s="7" t="str">
         <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>46</v>
@@ -1564,10 +1578,18 @@
       <c r="N4" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
+      <c r="O4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S4" s="23"/>
       <c r="T4" s="23"/>
       <c r="U4" s="23"/>
@@ -1621,10 +1643,18 @@
       <c r="N5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
+      <c r="O5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R5" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S5" s="23"/>
       <c r="T5" s="23"/>
       <c r="U5" s="23"/>
@@ -1678,10 +1708,18 @@
       <c r="N6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
+      <c r="O6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R6" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S6" s="23"/>
       <c r="T6" s="23"/>
       <c r="U6" s="23"/>
@@ -1735,10 +1773,18 @@
       <c r="N7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
+      <c r="O7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R7" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S7" s="23"/>
       <c r="T7" s="23"/>
       <c r="U7" s="23"/>
@@ -1792,10 +1838,18 @@
       <c r="N8" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
+      <c r="O8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R8" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S8" s="23"/>
       <c r="T8" s="23"/>
       <c r="U8" s="23"/>
@@ -1849,10 +1903,18 @@
       <c r="N9" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
+      <c r="O9" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S9" s="23"/>
       <c r="T9" s="23"/>
       <c r="U9" s="23"/>
@@ -1869,7 +1931,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1908,10 +1970,18 @@
       <c r="N10" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
+      <c r="O10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R10" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S10" s="23"/>
       <c r="T10" s="23"/>
       <c r="U10" s="23"/>
@@ -1965,10 +2035,18 @@
       <c r="N11" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
+      <c r="O11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S11" s="23"/>
       <c r="T11" s="23"/>
       <c r="U11" s="23"/>
@@ -2022,10 +2100,18 @@
       <c r="N12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
+      <c r="O12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P12" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R12" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
       <c r="U12" s="23"/>
@@ -2079,10 +2165,18 @@
       <c r="N13" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
+      <c r="O13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R13" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S13" s="23"/>
       <c r="T13" s="23"/>
       <c r="U13" s="23"/>
@@ -2136,10 +2230,18 @@
       <c r="N14" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
+      <c r="O14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S14" s="23"/>
       <c r="T14" s="23"/>
       <c r="U14" s="23"/>
@@ -2193,10 +2295,18 @@
       <c r="N15" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="O15" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
@@ -2213,7 +2323,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="45" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2252,10 +2362,18 @@
       <c r="N16" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
+      <c r="O16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q16" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R16" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
       <c r="U16" s="23"/>
@@ -2309,10 +2427,18 @@
       <c r="N17" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
+      <c r="O17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R17" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S17" s="23"/>
       <c r="T17" s="23"/>
       <c r="U17" s="23"/>
@@ -2366,10 +2492,18 @@
       <c r="N18" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
+      <c r="O18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q18" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R18" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S18" s="23"/>
       <c r="T18" s="23"/>
       <c r="U18" s="23"/>
@@ -2423,10 +2557,18 @@
       <c r="N19" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
+      <c r="O19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S19" s="23"/>
       <c r="T19" s="23"/>
       <c r="U19" s="23"/>
@@ -2480,10 +2622,18 @@
       <c r="N20" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
+      <c r="O20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q20" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R20" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
       <c r="U20" s="23"/>
@@ -2537,10 +2687,18 @@
       <c r="N21" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
+      <c r="O21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S21" s="23"/>
       <c r="T21" s="23"/>
       <c r="U21" s="23"/>
@@ -2557,7 +2715,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="42" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2596,10 +2754,18 @@
       <c r="N22" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="O22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P22" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R22" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S22" s="23"/>
       <c r="T22" s="23"/>
       <c r="U22" s="23"/>
@@ -2653,10 +2819,18 @@
       <c r="N23" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
+      <c r="O23" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q23" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R23" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
       <c r="U23" s="23"/>
@@ -2710,10 +2884,18 @@
       <c r="N24" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
+      <c r="O24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R24" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
       <c r="U24" s="23"/>
@@ -2767,10 +2949,18 @@
       <c r="N25" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
+      <c r="O25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R25" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S25" s="23"/>
       <c r="T25" s="23"/>
       <c r="U25" s="23"/>
@@ -2824,10 +3014,18 @@
       <c r="N26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
+      <c r="O26" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R26" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
       <c r="U26" s="23"/>
@@ -2881,10 +3079,18 @@
       <c r="N27" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
+      <c r="O27" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P27" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q27" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R27" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S27" s="23"/>
       <c r="T27" s="23"/>
       <c r="U27" s="23"/>
@@ -2901,7 +3107,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -2940,10 +3146,18 @@
       <c r="N28" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
+      <c r="O28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R28" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S28" s="23"/>
       <c r="T28" s="23"/>
       <c r="U28" s="23"/>
@@ -2997,10 +3211,18 @@
       <c r="N29" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="23"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="23"/>
-      <c r="R29" s="23"/>
+      <c r="O29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S29" s="23"/>
       <c r="T29" s="23"/>
       <c r="U29" s="23"/>
@@ -3054,10 +3276,18 @@
       <c r="N30" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="23"/>
+      <c r="O30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R30" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S30" s="23"/>
       <c r="T30" s="23"/>
       <c r="U30" s="23"/>
@@ -3111,10 +3341,18 @@
       <c r="N31" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
+      <c r="O31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q31" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R31" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
@@ -3168,10 +3406,18 @@
       <c r="N32" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="23"/>
+      <c r="O32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P32" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q32" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R32" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S32" s="23"/>
       <c r="T32" s="23"/>
       <c r="U32" s="23"/>
@@ -3225,10 +3471,18 @@
       <c r="N33" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="23"/>
+      <c r="O33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q33" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R33" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S33" s="23"/>
       <c r="T33" s="23"/>
       <c r="U33" s="23"/>
@@ -3245,7 +3499,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3284,10 +3538,18 @@
       <c r="N34" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
+      <c r="O34" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R34" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S34" s="23"/>
       <c r="T34" s="23"/>
       <c r="U34" s="23"/>
@@ -3341,10 +3603,18 @@
       <c r="N35" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
+      <c r="O35" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P35" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R35" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S35" s="23"/>
       <c r="T35" s="23"/>
       <c r="U35" s="23"/>
@@ -3398,10 +3668,18 @@
       <c r="N36" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
-      <c r="R36" s="23"/>
+      <c r="O36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q36" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R36" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S36" s="23"/>
       <c r="T36" s="23"/>
       <c r="U36" s="23"/>
@@ -3455,10 +3733,18 @@
       <c r="N37" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23"/>
-      <c r="Q37" s="23"/>
-      <c r="R37" s="23"/>
+      <c r="O37" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P37" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R37" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S37" s="23"/>
       <c r="T37" s="23"/>
       <c r="U37" s="23"/>
@@ -3512,10 +3798,18 @@
       <c r="N38" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O38" s="23"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="23"/>
-      <c r="R38" s="23"/>
+      <c r="O38" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P38" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q38" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R38" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S38" s="23"/>
       <c r="T38" s="23"/>
       <c r="U38" s="23"/>
@@ -3569,10 +3863,18 @@
       <c r="N39" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O39" s="23"/>
-      <c r="P39" s="23"/>
-      <c r="Q39" s="23"/>
-      <c r="R39" s="23"/>
+      <c r="O39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P39" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R39" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S39" s="23"/>
       <c r="T39" s="23"/>
       <c r="U39" s="23"/>
@@ -3589,7 +3891,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3628,10 +3930,18 @@
       <c r="N40" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O40" s="23"/>
-      <c r="P40" s="23"/>
-      <c r="Q40" s="23"/>
-      <c r="R40" s="23"/>
+      <c r="O40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q40" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R40" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S40" s="23"/>
       <c r="T40" s="23"/>
       <c r="U40" s="23"/>
@@ -3685,10 +3995,18 @@
       <c r="N41" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O41" s="23"/>
-      <c r="P41" s="23"/>
-      <c r="Q41" s="23"/>
-      <c r="R41" s="23"/>
+      <c r="O41" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P41" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q41" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R41" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S41" s="23"/>
       <c r="T41" s="23"/>
       <c r="U41" s="23"/>
@@ -3742,10 +4060,18 @@
       <c r="N42" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O42" s="23"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="23"/>
+      <c r="O42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q42" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R42" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="S42" s="23"/>
       <c r="T42" s="23"/>
       <c r="U42" s="23"/>
@@ -3799,10 +4125,18 @@
       <c r="N43" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O43" s="23"/>
-      <c r="P43" s="23"/>
-      <c r="Q43" s="23"/>
-      <c r="R43" s="23"/>
+      <c r="O43" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P43" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q43" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R43" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S43" s="23"/>
       <c r="T43" s="23"/>
       <c r="U43" s="23"/>
@@ -3856,10 +4190,18 @@
       <c r="N44" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O44" s="23"/>
-      <c r="P44" s="23"/>
-      <c r="Q44" s="23"/>
-      <c r="R44" s="23"/>
+      <c r="O44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R44" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S44" s="23"/>
       <c r="T44" s="23"/>
       <c r="U44" s="23"/>
@@ -3913,10 +4255,18 @@
       <c r="N45" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O45" s="23"/>
-      <c r="P45" s="23"/>
-      <c r="Q45" s="23"/>
-      <c r="R45" s="23"/>
+      <c r="O45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q45" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R45" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S45" s="23"/>
       <c r="T45" s="23"/>
       <c r="U45" s="23"/>
@@ -3933,7 +4283,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="37" t="s">
+      <c r="A46" s="57" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -3972,10 +4322,18 @@
       <c r="N46" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O46" s="23"/>
-      <c r="P46" s="23"/>
-      <c r="Q46" s="23"/>
-      <c r="R46" s="23"/>
+      <c r="O46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q46" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R46" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S46" s="23"/>
       <c r="T46" s="23"/>
       <c r="U46" s="23"/>
@@ -4029,10 +4387,18 @@
       <c r="N47" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O47" s="23"/>
-      <c r="P47" s="23"/>
-      <c r="Q47" s="23"/>
-      <c r="R47" s="23"/>
+      <c r="O47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P47" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q47" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R47" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S47" s="23"/>
       <c r="T47" s="23"/>
       <c r="U47" s="23"/>
@@ -4086,10 +4452,18 @@
       <c r="N48" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O48" s="23"/>
-      <c r="P48" s="23"/>
-      <c r="Q48" s="23"/>
-      <c r="R48" s="23"/>
+      <c r="O48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q48" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R48" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="S48" s="23"/>
       <c r="T48" s="23"/>
       <c r="U48" s="23"/>
@@ -4105,7 +4479,7 @@
       <c r="AE48" s="23"/>
       <c r="AF48" s="23"/>
     </row>
-    <row r="49" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="38"/>
       <c r="B49" s="7">
         <v>46</v>
@@ -4143,10 +4517,18 @@
       <c r="N49" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O49" s="23"/>
-      <c r="P49" s="23"/>
-      <c r="Q49" s="23"/>
-      <c r="R49" s="23"/>
+      <c r="O49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="P49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q49" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R49" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S49" s="23"/>
       <c r="T49" s="23"/>
       <c r="U49" s="23"/>
@@ -4162,7 +4544,7 @@
       <c r="AE49" s="23"/>
       <c r="AF49" s="23"/>
     </row>
-    <row r="50" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="38"/>
       <c r="B50" s="7">
         <v>47</v>
@@ -4200,10 +4582,18 @@
       <c r="N50" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O50" s="23"/>
-      <c r="P50" s="23"/>
-      <c r="Q50" s="23"/>
-      <c r="R50" s="23"/>
+      <c r="O50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R50" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S50" s="23"/>
       <c r="T50" s="23"/>
       <c r="U50" s="23"/>
@@ -4219,7 +4609,7 @@
       <c r="AE50" s="23"/>
       <c r="AF50" s="23"/>
     </row>
-    <row r="51" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="39"/>
       <c r="B51" s="7">
         <v>48</v>
@@ -4257,10 +4647,18 @@
       <c r="N51" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="O51" s="23"/>
-      <c r="P51" s="23"/>
-      <c r="Q51" s="23"/>
-      <c r="R51" s="23"/>
+      <c r="O51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q51" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="R51" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="S51" s="23"/>
       <c r="T51" s="23"/>
       <c r="U51" s="23"/>
@@ -4276,8 +4674,8 @@
       <c r="AE51" s="23"/>
       <c r="AF51" s="23"/>
     </row>
-    <row r="52" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="44" t="s">
+    <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="60" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4316,10 +4714,18 @@
       <c r="N52" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O52" s="25"/>
-      <c r="P52" s="25"/>
-      <c r="Q52" s="25"/>
-      <c r="R52" s="25"/>
+      <c r="O52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q52" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R52" s="25" t="s">
+        <v>10</v>
+      </c>
       <c r="S52" s="25"/>
       <c r="T52" s="25"/>
       <c r="U52" s="25"/>
@@ -4335,8 +4741,8 @@
       <c r="AE52" s="25"/>
       <c r="AF52" s="25"/>
     </row>
-    <row r="53" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="45"/>
+    <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="61"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4373,10 +4779,18 @@
       <c r="N53" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O53" s="25"/>
-      <c r="P53" s="25"/>
-      <c r="Q53" s="25"/>
-      <c r="R53" s="25"/>
+      <c r="O53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q53" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R53" s="25" t="s">
+        <v>104</v>
+      </c>
       <c r="S53" s="25"/>
       <c r="T53" s="25"/>
       <c r="U53" s="25"/>
@@ -4392,8 +4806,8 @@
       <c r="AE53" s="25"/>
       <c r="AF53" s="25"/>
     </row>
-    <row r="54" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="45"/>
+    <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="61"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4430,10 +4844,18 @@
       <c r="N54" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O54" s="25"/>
-      <c r="P54" s="25"/>
-      <c r="Q54" s="25"/>
-      <c r="R54" s="25"/>
+      <c r="O54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R54" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S54" s="25"/>
       <c r="T54" s="25"/>
       <c r="U54" s="25"/>
@@ -4449,8 +4871,8 @@
       <c r="AE54" s="25"/>
       <c r="AF54" s="25"/>
     </row>
-    <row r="55" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="45"/>
+    <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="61"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4487,10 +4909,18 @@
       <c r="N55" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O55" s="25"/>
-      <c r="P55" s="25"/>
-      <c r="Q55" s="25"/>
-      <c r="R55" s="25"/>
+      <c r="O55" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q55" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R55" s="25" t="s">
+        <v>10</v>
+      </c>
       <c r="S55" s="25"/>
       <c r="T55" s="25"/>
       <c r="U55" s="25"/>
@@ -4505,9 +4935,10 @@
       <c r="AD55" s="25"/>
       <c r="AE55" s="25"/>
       <c r="AF55" s="25"/>
-    </row>
-    <row r="56" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="45"/>
+      <c r="AK55" s="31"/>
+    </row>
+    <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="61"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -4544,10 +4975,18 @@
       <c r="N56" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O56" s="25"/>
-      <c r="P56" s="25"/>
-      <c r="Q56" s="25"/>
-      <c r="R56" s="25"/>
+      <c r="O56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R56" s="25" t="s">
+        <v>10</v>
+      </c>
       <c r="S56" s="25"/>
       <c r="T56" s="25"/>
       <c r="U56" s="25"/>
@@ -4563,8 +5002,8 @@
       <c r="AE56" s="25"/>
       <c r="AF56" s="25"/>
     </row>
-    <row r="57" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="46"/>
+    <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="62"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -4601,10 +5040,18 @@
       <c r="N57" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O57" s="25"/>
-      <c r="P57" s="25"/>
-      <c r="Q57" s="25"/>
-      <c r="R57" s="25"/>
+      <c r="O57" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P57" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q57" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R57" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S57" s="25"/>
       <c r="T57" s="25"/>
       <c r="U57" s="25"/>
@@ -4620,8 +5067,8 @@
       <c r="AE57" s="25"/>
       <c r="AF57" s="25"/>
     </row>
-    <row r="58" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="47" t="s">
+    <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="63" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -4660,10 +5107,18 @@
       <c r="N58" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O58" s="25"/>
-      <c r="P58" s="25"/>
-      <c r="Q58" s="25"/>
-      <c r="R58" s="25"/>
+      <c r="O58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R58" s="25" t="s">
+        <v>10</v>
+      </c>
       <c r="S58" s="25"/>
       <c r="T58" s="25"/>
       <c r="U58" s="25"/>
@@ -4679,8 +5134,8 @@
       <c r="AE58" s="25"/>
       <c r="AF58" s="25"/>
     </row>
-    <row r="59" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="48"/>
+    <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="64"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -4717,10 +5172,18 @@
       <c r="N59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O59" s="25"/>
-      <c r="P59" s="25"/>
-      <c r="Q59" s="25"/>
-      <c r="R59" s="25"/>
+      <c r="O59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P59" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q59" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R59" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S59" s="25"/>
       <c r="T59" s="25"/>
       <c r="U59" s="25"/>
@@ -4736,8 +5199,8 @@
       <c r="AE59" s="25"/>
       <c r="AF59" s="25"/>
     </row>
-    <row r="60" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="48"/>
+    <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="64"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -4774,10 +5237,18 @@
       <c r="N60" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O60" s="25"/>
-      <c r="P60" s="25"/>
-      <c r="Q60" s="25"/>
-      <c r="R60" s="25"/>
+      <c r="O60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q60" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R60" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S60" s="25"/>
       <c r="T60" s="25"/>
       <c r="U60" s="25"/>
@@ -4793,8 +5264,8 @@
       <c r="AE60" s="25"/>
       <c r="AF60" s="25"/>
     </row>
-    <row r="61" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="48"/>
+    <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="64"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -4831,10 +5302,18 @@
       <c r="N61" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O61" s="25"/>
-      <c r="P61" s="25"/>
-      <c r="Q61" s="25"/>
-      <c r="R61" s="25"/>
+      <c r="O61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P61" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q61" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R61" s="25" t="s">
+        <v>104</v>
+      </c>
       <c r="S61" s="25"/>
       <c r="T61" s="25"/>
       <c r="U61" s="25"/>
@@ -4850,8 +5329,8 @@
       <c r="AE61" s="25"/>
       <c r="AF61" s="25"/>
     </row>
-    <row r="62" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="48"/>
+    <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="64"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -4888,10 +5367,18 @@
       <c r="N62" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O62" s="25"/>
-      <c r="P62" s="25"/>
-      <c r="Q62" s="25"/>
-      <c r="R62" s="25"/>
+      <c r="O62" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P62" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q62" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R62" s="25" t="s">
+        <v>10</v>
+      </c>
       <c r="S62" s="25"/>
       <c r="T62" s="25"/>
       <c r="U62" s="25"/>
@@ -4907,8 +5394,8 @@
       <c r="AE62" s="25"/>
       <c r="AF62" s="25"/>
     </row>
-    <row r="63" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="49"/>
+    <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="65"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -4945,10 +5432,18 @@
       <c r="N63" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O63" s="25"/>
-      <c r="P63" s="25"/>
-      <c r="Q63" s="25"/>
-      <c r="R63" s="25"/>
+      <c r="O63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q63" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R63" s="25" t="s">
+        <v>104</v>
+      </c>
       <c r="S63" s="25"/>
       <c r="T63" s="25"/>
       <c r="U63" s="25"/>
@@ -4964,8 +5459,8 @@
       <c r="AE63" s="25"/>
       <c r="AF63" s="25"/>
     </row>
-    <row r="64" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="31" t="s">
+    <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="51" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5004,10 +5499,18 @@
       <c r="N64" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O64" s="25"/>
-      <c r="P64" s="25"/>
-      <c r="Q64" s="25"/>
-      <c r="R64" s="25"/>
+      <c r="O64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q64" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R64" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S64" s="25"/>
       <c r="T64" s="25"/>
       <c r="U64" s="25"/>
@@ -5023,8 +5526,8 @@
       <c r="AE64" s="25"/>
       <c r="AF64" s="25"/>
     </row>
-    <row r="65" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="32"/>
+    <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="52"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5061,10 +5564,18 @@
       <c r="N65" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O65" s="25"/>
-      <c r="P65" s="25"/>
-      <c r="Q65" s="25"/>
-      <c r="R65" s="25"/>
+      <c r="O65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q65" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R65" s="25" t="s">
+        <v>104</v>
+      </c>
       <c r="S65" s="25"/>
       <c r="T65" s="25"/>
       <c r="U65" s="25"/>
@@ -5080,8 +5591,8 @@
       <c r="AE65" s="25"/>
       <c r="AF65" s="25"/>
     </row>
-    <row r="66" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="32"/>
+    <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="52"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5118,10 +5629,18 @@
       <c r="N66" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O66" s="25"/>
-      <c r="P66" s="25"/>
-      <c r="Q66" s="25"/>
-      <c r="R66" s="25"/>
+      <c r="O66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R66" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S66" s="25"/>
       <c r="T66" s="25"/>
       <c r="U66" s="25"/>
@@ -5137,8 +5656,8 @@
       <c r="AE66" s="25"/>
       <c r="AF66" s="25"/>
     </row>
-    <row r="67" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="32"/>
+    <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="52"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5175,10 +5694,18 @@
       <c r="N67" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O67" s="25"/>
-      <c r="P67" s="25"/>
-      <c r="Q67" s="25"/>
-      <c r="R67" s="25"/>
+      <c r="O67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q67" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R67" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S67" s="25"/>
       <c r="T67" s="25"/>
       <c r="U67" s="25"/>
@@ -5194,8 +5721,8 @@
       <c r="AE67" s="25"/>
       <c r="AF67" s="25"/>
     </row>
-    <row r="68" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="32"/>
+    <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="52"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5232,10 +5759,18 @@
       <c r="N68" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O68" s="25"/>
-      <c r="P68" s="25"/>
-      <c r="Q68" s="25"/>
-      <c r="R68" s="25"/>
+      <c r="O68" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P68" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q68" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R68" s="25" t="s">
+        <v>10</v>
+      </c>
       <c r="S68" s="25"/>
       <c r="T68" s="25"/>
       <c r="U68" s="25"/>
@@ -5250,18 +5785,9 @@
       <c r="AD68" s="25"/>
       <c r="AE68" s="25"/>
       <c r="AF68" s="25"/>
-      <c r="AK68">
-        <v>10</v>
-      </c>
-      <c r="AL68">
-        <v>9</v>
-      </c>
-      <c r="AM68">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="33"/>
+    </row>
+    <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="53"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5298,10 +5824,18 @@
       <c r="N69" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O69" s="25"/>
-      <c r="P69" s="25"/>
-      <c r="Q69" s="25"/>
-      <c r="R69" s="25"/>
+      <c r="O69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q69" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R69" s="25" t="s">
+        <v>104</v>
+      </c>
       <c r="S69" s="25"/>
       <c r="T69" s="25"/>
       <c r="U69" s="25"/>
@@ -5317,8 +5851,8 @@
       <c r="AE69" s="25"/>
       <c r="AF69" s="25"/>
     </row>
-    <row r="70" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="34" t="s">
+    <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="54" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5357,10 +5891,18 @@
       <c r="N70" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O70" s="25"/>
-      <c r="P70" s="25"/>
-      <c r="Q70" s="25"/>
-      <c r="R70" s="25"/>
+      <c r="O70" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P70" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q70" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R70" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S70" s="25"/>
       <c r="T70" s="25"/>
       <c r="U70" s="25"/>
@@ -5376,8 +5918,8 @@
       <c r="AE70" s="25"/>
       <c r="AF70" s="25"/>
     </row>
-    <row r="71" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="35"/>
+    <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="55"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5414,10 +5956,18 @@
       <c r="N71" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O71" s="25"/>
-      <c r="P71" s="25"/>
-      <c r="Q71" s="25"/>
-      <c r="R71" s="25"/>
+      <c r="O71" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P71" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q71" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R71" s="25" t="s">
+        <v>46</v>
+      </c>
       <c r="S71" s="25"/>
       <c r="T71" s="25"/>
       <c r="U71" s="25"/>
@@ -5433,8 +5983,8 @@
       <c r="AE71" s="25"/>
       <c r="AF71" s="25"/>
     </row>
-    <row r="72" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="35"/>
+    <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="55"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -5471,10 +6021,18 @@
       <c r="N72" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O72" s="25"/>
-      <c r="P72" s="25"/>
-      <c r="Q72" s="25"/>
-      <c r="R72" s="25"/>
+      <c r="O72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q72" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R72" s="25" t="s">
+        <v>10</v>
+      </c>
       <c r="S72" s="25"/>
       <c r="T72" s="25"/>
       <c r="U72" s="25"/>
@@ -5490,8 +6048,8 @@
       <c r="AE72" s="25"/>
       <c r="AF72" s="25"/>
     </row>
-    <row r="73" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="35"/>
+    <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="55"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -5528,10 +6086,18 @@
       <c r="N73" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O73" s="25"/>
-      <c r="P73" s="25"/>
-      <c r="Q73" s="25"/>
-      <c r="R73" s="25"/>
+      <c r="O73" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P73" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q73" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R73" s="25" t="s">
+        <v>104</v>
+      </c>
       <c r="S73" s="25"/>
       <c r="T73" s="25"/>
       <c r="U73" s="25"/>
@@ -5547,8 +6113,8 @@
       <c r="AE73" s="25"/>
       <c r="AF73" s="25"/>
     </row>
-    <row r="74" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="35"/>
+    <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="55"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -5585,10 +6151,18 @@
       <c r="N74" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="O74" s="25"/>
-      <c r="P74" s="25"/>
-      <c r="Q74" s="25"/>
-      <c r="R74" s="25"/>
+      <c r="O74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="P74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q74" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="R74" s="25" t="s">
+        <v>10</v>
+      </c>
       <c r="S74" s="25"/>
       <c r="T74" s="25"/>
       <c r="U74" s="25"/>
@@ -5604,8 +6178,8 @@
       <c r="AE74" s="25"/>
       <c r="AF74" s="25"/>
     </row>
-    <row r="75" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="36"/>
+    <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="56"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -5642,10 +6216,18 @@
       <c r="N75" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="O75" s="25"/>
-      <c r="P75" s="25"/>
-      <c r="Q75" s="25"/>
-      <c r="R75" s="25"/>
+      <c r="O75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P75" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="R75" s="25" t="s">
+        <v>104</v>
+      </c>
       <c r="S75" s="25"/>
       <c r="T75" s="25"/>
       <c r="U75" s="25"/>
@@ -5661,18 +6243,18 @@
       <c r="AE75" s="25"/>
       <c r="AF75" s="25"/>
     </row>
-    <row r="76" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="40" t="s">
+      <c r="D76" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="41"/>
-      <c r="F76" s="42"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="34"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" s="25">
         <v>172</v>
@@ -5696,11 +6278,17 @@
         <v>222</v>
       </c>
       <c r="O76" s="25">
-        <v>187</v>
-      </c>
-      <c r="P76" s="25"/>
-      <c r="Q76" s="25"/>
-      <c r="R76" s="25"/>
+        <v>197</v>
+      </c>
+      <c r="P76" s="25">
+        <v>169</v>
+      </c>
+      <c r="Q76" s="25">
+        <v>190</v>
+      </c>
+      <c r="R76" s="25">
+        <v>186</v>
+      </c>
       <c r="S76" s="25"/>
       <c r="T76" s="25"/>
       <c r="U76" s="25"/>
@@ -5716,16 +6304,16 @@
       <c r="AE76" s="25"/>
       <c r="AF76" s="25"/>
     </row>
-    <row r="77" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="43" t="s">
+      <c r="D77" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="41"/>
-      <c r="F77" s="41"/>
-      <c r="G77" s="42"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="34"/>
       <c r="H77" s="28">
         <f t="shared" ref="H77:AF77" si="3">SUM(H78:H81)</f>
         <v>0</v>
@@ -5760,74 +6348,74 @@
       </c>
       <c r="P77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="V77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="W77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Y77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Z77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AB77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AC77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AD77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AE77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AF77" s="28">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" spans="1:39" ht="14.4" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -5869,74 +6457,74 @@
       </c>
       <c r="P78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" spans="1:39" ht="14.4" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6045,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:39" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -7127,6 +7715,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7138,13 +7733,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
+++ b/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="752" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CACA8D8-015D-4804-A5D7-8D31D52245E8}"/>
+  <xr:revisionPtr revIDLastSave="754" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA487246-EEBC-40F7-8204-11D6990BFD7D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="pagos" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -842,11 +843,58 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -854,8 +902,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -889,51 +935,6 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -963,6 +964,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1268,15 +1273,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="19">
         <v>1</v>
       </c>
@@ -1354,17 +1359,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="65"/>
       <c r="H2" s="29" t="s">
         <v>102</v>
       </c>
@@ -1426,16 +1431,16 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="36"/>
+      <c r="F3" s="53"/>
       <c r="G3" s="22" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
         <f t="shared" ref="H3:AF3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="14">
         <f t="shared" si="0"/>
@@ -1443,23 +1448,23 @@
       </c>
       <c r="J3" s="14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" s="14">
         <f t="shared" si="0"/>
@@ -1475,7 +1480,7 @@
       </c>
       <c r="R3" s="14">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" si="0"/>
@@ -1535,7 +1540,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="54" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1606,7 +1611,7 @@
       <c r="AF4" s="23"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="38"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1616,11 +1621,15 @@
       <c r="D5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
       <c r="G5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>46</v>
@@ -1671,7 +1680,7 @@
       <c r="AF5" s="23"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1736,7 +1745,7 @@
       <c r="AF6" s="23"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1801,7 +1810,7 @@
       <c r="AF7" s="23"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="38"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1866,7 +1875,7 @@
       <c r="AF8" s="23"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1931,7 +1940,7 @@
       <c r="AF9" s="23"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="59" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1998,7 +2007,7 @@
       <c r="AF10" s="23"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="38"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2063,7 +2072,7 @@
       <c r="AF11" s="23"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="38"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2128,7 +2137,7 @@
       <c r="AF12" s="23"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="38"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2193,7 +2202,7 @@
       <c r="AF13" s="23"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+      <c r="A14" s="39"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2258,7 +2267,7 @@
       <c r="AF14" s="23"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="39"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2323,7 +2332,7 @@
       <c r="AF15" s="23"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="60" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2390,7 +2399,7 @@
       <c r="AF16" s="23"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2455,7 +2464,7 @@
       <c r="AF17" s="23"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2520,7 +2529,7 @@
       <c r="AF18" s="23"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="38"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2585,7 +2594,7 @@
       <c r="AF19" s="23"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="38"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2650,7 +2659,7 @@
       <c r="AF20" s="23"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2715,7 +2724,7 @@
       <c r="AF21" s="23"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="57" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2782,7 +2791,7 @@
       <c r="AF22" s="23"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2847,7 +2856,7 @@
       <c r="AF23" s="23"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2912,7 +2921,7 @@
       <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="38"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2977,7 +2986,7 @@
       <c r="AF25" s="23"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3042,7 +3051,7 @@
       <c r="AF26" s="23"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
+      <c r="A27" s="40"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3107,7 +3116,7 @@
       <c r="AF27" s="23"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="58" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3174,7 +3183,7 @@
       <c r="AF28" s="23"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="38"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3239,7 +3248,7 @@
       <c r="AF29" s="23"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3304,7 +3313,7 @@
       <c r="AF30" s="23"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="38"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3369,7 +3378,7 @@
       <c r="AF31" s="23"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="38"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3434,7 +3443,7 @@
       <c r="AF32" s="23"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="39"/>
+      <c r="A33" s="40"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3499,7 +3508,7 @@
       <c r="AF33" s="23"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="56" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3566,7 +3575,7 @@
       <c r="AF34" s="23"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="38"/>
+      <c r="A35" s="39"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3631,7 +3640,7 @@
       <c r="AF35" s="23"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="38"/>
+      <c r="A36" s="39"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3696,7 +3705,7 @@
       <c r="AF36" s="23"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="38"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3761,7 +3770,7 @@
       <c r="AF37" s="23"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="38"/>
+      <c r="A38" s="39"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3826,7 +3835,7 @@
       <c r="AF38" s="23"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="39"/>
+      <c r="A39" s="40"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3891,7 +3900,7 @@
       <c r="AF39" s="23"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="55" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3958,7 +3967,7 @@
       <c r="AF40" s="23"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="38"/>
+      <c r="A41" s="39"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4023,7 +4032,7 @@
       <c r="AF41" s="23"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="38"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4088,7 +4097,7 @@
       <c r="AF42" s="23"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="38"/>
+      <c r="A43" s="39"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4153,7 +4162,7 @@
       <c r="AF43" s="23"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="38"/>
+      <c r="A44" s="39"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4218,7 +4227,7 @@
       <c r="AF44" s="23"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="39"/>
+      <c r="A45" s="40"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4283,7 +4292,7 @@
       <c r="AF45" s="23"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="57" t="s">
+      <c r="A46" s="38" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4350,7 +4359,7 @@
       <c r="AF46" s="23"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="38"/>
+      <c r="A47" s="39"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4415,7 +4424,7 @@
       <c r="AF47" s="23"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="38"/>
+      <c r="A48" s="39"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4480,7 +4489,7 @@
       <c r="AF48" s="23"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="38"/>
+      <c r="A49" s="39"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4545,7 +4554,7 @@
       <c r="AF49" s="23"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="38"/>
+      <c r="A50" s="39"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4610,7 +4619,7 @@
       <c r="AF50" s="23"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="39"/>
+      <c r="A51" s="40"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4675,7 +4684,7 @@
       <c r="AF51" s="23"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="45" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4742,7 +4751,7 @@
       <c r="AF52" s="25"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="61"/>
+      <c r="A53" s="46"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4807,7 +4816,7 @@
       <c r="AF53" s="25"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="61"/>
+      <c r="A54" s="46"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4872,7 +4881,7 @@
       <c r="AF54" s="25"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="61"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4938,7 +4947,7 @@
       <c r="AK55" s="31"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="61"/>
+      <c r="A56" s="46"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5003,7 +5012,7 @@
       <c r="AF56" s="25"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="62"/>
+      <c r="A57" s="47"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5068,7 +5077,7 @@
       <c r="AF57" s="25"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="48" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5135,7 +5144,7 @@
       <c r="AF58" s="25"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="64"/>
+      <c r="A59" s="49"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5200,7 +5209,7 @@
       <c r="AF59" s="25"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="64"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5265,7 +5274,7 @@
       <c r="AF60" s="25"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="64"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5330,7 +5339,7 @@
       <c r="AF61" s="25"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="64"/>
+      <c r="A62" s="49"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5395,7 +5404,7 @@
       <c r="AF62" s="25"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="65"/>
+      <c r="A63" s="50"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5460,7 +5469,7 @@
       <c r="AF63" s="25"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="51" t="s">
+      <c r="A64" s="32" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5527,7 +5536,7 @@
       <c r="AF64" s="25"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="52"/>
+      <c r="A65" s="33"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5592,7 +5601,7 @@
       <c r="AF65" s="25"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="52"/>
+      <c r="A66" s="33"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5657,7 +5666,7 @@
       <c r="AF66" s="25"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="52"/>
+      <c r="A67" s="33"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5722,7 +5731,7 @@
       <c r="AF67" s="25"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="52"/>
+      <c r="A68" s="33"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5787,7 +5796,7 @@
       <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="53"/>
+      <c r="A69" s="34"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5852,7 +5861,7 @@
       <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="54" t="s">
+      <c r="A70" s="35" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5919,7 +5928,7 @@
       <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="55"/>
+      <c r="A71" s="36"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5984,7 +5993,7 @@
       <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="55"/>
+      <c r="A72" s="36"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6049,7 +6058,7 @@
       <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="55"/>
+      <c r="A73" s="36"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6114,7 +6123,7 @@
       <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="55"/>
+      <c r="A74" s="36"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6179,7 +6188,7 @@
       <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="56"/>
+      <c r="A75" s="37"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6247,14 +6256,14 @@
       <c r="A76" s="27"/>
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
-      <c r="D76" s="58" t="s">
+      <c r="D76" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="33"/>
-      <c r="F76" s="34"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="43"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H76" s="25">
         <v>172</v>
@@ -6308,12 +6317,12 @@
       <c r="A77" s="27"/>
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
-      <c r="D77" s="59" t="s">
+      <c r="D77" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="34"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="43"/>
       <c r="H77" s="28">
         <f t="shared" ref="H77:AF77" si="3">SUM(H78:H81)</f>
         <v>0</v>
@@ -6360,59 +6369,59 @@
       </c>
       <c r="S77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="T77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="U77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="V77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="W77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="X77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Y77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Z77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AA77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AB77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AC77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AD77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AE77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AF77" s="28">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6469,59 +6478,59 @@
       </c>
       <c r="S78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="4"/>
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -7715,13 +7724,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7733,6 +7735,13 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
+++ b/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="754" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA487246-EEBC-40F7-8204-11D6990BFD7D}"/>
+  <xr:revisionPtr revIDLastSave="773" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B65F00F5-2D97-4861-BC01-C7C53CB5B697}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="pagos" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -459,7 +458,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -470,18 +469,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
         <bgColor rgb="FF0070C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -750,15 +737,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -767,7 +754,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -785,13 +778,13 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -800,22 +793,7 @@
     <xf numFmtId="0" fontId="5" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -833,7 +811,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -843,36 +821,8 @@
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -892,26 +842,51 @@
     <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -920,19 +895,25 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1273,156 +1254,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="19">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="29">
         <v>1</v>
       </c>
-      <c r="I1" s="19">
+      <c r="I1" s="29">
         <v>2</v>
       </c>
-      <c r="J1" s="19">
+      <c r="J1" s="29">
         <v>3</v>
       </c>
-      <c r="K1" s="20">
+      <c r="K1" s="29">
         <v>4</v>
       </c>
-      <c r="L1" s="20">
+      <c r="L1" s="29">
         <v>5</v>
       </c>
-      <c r="M1" s="20">
+      <c r="M1" s="29">
         <v>6</v>
       </c>
-      <c r="N1" s="20">
+      <c r="N1" s="29">
         <v>7</v>
       </c>
-      <c r="O1" s="20">
+      <c r="O1" s="29">
         <v>8</v>
       </c>
-      <c r="P1" s="20">
+      <c r="P1" s="29">
         <v>9</v>
       </c>
-      <c r="Q1" s="20">
-        <v>10</v>
-      </c>
-      <c r="R1" s="20">
+      <c r="Q1" s="29">
+        <v>10</v>
+      </c>
+      <c r="R1" s="29">
         <v>11</v>
       </c>
-      <c r="S1" s="20">
+      <c r="S1" s="29">
         <v>12</v>
       </c>
-      <c r="T1" s="20">
+      <c r="T1" s="29">
         <v>13</v>
       </c>
-      <c r="U1" s="20">
+      <c r="U1" s="29">
         <v>14</v>
       </c>
-      <c r="V1" s="20">
+      <c r="V1" s="29">
         <v>15</v>
       </c>
-      <c r="W1" s="20">
-        <v>16</v>
-      </c>
-      <c r="X1" s="20">
-        <v>17</v>
-      </c>
-      <c r="Y1" s="20">
+      <c r="W1" s="29">
+        <v>16</v>
+      </c>
+      <c r="X1" s="29">
+        <v>17</v>
+      </c>
+      <c r="Y1" s="29">
         <v>18</v>
       </c>
-      <c r="Z1" s="20">
+      <c r="Z1" s="29">
         <v>19</v>
       </c>
-      <c r="AA1" s="20">
+      <c r="AA1" s="29">
         <v>20</v>
       </c>
-      <c r="AB1" s="20">
+      <c r="AB1" s="29">
         <v>21</v>
       </c>
-      <c r="AC1" s="20">
+      <c r="AC1" s="29">
         <v>22</v>
       </c>
-      <c r="AD1" s="20">
+      <c r="AD1" s="29">
         <v>23</v>
       </c>
-      <c r="AE1" s="20">
+      <c r="AE1" s="29">
         <v>24</v>
       </c>
-      <c r="AF1" s="21">
+      <c r="AF1" s="29">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="63" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="29" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="M2" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="O2" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="P2" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="O2" s="29" t="s">
+      <c r="Q2" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="P2" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q2" s="29" t="s">
+      <c r="R2" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
     </row>
     <row r="3" spans="1:32" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="14" t="s">
@@ -1431,59 +1412,59 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="53"/>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="51"/>
+      <c r="G3" s="19" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f t="shared" ref="H3:AF3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="I3" s="14">
+        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
+        <v>4</v>
+      </c>
+      <c r="J3" s="14">
+        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
+        <v>4</v>
+      </c>
+      <c r="K3" s="14">
+        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L3" s="14">
+        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+        <v>3</v>
+      </c>
+      <c r="M3" s="14">
+        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
+        <v>3</v>
+      </c>
+      <c r="N3" s="14">
+        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+        <v>3</v>
+      </c>
+      <c r="O3" s="14">
+        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
         <v>2</v>
       </c>
-      <c r="I3" s="14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J3" s="14">
-        <f t="shared" si="0"/>
+      <c r="P3" s="14">
+        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
         <v>2</v>
       </c>
-      <c r="K3" s="14">
-        <f t="shared" si="0"/>
+      <c r="Q3" s="14">
+        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
         <v>2</v>
       </c>
-      <c r="L3" s="14">
-        <f t="shared" si="0"/>
+      <c r="R3" s="14">
+        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
         <v>2</v>
       </c>
-      <c r="M3" s="14">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="N3" s="14">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="O3" s="14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="P3" s="14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="R3" s="14">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
       <c r="S3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="T3" s="14">
@@ -1540,7 +1521,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="52" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1562,56 +1543,56 @@
         <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
         <v>L</v>
       </c>
-      <c r="H4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="23"/>
-      <c r="AA4" s="23"/>
-      <c r="AB4" s="23"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="23"/>
-      <c r="AE4" s="23"/>
-      <c r="AF4" s="23"/>
+      <c r="H4" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="20"/>
+      <c r="AE4" s="20"/>
+      <c r="AF4" s="20"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1631,56 +1612,56 @@
         <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="H5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R5" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="V5" s="23"/>
-      <c r="W5" s="23"/>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="23"/>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="23"/>
-      <c r="AC5" s="23"/>
-      <c r="AD5" s="23"/>
-      <c r="AE5" s="23"/>
-      <c r="AF5" s="23"/>
+      <c r="H5" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R5" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1696,56 +1677,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="24" t="s">
+      <c r="H6" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="L6" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="23"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="23"/>
+      <c r="N6" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
+      <c r="A7" s="37"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1761,56 +1742,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M7" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q7" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
-      <c r="AC7" s="23"/>
-      <c r="AD7" s="23"/>
-      <c r="AE7" s="23"/>
-      <c r="AF7" s="23"/>
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P7" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1826,56 +1807,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L8" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R8" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="23"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="23"/>
+      <c r="H8" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P8" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R8" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="40"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1891,56 +1872,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O9" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="23"/>
-      <c r="AE9" s="23"/>
-      <c r="AF9" s="23"/>
+      <c r="H9" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="57" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1952,62 +1933,66 @@
       <c r="D10" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
       <c r="G10" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-      <c r="AC10" s="23"/>
-      <c r="AD10" s="23"/>
-      <c r="AE10" s="23"/>
-      <c r="AF10" s="23"/>
+        <v>E</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q10" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R10" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="39"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2017,62 +2002,66 @@
       <c r="D11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
       <c r="G11" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L11" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="23"/>
-      <c r="AA11" s="23"/>
-      <c r="AB11" s="23"/>
-      <c r="AC11" s="23"/>
-      <c r="AD11" s="23"/>
-      <c r="AE11" s="23"/>
-      <c r="AF11" s="23"/>
+        <v>E</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P11" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2088,56 +2077,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P12" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R12" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
-      <c r="AC12" s="23"/>
-      <c r="AD12" s="23"/>
-      <c r="AE12" s="23"/>
-      <c r="AF12" s="23"/>
+      <c r="H12" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P12" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="39"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2153,56 +2142,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R13" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
-      <c r="AD13" s="23"/>
-      <c r="AE13" s="23"/>
-      <c r="AF13" s="23"/>
+      <c r="H13" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P13" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="39"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2218,56 +2207,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M14" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N14" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P14" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R14" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
+      <c r="H14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P14" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q14" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="20"/>
+      <c r="AE14" s="20"/>
+      <c r="AF14" s="20"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="40"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2283,56 +2272,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H15" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K15" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L15" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O15" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P15" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R15" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="23"/>
-      <c r="AB15" s="23"/>
-      <c r="AC15" s="23"/>
-      <c r="AD15" s="23"/>
-      <c r="AE15" s="23"/>
-      <c r="AF15" s="23"/>
+      <c r="H15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O15" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R15" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="58" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2344,62 +2333,66 @@
       <c r="D16" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
       <c r="G16" s="9" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N16" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="23"/>
-      <c r="AB16" s="23"/>
-      <c r="AC16" s="23"/>
-      <c r="AD16" s="23"/>
-      <c r="AE16" s="23"/>
-      <c r="AF16" s="23"/>
+        <v>E</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O16" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P16" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q16" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R16" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
+      <c r="AE16" s="20"/>
+      <c r="AF16" s="20"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2415,56 +2408,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R17" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="23"/>
-      <c r="AA17" s="23"/>
-      <c r="AB17" s="23"/>
-      <c r="AC17" s="23"/>
-      <c r="AD17" s="23"/>
-      <c r="AE17" s="23"/>
-      <c r="AF17" s="23"/>
+      <c r="H17" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O17" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P17" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q17" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R17" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="20"/>
+      <c r="AE17" s="20"/>
+      <c r="AF17" s="20"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2480,56 +2473,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q18" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R18" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="23"/>
-      <c r="AA18" s="23"/>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="23"/>
-      <c r="AD18" s="23"/>
-      <c r="AE18" s="23"/>
-      <c r="AF18" s="23"/>
+      <c r="H18" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N18" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O18" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q18" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R18" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="20"/>
+      <c r="AF18" s="20"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2545,56 +2538,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R19" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="23"/>
-      <c r="AA19" s="23"/>
-      <c r="AB19" s="23"/>
-      <c r="AC19" s="23"/>
-      <c r="AD19" s="23"/>
-      <c r="AE19" s="23"/>
-      <c r="AF19" s="23"/>
+      <c r="H19" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N19" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="20"/>
+      <c r="AD19" s="20"/>
+      <c r="AE19" s="20"/>
+      <c r="AF19" s="20"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2610,56 +2603,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K20" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M20" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R20" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="23"/>
-      <c r="AA20" s="23"/>
-      <c r="AB20" s="23"/>
-      <c r="AC20" s="23"/>
-      <c r="AD20" s="23"/>
-      <c r="AE20" s="23"/>
-      <c r="AF20" s="23"/>
+      <c r="H20" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O20" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R20" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
+      <c r="AE20" s="20"/>
+      <c r="AF20" s="20"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2675,56 +2668,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M21" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q21" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R21" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="23"/>
-      <c r="AC21" s="23"/>
-      <c r="AD21" s="23"/>
-      <c r="AE21" s="23"/>
-      <c r="AF21" s="23"/>
+      <c r="H21" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N21" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O21" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R21" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="55" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2736,62 +2729,66 @@
       <c r="D22" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
+      <c r="E22" s="10">
+        <v>4</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1</v>
+      </c>
       <c r="G22" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N22" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P22" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q22" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R22" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="23"/>
-      <c r="AA22" s="23"/>
-      <c r="AB22" s="23"/>
-      <c r="AC22" s="23"/>
-      <c r="AD22" s="23"/>
-      <c r="AE22" s="23"/>
-      <c r="AF22" s="23"/>
+        <v>L</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N22" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O22" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="20"/>
+      <c r="AE22" s="20"/>
+      <c r="AF22" s="20"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2807,56 +2804,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H23" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N23" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O23" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P23" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q23" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R23" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="23"/>
-      <c r="AA23" s="23"/>
-      <c r="AB23" s="23"/>
-      <c r="AC23" s="23"/>
-      <c r="AD23" s="23"/>
-      <c r="AE23" s="23"/>
-      <c r="AF23" s="23"/>
+      <c r="H23" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N23" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O23" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P23" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q23" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="20"/>
+      <c r="AE23" s="20"/>
+      <c r="AF23" s="20"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="39"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2872,56 +2869,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M24" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N24" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R24" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="23"/>
-      <c r="AA24" s="23"/>
-      <c r="AB24" s="23"/>
-      <c r="AC24" s="23"/>
-      <c r="AD24" s="23"/>
-      <c r="AE24" s="23"/>
-      <c r="AF24" s="23"/>
+      <c r="H24" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O24" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R24" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="20"/>
+      <c r="AE24" s="20"/>
+      <c r="AF24" s="20"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2937,56 +2934,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K25" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M25" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N25" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R25" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="23"/>
-      <c r="AA25" s="23"/>
-      <c r="AB25" s="23"/>
-      <c r="AC25" s="23"/>
-      <c r="AD25" s="23"/>
-      <c r="AE25" s="23"/>
-      <c r="AF25" s="23"/>
+      <c r="H25" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N25" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O25" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P25" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q25" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R25" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AD25" s="20"/>
+      <c r="AE25" s="20"/>
+      <c r="AF25" s="20"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3002,56 +2999,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M26" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P26" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q26" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="23"/>
-      <c r="AA26" s="23"/>
-      <c r="AB26" s="23"/>
-      <c r="AC26" s="23"/>
-      <c r="AD26" s="23"/>
-      <c r="AE26" s="23"/>
-      <c r="AF26" s="23"/>
+      <c r="H26" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O26" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P26" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R26" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="20"/>
+      <c r="AD26" s="20"/>
+      <c r="AE26" s="20"/>
+      <c r="AF26" s="20"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="40"/>
+      <c r="A27" s="38"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3067,56 +3064,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J27" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L27" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M27" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N27" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q27" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R27" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="23"/>
-      <c r="AA27" s="23"/>
-      <c r="AB27" s="23"/>
-      <c r="AC27" s="23"/>
-      <c r="AD27" s="23"/>
-      <c r="AE27" s="23"/>
-      <c r="AF27" s="23"/>
+      <c r="H27" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N27" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O27" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P27" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q27" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R27" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="20"/>
+      <c r="AD27" s="20"/>
+      <c r="AE27" s="20"/>
+      <c r="AF27" s="20"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="56" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3134,56 +3131,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M28" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R28" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="23"/>
-      <c r="AA28" s="23"/>
-      <c r="AB28" s="23"/>
-      <c r="AC28" s="23"/>
-      <c r="AD28" s="23"/>
-      <c r="AE28" s="23"/>
-      <c r="AF28" s="23"/>
+      <c r="H28" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N28" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P28" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="20"/>
+      <c r="AD28" s="20"/>
+      <c r="AE28" s="20"/>
+      <c r="AF28" s="20"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="39"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3199,56 +3196,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H29" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M29" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q29" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R29" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="23"/>
-      <c r="W29" s="23"/>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="23"/>
-      <c r="AA29" s="23"/>
-      <c r="AB29" s="23"/>
-      <c r="AC29" s="23"/>
-      <c r="AD29" s="23"/>
-      <c r="AE29" s="23"/>
-      <c r="AF29" s="23"/>
+      <c r="H29" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K29" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M29" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N29" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q29" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="20"/>
+      <c r="AE29" s="20"/>
+      <c r="AF29" s="20"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3264,56 +3261,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M30" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R30" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
-      <c r="AA30" s="23"/>
-      <c r="AB30" s="23"/>
-      <c r="AC30" s="23"/>
-      <c r="AD30" s="23"/>
-      <c r="AE30" s="23"/>
-      <c r="AF30" s="23"/>
+      <c r="H30" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M30" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N30" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P30" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
+      <c r="AA30" s="20"/>
+      <c r="AB30" s="20"/>
+      <c r="AC30" s="20"/>
+      <c r="AD30" s="20"/>
+      <c r="AE30" s="20"/>
+      <c r="AF30" s="20"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="39"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3329,56 +3326,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J31" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M31" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P31" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q31" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R31" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
-      <c r="W31" s="23"/>
-      <c r="X31" s="23"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="23"/>
-      <c r="AA31" s="23"/>
-      <c r="AB31" s="23"/>
-      <c r="AC31" s="23"/>
-      <c r="AD31" s="23"/>
-      <c r="AE31" s="23"/>
-      <c r="AF31" s="23"/>
+      <c r="H31" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K31" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N31" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O31" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P31" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q31" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R31" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="20"/>
+      <c r="AE31" s="20"/>
+      <c r="AF31" s="20"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3394,56 +3391,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K32" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L32" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q32" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R32" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S32" s="23"/>
-      <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="23"/>
-      <c r="W32" s="23"/>
-      <c r="X32" s="23"/>
-      <c r="Y32" s="23"/>
-      <c r="Z32" s="23"/>
-      <c r="AA32" s="23"/>
-      <c r="AB32" s="23"/>
-      <c r="AC32" s="23"/>
-      <c r="AD32" s="23"/>
-      <c r="AE32" s="23"/>
-      <c r="AF32" s="23"/>
+      <c r="H32" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N32" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O32" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P32" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R32" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="20"/>
+      <c r="AD32" s="20"/>
+      <c r="AE32" s="20"/>
+      <c r="AF32" s="20"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
+      <c r="A33" s="38"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3459,56 +3456,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H33" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I33" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J33" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K33" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L33" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R33" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="23"/>
-      <c r="W33" s="23"/>
-      <c r="X33" s="23"/>
-      <c r="Y33" s="23"/>
-      <c r="Z33" s="23"/>
-      <c r="AA33" s="23"/>
-      <c r="AB33" s="23"/>
-      <c r="AC33" s="23"/>
-      <c r="AD33" s="23"/>
-      <c r="AE33" s="23"/>
-      <c r="AF33" s="23"/>
+      <c r="H33" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M33" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N33" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O33" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P33" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q33" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R33" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
+      <c r="AC33" s="20"/>
+      <c r="AD33" s="20"/>
+      <c r="AE33" s="20"/>
+      <c r="AF33" s="20"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="54" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3526,56 +3523,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J34" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K34" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L34" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M34" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O34" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P34" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R34" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S34" s="23"/>
-      <c r="T34" s="23"/>
-      <c r="U34" s="23"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="23"/>
-      <c r="X34" s="23"/>
-      <c r="Y34" s="23"/>
-      <c r="Z34" s="23"/>
-      <c r="AA34" s="23"/>
-      <c r="AB34" s="23"/>
-      <c r="AC34" s="23"/>
-      <c r="AD34" s="23"/>
-      <c r="AE34" s="23"/>
-      <c r="AF34" s="23"/>
+      <c r="H34" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M34" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N34" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O34" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P34" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q34" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R34" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="20"/>
+      <c r="AA34" s="20"/>
+      <c r="AB34" s="20"/>
+      <c r="AC34" s="20"/>
+      <c r="AD34" s="20"/>
+      <c r="AE34" s="20"/>
+      <c r="AF34" s="20"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3591,56 +3588,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M35" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P35" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R35" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S35" s="23"/>
-      <c r="T35" s="23"/>
-      <c r="U35" s="23"/>
-      <c r="V35" s="23"/>
-      <c r="W35" s="23"/>
-      <c r="X35" s="23"/>
-      <c r="Y35" s="23"/>
-      <c r="Z35" s="23"/>
-      <c r="AA35" s="23"/>
-      <c r="AB35" s="23"/>
-      <c r="AC35" s="23"/>
-      <c r="AD35" s="23"/>
-      <c r="AE35" s="23"/>
-      <c r="AF35" s="23"/>
+      <c r="H35" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K35" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M35" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N35" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O35" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q35" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R35" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="20"/>
+      <c r="AB35" s="20"/>
+      <c r="AC35" s="20"/>
+      <c r="AD35" s="20"/>
+      <c r="AE35" s="20"/>
+      <c r="AF35" s="20"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3656,56 +3653,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K36" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L36" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M36" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R36" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S36" s="23"/>
-      <c r="T36" s="23"/>
-      <c r="U36" s="23"/>
-      <c r="V36" s="23"/>
-      <c r="W36" s="23"/>
-      <c r="X36" s="23"/>
-      <c r="Y36" s="23"/>
-      <c r="Z36" s="23"/>
-      <c r="AA36" s="23"/>
-      <c r="AB36" s="23"/>
-      <c r="AC36" s="23"/>
-      <c r="AD36" s="23"/>
-      <c r="AE36" s="23"/>
-      <c r="AF36" s="23"/>
+      <c r="H36" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K36" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M36" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N36" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O36" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P36" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q36" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R36" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
+      <c r="AC36" s="20"/>
+      <c r="AD36" s="20"/>
+      <c r="AE36" s="20"/>
+      <c r="AF36" s="20"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="39"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3721,56 +3718,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M37" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P37" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R37" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S37" s="23"/>
-      <c r="T37" s="23"/>
-      <c r="U37" s="23"/>
-      <c r="V37" s="23"/>
-      <c r="W37" s="23"/>
-      <c r="X37" s="23"/>
-      <c r="Y37" s="23"/>
-      <c r="Z37" s="23"/>
-      <c r="AA37" s="23"/>
-      <c r="AB37" s="23"/>
-      <c r="AC37" s="23"/>
-      <c r="AD37" s="23"/>
-      <c r="AE37" s="23"/>
-      <c r="AF37" s="23"/>
+      <c r="H37" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M37" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N37" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O37" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P37" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q37" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R37" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S37" s="20"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="20"/>
+      <c r="V37" s="20"/>
+      <c r="W37" s="20"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
+      <c r="Z37" s="20"/>
+      <c r="AA37" s="20"/>
+      <c r="AB37" s="20"/>
+      <c r="AC37" s="20"/>
+      <c r="AD37" s="20"/>
+      <c r="AE37" s="20"/>
+      <c r="AF37" s="20"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="39"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3786,56 +3783,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J38" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M38" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P38" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S38" s="23"/>
-      <c r="T38" s="23"/>
-      <c r="U38" s="23"/>
-      <c r="V38" s="23"/>
-      <c r="W38" s="23"/>
-      <c r="X38" s="23"/>
-      <c r="Y38" s="23"/>
-      <c r="Z38" s="23"/>
-      <c r="AA38" s="23"/>
-      <c r="AB38" s="23"/>
-      <c r="AC38" s="23"/>
-      <c r="AD38" s="23"/>
-      <c r="AE38" s="23"/>
-      <c r="AF38" s="23"/>
+      <c r="H38" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M38" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="N38" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P38" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q38" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R38" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S38" s="20"/>
+      <c r="T38" s="20"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="20"/>
+      <c r="AB38" s="20"/>
+      <c r="AC38" s="20"/>
+      <c r="AD38" s="20"/>
+      <c r="AE38" s="20"/>
+      <c r="AF38" s="20"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="40"/>
+      <c r="A39" s="38"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3851,56 +3848,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M39" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P39" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q39" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R39" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S39" s="23"/>
-      <c r="T39" s="23"/>
-      <c r="U39" s="23"/>
-      <c r="V39" s="23"/>
-      <c r="W39" s="23"/>
-      <c r="X39" s="23"/>
-      <c r="Y39" s="23"/>
-      <c r="Z39" s="23"/>
-      <c r="AA39" s="23"/>
-      <c r="AB39" s="23"/>
-      <c r="AC39" s="23"/>
-      <c r="AD39" s="23"/>
-      <c r="AE39" s="23"/>
-      <c r="AF39" s="23"/>
+      <c r="H39" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K39" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="N39" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O39" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P39" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q39" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R39" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+      <c r="AC39" s="20"/>
+      <c r="AD39" s="20"/>
+      <c r="AE39" s="20"/>
+      <c r="AF39" s="20"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3918,56 +3915,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H40" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I40" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M40" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R40" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S40" s="23"/>
-      <c r="T40" s="23"/>
-      <c r="U40" s="23"/>
-      <c r="V40" s="23"/>
-      <c r="W40" s="23"/>
-      <c r="X40" s="23"/>
-      <c r="Y40" s="23"/>
-      <c r="Z40" s="23"/>
-      <c r="AA40" s="23"/>
-      <c r="AB40" s="23"/>
-      <c r="AC40" s="23"/>
-      <c r="AD40" s="23"/>
-      <c r="AE40" s="23"/>
-      <c r="AF40" s="23"/>
+      <c r="H40" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K40" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M40" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N40" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O40" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P40" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q40" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R40" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="20"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+      <c r="AC40" s="20"/>
+      <c r="AD40" s="20"/>
+      <c r="AE40" s="20"/>
+      <c r="AF40" s="20"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="39"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -3983,56 +3980,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H41" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J41" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L41" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M41" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N41" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q41" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R41" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S41" s="23"/>
-      <c r="T41" s="23"/>
-      <c r="U41" s="23"/>
-      <c r="V41" s="23"/>
-      <c r="W41" s="23"/>
-      <c r="X41" s="23"/>
-      <c r="Y41" s="23"/>
-      <c r="Z41" s="23"/>
-      <c r="AA41" s="23"/>
-      <c r="AB41" s="23"/>
-      <c r="AC41" s="23"/>
-      <c r="AD41" s="23"/>
-      <c r="AE41" s="23"/>
-      <c r="AF41" s="23"/>
+      <c r="H41" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I41" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M41" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N41" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O41" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P41" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q41" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R41" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+      <c r="AC41" s="20"/>
+      <c r="AD41" s="20"/>
+      <c r="AE41" s="20"/>
+      <c r="AF41" s="20"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="39"/>
+      <c r="A42" s="37"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4048,56 +4045,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M42" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q42" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R42" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="S42" s="23"/>
-      <c r="T42" s="23"/>
-      <c r="U42" s="23"/>
-      <c r="V42" s="23"/>
-      <c r="W42" s="23"/>
-      <c r="X42" s="23"/>
-      <c r="Y42" s="23"/>
-      <c r="Z42" s="23"/>
-      <c r="AA42" s="23"/>
-      <c r="AB42" s="23"/>
-      <c r="AC42" s="23"/>
-      <c r="AD42" s="23"/>
-      <c r="AE42" s="23"/>
-      <c r="AF42" s="23"/>
+      <c r="H42" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I42" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K42" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M42" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N42" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O42" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P42" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q42" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R42" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S42" s="20"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="20"/>
+      <c r="V42" s="20"/>
+      <c r="W42" s="20"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+      <c r="Z42" s="20"/>
+      <c r="AA42" s="20"/>
+      <c r="AB42" s="20"/>
+      <c r="AC42" s="20"/>
+      <c r="AD42" s="20"/>
+      <c r="AE42" s="20"/>
+      <c r="AF42" s="20"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
+      <c r="A43" s="37"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4113,56 +4110,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K43" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L43" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N43" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="O43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q43" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R43" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S43" s="23"/>
-      <c r="T43" s="23"/>
-      <c r="U43" s="23"/>
-      <c r="V43" s="23"/>
-      <c r="W43" s="23"/>
-      <c r="X43" s="23"/>
-      <c r="Y43" s="23"/>
-      <c r="Z43" s="23"/>
-      <c r="AA43" s="23"/>
-      <c r="AB43" s="23"/>
-      <c r="AC43" s="23"/>
-      <c r="AD43" s="23"/>
-      <c r="AE43" s="23"/>
-      <c r="AF43" s="23"/>
+      <c r="H43" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K43" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N43" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O43" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P43" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q43" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R43" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="20"/>
+      <c r="W43" s="20"/>
+      <c r="X43" s="20"/>
+      <c r="Y43" s="20"/>
+      <c r="Z43" s="20"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
+      <c r="AC43" s="20"/>
+      <c r="AD43" s="20"/>
+      <c r="AE43" s="20"/>
+      <c r="AF43" s="20"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4178,56 +4175,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H44" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J44" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K44" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L44" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N44" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O44" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P44" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R44" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S44" s="23"/>
-      <c r="T44" s="23"/>
-      <c r="U44" s="23"/>
-      <c r="V44" s="23"/>
-      <c r="W44" s="23"/>
-      <c r="X44" s="23"/>
-      <c r="Y44" s="23"/>
-      <c r="Z44" s="23"/>
-      <c r="AA44" s="23"/>
-      <c r="AB44" s="23"/>
-      <c r="AC44" s="23"/>
-      <c r="AD44" s="23"/>
-      <c r="AE44" s="23"/>
-      <c r="AF44" s="23"/>
+      <c r="H44" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K44" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L44" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M44" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N44" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O44" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R44" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S44" s="20"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="20"/>
+      <c r="W44" s="20"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="20"/>
+      <c r="AA44" s="20"/>
+      <c r="AB44" s="20"/>
+      <c r="AC44" s="20"/>
+      <c r="AD44" s="20"/>
+      <c r="AE44" s="20"/>
+      <c r="AF44" s="20"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="40"/>
+      <c r="A45" s="38"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4243,56 +4240,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M45" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R45" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S45" s="23"/>
-      <c r="T45" s="23"/>
-      <c r="U45" s="23"/>
-      <c r="V45" s="23"/>
-      <c r="W45" s="23"/>
-      <c r="X45" s="23"/>
-      <c r="Y45" s="23"/>
-      <c r="Z45" s="23"/>
-      <c r="AA45" s="23"/>
-      <c r="AB45" s="23"/>
-      <c r="AC45" s="23"/>
-      <c r="AD45" s="23"/>
-      <c r="AE45" s="23"/>
-      <c r="AF45" s="23"/>
+      <c r="H45" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K45" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L45" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N45" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O45" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P45" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q45" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R45" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S45" s="20"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="20"/>
+      <c r="V45" s="20"/>
+      <c r="W45" s="20"/>
+      <c r="X45" s="20"/>
+      <c r="Y45" s="20"/>
+      <c r="Z45" s="20"/>
+      <c r="AA45" s="20"/>
+      <c r="AB45" s="20"/>
+      <c r="AC45" s="20"/>
+      <c r="AD45" s="20"/>
+      <c r="AE45" s="20"/>
+      <c r="AF45" s="20"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="36" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4310,56 +4307,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M46" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S46" s="23"/>
-      <c r="T46" s="23"/>
-      <c r="U46" s="23"/>
-      <c r="V46" s="23"/>
-      <c r="W46" s="23"/>
-      <c r="X46" s="23"/>
-      <c r="Y46" s="23"/>
-      <c r="Z46" s="23"/>
-      <c r="AA46" s="23"/>
-      <c r="AB46" s="23"/>
-      <c r="AC46" s="23"/>
-      <c r="AD46" s="23"/>
-      <c r="AE46" s="23"/>
-      <c r="AF46" s="23"/>
+      <c r="H46" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K46" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L46" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M46" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N46" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O46" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P46" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q46" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R46" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S46" s="20"/>
+      <c r="T46" s="20"/>
+      <c r="U46" s="20"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="20"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="20"/>
+      <c r="AA46" s="20"/>
+      <c r="AB46" s="20"/>
+      <c r="AC46" s="20"/>
+      <c r="AD46" s="20"/>
+      <c r="AE46" s="20"/>
+      <c r="AF46" s="20"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="39"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4375,56 +4372,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="K47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="M47" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q47" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R47" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S47" s="23"/>
-      <c r="T47" s="23"/>
-      <c r="U47" s="23"/>
-      <c r="V47" s="23"/>
-      <c r="W47" s="23"/>
-      <c r="X47" s="23"/>
-      <c r="Y47" s="23"/>
-      <c r="Z47" s="23"/>
-      <c r="AA47" s="23"/>
-      <c r="AB47" s="23"/>
-      <c r="AC47" s="23"/>
-      <c r="AD47" s="23"/>
-      <c r="AE47" s="23"/>
-      <c r="AF47" s="23"/>
+      <c r="H47" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="I47" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K47" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L47" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M47" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N47" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="O47" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P47" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q47" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R47" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S47" s="20"/>
+      <c r="T47" s="20"/>
+      <c r="U47" s="20"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="20"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="20"/>
+      <c r="AA47" s="20"/>
+      <c r="AB47" s="20"/>
+      <c r="AC47" s="20"/>
+      <c r="AD47" s="20"/>
+      <c r="AE47" s="20"/>
+      <c r="AF47" s="20"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4440,56 +4437,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M48" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R48" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="S48" s="23"/>
-      <c r="T48" s="23"/>
-      <c r="U48" s="23"/>
-      <c r="V48" s="23"/>
-      <c r="W48" s="23"/>
-      <c r="X48" s="23"/>
-      <c r="Y48" s="23"/>
-      <c r="Z48" s="23"/>
-      <c r="AA48" s="23"/>
-      <c r="AB48" s="23"/>
-      <c r="AC48" s="23"/>
-      <c r="AD48" s="23"/>
-      <c r="AE48" s="23"/>
-      <c r="AF48" s="23"/>
+      <c r="H48" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K48" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L48" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M48" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N48" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O48" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P48" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q48" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R48" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S48" s="20"/>
+      <c r="T48" s="20"/>
+      <c r="U48" s="20"/>
+      <c r="V48" s="20"/>
+      <c r="W48" s="20"/>
+      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
+      <c r="Z48" s="20"/>
+      <c r="AA48" s="20"/>
+      <c r="AB48" s="20"/>
+      <c r="AC48" s="20"/>
+      <c r="AD48" s="20"/>
+      <c r="AE48" s="20"/>
+      <c r="AF48" s="20"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="39"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4505,56 +4502,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="I49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="J49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="K49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="L49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="M49" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="O49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="P49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q49" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="R49" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S49" s="23"/>
-      <c r="T49" s="23"/>
-      <c r="U49" s="23"/>
-      <c r="V49" s="23"/>
-      <c r="W49" s="23"/>
-      <c r="X49" s="23"/>
-      <c r="Y49" s="23"/>
-      <c r="Z49" s="23"/>
-      <c r="AA49" s="23"/>
-      <c r="AB49" s="23"/>
-      <c r="AC49" s="23"/>
-      <c r="AD49" s="23"/>
-      <c r="AE49" s="23"/>
-      <c r="AF49" s="23"/>
+      <c r="H49" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K49" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="L49" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M49" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N49" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O49" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P49" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q49" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="R49" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="S49" s="20"/>
+      <c r="T49" s="20"/>
+      <c r="U49" s="20"/>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="20"/>
+      <c r="AC49" s="20"/>
+      <c r="AD49" s="20"/>
+      <c r="AE49" s="20"/>
+      <c r="AF49" s="20"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="39"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4570,56 +4567,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="I50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="L50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M50" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="N50" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R50" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S50" s="23"/>
-      <c r="T50" s="23"/>
-      <c r="U50" s="23"/>
-      <c r="V50" s="23"/>
-      <c r="W50" s="23"/>
-      <c r="X50" s="23"/>
-      <c r="Y50" s="23"/>
-      <c r="Z50" s="23"/>
-      <c r="AA50" s="23"/>
-      <c r="AB50" s="23"/>
-      <c r="AC50" s="23"/>
-      <c r="AD50" s="23"/>
-      <c r="AE50" s="23"/>
-      <c r="AF50" s="23"/>
+      <c r="H50" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L50" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M50" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="N50" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O50" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P50" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="R50" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S50" s="20"/>
+      <c r="T50" s="20"/>
+      <c r="U50" s="20"/>
+      <c r="V50" s="20"/>
+      <c r="W50" s="20"/>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
+      <c r="Z50" s="20"/>
+      <c r="AA50" s="20"/>
+      <c r="AB50" s="20"/>
+      <c r="AC50" s="20"/>
+      <c r="AD50" s="20"/>
+      <c r="AE50" s="20"/>
+      <c r="AF50" s="20"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4635,56 +4632,56 @@
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="H51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I51" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="J51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="K51" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="L51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="N51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="O51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="P51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="R51" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="S51" s="23"/>
-      <c r="T51" s="23"/>
-      <c r="U51" s="23"/>
-      <c r="V51" s="23"/>
-      <c r="W51" s="23"/>
-      <c r="X51" s="23"/>
-      <c r="Y51" s="23"/>
-      <c r="Z51" s="23"/>
-      <c r="AA51" s="23"/>
-      <c r="AB51" s="23"/>
-      <c r="AC51" s="23"/>
-      <c r="AD51" s="23"/>
-      <c r="AE51" s="23"/>
-      <c r="AF51" s="23"/>
+      <c r="H51" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I51" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="J51" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K51" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L51" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="M51" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N51" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="O51" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q51" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="R51" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="S51" s="20"/>
+      <c r="T51" s="20"/>
+      <c r="U51" s="20"/>
+      <c r="V51" s="20"/>
+      <c r="W51" s="20"/>
+      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
+      <c r="Z51" s="20"/>
+      <c r="AA51" s="20"/>
+      <c r="AB51" s="20"/>
+      <c r="AC51" s="20"/>
+      <c r="AD51" s="20"/>
+      <c r="AE51" s="20"/>
+      <c r="AF51" s="20"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="43" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4702,56 +4699,56 @@
         <f t="shared" ref="G52:G75" si="2">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
-      <c r="H52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I52" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K52" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M52" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q52" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R52" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S52" s="25"/>
-      <c r="T52" s="25"/>
-      <c r="U52" s="25"/>
-      <c r="V52" s="25"/>
-      <c r="W52" s="25"/>
-      <c r="X52" s="25"/>
-      <c r="Y52" s="25"/>
-      <c r="Z52" s="25"/>
-      <c r="AA52" s="25"/>
-      <c r="AB52" s="25"/>
-      <c r="AC52" s="25"/>
-      <c r="AD52" s="25"/>
-      <c r="AE52" s="25"/>
-      <c r="AF52" s="25"/>
+      <c r="H52" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I52" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J52" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K52" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L52" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N52" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O52" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P52" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q52" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R52" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S52" s="22"/>
+      <c r="T52" s="22"/>
+      <c r="U52" s="22"/>
+      <c r="V52" s="22"/>
+      <c r="W52" s="22"/>
+      <c r="X52" s="22"/>
+      <c r="Y52" s="22"/>
+      <c r="Z52" s="22"/>
+      <c r="AA52" s="22"/>
+      <c r="AB52" s="22"/>
+      <c r="AC52" s="22"/>
+      <c r="AD52" s="22"/>
+      <c r="AE52" s="22"/>
+      <c r="AF52" s="22"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
+      <c r="A53" s="44"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4767,56 +4764,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J53" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="K53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L53" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M53" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="R53" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="S53" s="25"/>
-      <c r="T53" s="25"/>
-      <c r="U53" s="25"/>
-      <c r="V53" s="25"/>
-      <c r="W53" s="25"/>
-      <c r="X53" s="25"/>
-      <c r="Y53" s="25"/>
-      <c r="Z53" s="25"/>
-      <c r="AA53" s="25"/>
-      <c r="AB53" s="25"/>
-      <c r="AC53" s="25"/>
-      <c r="AD53" s="25"/>
-      <c r="AE53" s="25"/>
-      <c r="AF53" s="25"/>
+      <c r="H53" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K53" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M53" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N53" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P53" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="S53" s="22"/>
+      <c r="T53" s="22"/>
+      <c r="U53" s="22"/>
+      <c r="V53" s="22"/>
+      <c r="W53" s="22"/>
+      <c r="X53" s="22"/>
+      <c r="Y53" s="22"/>
+      <c r="Z53" s="22"/>
+      <c r="AA53" s="22"/>
+      <c r="AB53" s="22"/>
+      <c r="AC53" s="22"/>
+      <c r="AD53" s="22"/>
+      <c r="AE53" s="22"/>
+      <c r="AF53" s="22"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
+      <c r="A54" s="44"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4832,56 +4829,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M54" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R54" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S54" s="25"/>
-      <c r="T54" s="25"/>
-      <c r="U54" s="25"/>
-      <c r="V54" s="25"/>
-      <c r="W54" s="25"/>
-      <c r="X54" s="25"/>
-      <c r="Y54" s="25"/>
-      <c r="Z54" s="25"/>
-      <c r="AA54" s="25"/>
-      <c r="AB54" s="25"/>
-      <c r="AC54" s="25"/>
-      <c r="AD54" s="25"/>
-      <c r="AE54" s="25"/>
-      <c r="AF54" s="25"/>
+      <c r="H54" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I54" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J54" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K54" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L54" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M54" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N54" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O54" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P54" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q54" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R54" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S54" s="22"/>
+      <c r="T54" s="22"/>
+      <c r="U54" s="22"/>
+      <c r="V54" s="22"/>
+      <c r="W54" s="22"/>
+      <c r="X54" s="22"/>
+      <c r="Y54" s="22"/>
+      <c r="Z54" s="22"/>
+      <c r="AA54" s="22"/>
+      <c r="AB54" s="22"/>
+      <c r="AC54" s="22"/>
+      <c r="AD54" s="22"/>
+      <c r="AE54" s="22"/>
+      <c r="AF54" s="22"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
+      <c r="A55" s="44"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4897,57 +4894,57 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H55" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I55" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K55" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M55" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="O55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P55" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q55" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R55" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S55" s="25"/>
-      <c r="T55" s="25"/>
-      <c r="U55" s="25"/>
-      <c r="V55" s="25"/>
-      <c r="W55" s="25"/>
-      <c r="X55" s="25"/>
-      <c r="Y55" s="25"/>
-      <c r="Z55" s="25"/>
-      <c r="AA55" s="25"/>
-      <c r="AB55" s="25"/>
-      <c r="AC55" s="25"/>
-      <c r="AD55" s="25"/>
-      <c r="AE55" s="25"/>
-      <c r="AF55" s="25"/>
-      <c r="AK55" s="31"/>
+      <c r="H55" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J55" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K55" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M55" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N55" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O55" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P55" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q55" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="R55" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S55" s="22"/>
+      <c r="T55" s="22"/>
+      <c r="U55" s="22"/>
+      <c r="V55" s="22"/>
+      <c r="W55" s="22"/>
+      <c r="X55" s="22"/>
+      <c r="Y55" s="22"/>
+      <c r="Z55" s="22"/>
+      <c r="AA55" s="22"/>
+      <c r="AB55" s="22"/>
+      <c r="AC55" s="22"/>
+      <c r="AD55" s="22"/>
+      <c r="AE55" s="22"/>
+      <c r="AF55" s="22"/>
+      <c r="AK55" s="28"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
+      <c r="A56" s="44"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -4963,56 +4960,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I56" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M56" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="N56" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q56" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="R56" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S56" s="25"/>
-      <c r="T56" s="25"/>
-      <c r="U56" s="25"/>
-      <c r="V56" s="25"/>
-      <c r="W56" s="25"/>
-      <c r="X56" s="25"/>
-      <c r="Y56" s="25"/>
-      <c r="Z56" s="25"/>
-      <c r="AA56" s="25"/>
-      <c r="AB56" s="25"/>
-      <c r="AC56" s="25"/>
-      <c r="AD56" s="25"/>
-      <c r="AE56" s="25"/>
-      <c r="AF56" s="25"/>
+      <c r="H56" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="I56" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J56" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K56" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L56" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M56" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N56" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O56" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P56" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q56" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R56" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="S56" s="22"/>
+      <c r="T56" s="22"/>
+      <c r="U56" s="22"/>
+      <c r="V56" s="22"/>
+      <c r="W56" s="22"/>
+      <c r="X56" s="22"/>
+      <c r="Y56" s="22"/>
+      <c r="Z56" s="22"/>
+      <c r="AA56" s="22"/>
+      <c r="AB56" s="22"/>
+      <c r="AC56" s="22"/>
+      <c r="AD56" s="22"/>
+      <c r="AE56" s="22"/>
+      <c r="AF56" s="22"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="47"/>
+      <c r="A57" s="45"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5028,56 +5025,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H57" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I57" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J57" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="K57" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L57" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M57" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="N57" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="O57" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P57" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q57" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="R57" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S57" s="25"/>
-      <c r="T57" s="25"/>
-      <c r="U57" s="25"/>
-      <c r="V57" s="25"/>
-      <c r="W57" s="25"/>
-      <c r="X57" s="25"/>
-      <c r="Y57" s="25"/>
-      <c r="Z57" s="25"/>
-      <c r="AA57" s="25"/>
-      <c r="AB57" s="25"/>
-      <c r="AC57" s="25"/>
-      <c r="AD57" s="25"/>
-      <c r="AE57" s="25"/>
-      <c r="AF57" s="25"/>
+      <c r="H57" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J57" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K57" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L57" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M57" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N57" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O57" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="P57" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q57" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R57" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S57" s="22"/>
+      <c r="T57" s="22"/>
+      <c r="U57" s="22"/>
+      <c r="V57" s="22"/>
+      <c r="W57" s="22"/>
+      <c r="X57" s="22"/>
+      <c r="Y57" s="22"/>
+      <c r="Z57" s="22"/>
+      <c r="AA57" s="22"/>
+      <c r="AB57" s="22"/>
+      <c r="AC57" s="22"/>
+      <c r="AD57" s="22"/>
+      <c r="AE57" s="22"/>
+      <c r="AF57" s="22"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48" t="s">
+      <c r="A58" s="46" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5095,56 +5092,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M58" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q58" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R58" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S58" s="25"/>
-      <c r="T58" s="25"/>
-      <c r="U58" s="25"/>
-      <c r="V58" s="25"/>
-      <c r="W58" s="25"/>
-      <c r="X58" s="25"/>
-      <c r="Y58" s="25"/>
-      <c r="Z58" s="25"/>
-      <c r="AA58" s="25"/>
-      <c r="AB58" s="25"/>
-      <c r="AC58" s="25"/>
-      <c r="AD58" s="25"/>
-      <c r="AE58" s="25"/>
-      <c r="AF58" s="25"/>
+      <c r="H58" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J58" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K58" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L58" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M58" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N58" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O58" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P58" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R58" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S58" s="22"/>
+      <c r="T58" s="22"/>
+      <c r="U58" s="22"/>
+      <c r="V58" s="22"/>
+      <c r="W58" s="22"/>
+      <c r="X58" s="22"/>
+      <c r="Y58" s="22"/>
+      <c r="Z58" s="22"/>
+      <c r="AA58" s="22"/>
+      <c r="AB58" s="22"/>
+      <c r="AC58" s="22"/>
+      <c r="AD58" s="22"/>
+      <c r="AE58" s="22"/>
+      <c r="AF58" s="22"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="49"/>
+      <c r="A59" s="47"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5160,56 +5157,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I59" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M59" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q59" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="R59" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S59" s="25"/>
-      <c r="T59" s="25"/>
-      <c r="U59" s="25"/>
-      <c r="V59" s="25"/>
-      <c r="W59" s="25"/>
-      <c r="X59" s="25"/>
-      <c r="Y59" s="25"/>
-      <c r="Z59" s="25"/>
-      <c r="AA59" s="25"/>
-      <c r="AB59" s="25"/>
-      <c r="AC59" s="25"/>
-      <c r="AD59" s="25"/>
-      <c r="AE59" s="25"/>
-      <c r="AF59" s="25"/>
+      <c r="H59" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I59" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J59" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K59" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L59" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M59" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N59" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O59" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P59" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q59" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R59" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S59" s="22"/>
+      <c r="T59" s="22"/>
+      <c r="U59" s="22"/>
+      <c r="V59" s="22"/>
+      <c r="W59" s="22"/>
+      <c r="X59" s="22"/>
+      <c r="Y59" s="22"/>
+      <c r="Z59" s="22"/>
+      <c r="AA59" s="22"/>
+      <c r="AB59" s="22"/>
+      <c r="AC59" s="22"/>
+      <c r="AD59" s="22"/>
+      <c r="AE59" s="22"/>
+      <c r="AF59" s="22"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="49"/>
+      <c r="A60" s="47"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5225,56 +5222,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M60" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R60" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S60" s="25"/>
-      <c r="T60" s="25"/>
-      <c r="U60" s="25"/>
-      <c r="V60" s="25"/>
-      <c r="W60" s="25"/>
-      <c r="X60" s="25"/>
-      <c r="Y60" s="25"/>
-      <c r="Z60" s="25"/>
-      <c r="AA60" s="25"/>
-      <c r="AB60" s="25"/>
-      <c r="AC60" s="25"/>
-      <c r="AD60" s="25"/>
-      <c r="AE60" s="25"/>
-      <c r="AF60" s="25"/>
+      <c r="H60" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I60" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J60" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K60" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L60" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M60" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N60" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O60" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P60" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q60" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R60" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S60" s="22"/>
+      <c r="T60" s="22"/>
+      <c r="U60" s="22"/>
+      <c r="V60" s="22"/>
+      <c r="W60" s="22"/>
+      <c r="X60" s="22"/>
+      <c r="Y60" s="22"/>
+      <c r="Z60" s="22"/>
+      <c r="AA60" s="22"/>
+      <c r="AB60" s="22"/>
+      <c r="AC60" s="22"/>
+      <c r="AD60" s="22"/>
+      <c r="AE60" s="22"/>
+      <c r="AF60" s="22"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+      <c r="A61" s="47"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5290,56 +5287,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H61" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J61" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="K61" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="L61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M61" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q61" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="R61" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="S61" s="25"/>
-      <c r="T61" s="25"/>
-      <c r="U61" s="25"/>
-      <c r="V61" s="25"/>
-      <c r="W61" s="25"/>
-      <c r="X61" s="25"/>
-      <c r="Y61" s="25"/>
-      <c r="Z61" s="25"/>
-      <c r="AA61" s="25"/>
-      <c r="AB61" s="25"/>
-      <c r="AC61" s="25"/>
-      <c r="AD61" s="25"/>
-      <c r="AE61" s="25"/>
-      <c r="AF61" s="25"/>
+      <c r="H61" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I61" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J61" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K61" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L61" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N61" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O61" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P61" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q61" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R61" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S61" s="22"/>
+      <c r="T61" s="22"/>
+      <c r="U61" s="22"/>
+      <c r="V61" s="22"/>
+      <c r="W61" s="22"/>
+      <c r="X61" s="22"/>
+      <c r="Y61" s="22"/>
+      <c r="Z61" s="22"/>
+      <c r="AA61" s="22"/>
+      <c r="AB61" s="22"/>
+      <c r="AC61" s="22"/>
+      <c r="AD61" s="22"/>
+      <c r="AE61" s="22"/>
+      <c r="AF61" s="22"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="49"/>
+      <c r="A62" s="47"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5355,56 +5352,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I62" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J62" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="K62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M62" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O62" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="R62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S62" s="25"/>
-      <c r="T62" s="25"/>
-      <c r="U62" s="25"/>
-      <c r="V62" s="25"/>
-      <c r="W62" s="25"/>
-      <c r="X62" s="25"/>
-      <c r="Y62" s="25"/>
-      <c r="Z62" s="25"/>
-      <c r="AA62" s="25"/>
-      <c r="AB62" s="25"/>
-      <c r="AC62" s="25"/>
-      <c r="AD62" s="25"/>
-      <c r="AE62" s="25"/>
-      <c r="AF62" s="25"/>
+      <c r="H62" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J62" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K62" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L62" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N62" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O62" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="P62" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q62" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R62" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S62" s="22"/>
+      <c r="T62" s="22"/>
+      <c r="U62" s="22"/>
+      <c r="V62" s="22"/>
+      <c r="W62" s="22"/>
+      <c r="X62" s="22"/>
+      <c r="Y62" s="22"/>
+      <c r="Z62" s="22"/>
+      <c r="AA62" s="22"/>
+      <c r="AB62" s="22"/>
+      <c r="AC62" s="22"/>
+      <c r="AD62" s="22"/>
+      <c r="AE62" s="22"/>
+      <c r="AF62" s="22"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="50"/>
+      <c r="A63" s="48"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5420,56 +5417,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M63" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="R63" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="S63" s="25"/>
-      <c r="T63" s="25"/>
-      <c r="U63" s="25"/>
-      <c r="V63" s="25"/>
-      <c r="W63" s="25"/>
-      <c r="X63" s="25"/>
-      <c r="Y63" s="25"/>
-      <c r="Z63" s="25"/>
-      <c r="AA63" s="25"/>
-      <c r="AB63" s="25"/>
-      <c r="AC63" s="25"/>
-      <c r="AD63" s="25"/>
-      <c r="AE63" s="25"/>
-      <c r="AF63" s="25"/>
+      <c r="H63" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="I63" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J63" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K63" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L63" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N63" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O63" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P63" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q63" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R63" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="S63" s="22"/>
+      <c r="T63" s="22"/>
+      <c r="U63" s="22"/>
+      <c r="V63" s="22"/>
+      <c r="W63" s="22"/>
+      <c r="X63" s="22"/>
+      <c r="Y63" s="22"/>
+      <c r="Z63" s="22"/>
+      <c r="AA63" s="22"/>
+      <c r="AB63" s="22"/>
+      <c r="AC63" s="22"/>
+      <c r="AD63" s="22"/>
+      <c r="AE63" s="22"/>
+      <c r="AF63" s="22"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="30" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5487,56 +5484,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M64" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R64" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S64" s="25"/>
-      <c r="T64" s="25"/>
-      <c r="U64" s="25"/>
-      <c r="V64" s="25"/>
-      <c r="W64" s="25"/>
-      <c r="X64" s="25"/>
-      <c r="Y64" s="25"/>
-      <c r="Z64" s="25"/>
-      <c r="AA64" s="25"/>
-      <c r="AB64" s="25"/>
-      <c r="AC64" s="25"/>
-      <c r="AD64" s="25"/>
-      <c r="AE64" s="25"/>
-      <c r="AF64" s="25"/>
+      <c r="H64" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I64" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J64" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K64" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L64" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N64" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O64" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P64" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q64" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R64" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S64" s="22"/>
+      <c r="T64" s="22"/>
+      <c r="U64" s="22"/>
+      <c r="V64" s="22"/>
+      <c r="W64" s="22"/>
+      <c r="X64" s="22"/>
+      <c r="Y64" s="22"/>
+      <c r="Z64" s="22"/>
+      <c r="AA64" s="22"/>
+      <c r="AB64" s="22"/>
+      <c r="AC64" s="22"/>
+      <c r="AD64" s="22"/>
+      <c r="AE64" s="22"/>
+      <c r="AF64" s="22"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5552,56 +5549,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M65" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="R65" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="S65" s="25"/>
-      <c r="T65" s="25"/>
-      <c r="U65" s="25"/>
-      <c r="V65" s="25"/>
-      <c r="W65" s="25"/>
-      <c r="X65" s="25"/>
-      <c r="Y65" s="25"/>
-      <c r="Z65" s="25"/>
-      <c r="AA65" s="25"/>
-      <c r="AB65" s="25"/>
-      <c r="AC65" s="25"/>
-      <c r="AD65" s="25"/>
-      <c r="AE65" s="25"/>
-      <c r="AF65" s="25"/>
+      <c r="H65" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="I65" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J65" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K65" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L65" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N65" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O65" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P65" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q65" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R65" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="S65" s="22"/>
+      <c r="T65" s="22"/>
+      <c r="U65" s="22"/>
+      <c r="V65" s="22"/>
+      <c r="W65" s="22"/>
+      <c r="X65" s="22"/>
+      <c r="Y65" s="22"/>
+      <c r="Z65" s="22"/>
+      <c r="AA65" s="22"/>
+      <c r="AB65" s="22"/>
+      <c r="AC65" s="22"/>
+      <c r="AD65" s="22"/>
+      <c r="AE65" s="22"/>
+      <c r="AF65" s="22"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5617,56 +5614,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M66" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R66" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S66" s="25"/>
-      <c r="T66" s="25"/>
-      <c r="U66" s="25"/>
-      <c r="V66" s="25"/>
-      <c r="W66" s="25"/>
-      <c r="X66" s="25"/>
-      <c r="Y66" s="25"/>
-      <c r="Z66" s="25"/>
-      <c r="AA66" s="25"/>
-      <c r="AB66" s="25"/>
-      <c r="AC66" s="25"/>
-      <c r="AD66" s="25"/>
-      <c r="AE66" s="25"/>
-      <c r="AF66" s="25"/>
+      <c r="H66" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I66" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J66" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K66" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L66" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N66" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O66" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P66" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q66" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R66" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S66" s="22"/>
+      <c r="T66" s="22"/>
+      <c r="U66" s="22"/>
+      <c r="V66" s="22"/>
+      <c r="W66" s="22"/>
+      <c r="X66" s="22"/>
+      <c r="Y66" s="22"/>
+      <c r="Z66" s="22"/>
+      <c r="AA66" s="22"/>
+      <c r="AB66" s="22"/>
+      <c r="AC66" s="22"/>
+      <c r="AD66" s="22"/>
+      <c r="AE66" s="22"/>
+      <c r="AF66" s="22"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5682,56 +5679,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M67" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N67" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R67" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S67" s="25"/>
-      <c r="T67" s="25"/>
-      <c r="U67" s="25"/>
-      <c r="V67" s="25"/>
-      <c r="W67" s="25"/>
-      <c r="X67" s="25"/>
-      <c r="Y67" s="25"/>
-      <c r="Z67" s="25"/>
-      <c r="AA67" s="25"/>
-      <c r="AB67" s="25"/>
-      <c r="AC67" s="25"/>
-      <c r="AD67" s="25"/>
-      <c r="AE67" s="25"/>
-      <c r="AF67" s="25"/>
+      <c r="H67" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I67" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J67" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K67" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L67" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N67" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O67" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P67" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q67" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R67" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S67" s="22"/>
+      <c r="T67" s="22"/>
+      <c r="U67" s="22"/>
+      <c r="V67" s="22"/>
+      <c r="W67" s="22"/>
+      <c r="X67" s="22"/>
+      <c r="Y67" s="22"/>
+      <c r="Z67" s="22"/>
+      <c r="AA67" s="22"/>
+      <c r="AB67" s="22"/>
+      <c r="AC67" s="22"/>
+      <c r="AD67" s="22"/>
+      <c r="AE67" s="22"/>
+      <c r="AF67" s="22"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5747,56 +5744,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H68" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I68" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J68" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="K68" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L68" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M68" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N68" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O68" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P68" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q68" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="R68" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S68" s="25"/>
-      <c r="T68" s="25"/>
-      <c r="U68" s="25"/>
-      <c r="V68" s="25"/>
-      <c r="W68" s="25"/>
-      <c r="X68" s="25"/>
-      <c r="Y68" s="25"/>
-      <c r="Z68" s="25"/>
-      <c r="AA68" s="25"/>
-      <c r="AB68" s="25"/>
-      <c r="AC68" s="25"/>
-      <c r="AD68" s="25"/>
-      <c r="AE68" s="25"/>
-      <c r="AF68" s="25"/>
+      <c r="H68" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I68" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J68" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K68" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L68" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N68" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O68" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="P68" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q68" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R68" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="S68" s="22"/>
+      <c r="T68" s="22"/>
+      <c r="U68" s="22"/>
+      <c r="V68" s="22"/>
+      <c r="W68" s="22"/>
+      <c r="X68" s="22"/>
+      <c r="Y68" s="22"/>
+      <c r="Z68" s="22"/>
+      <c r="AA68" s="22"/>
+      <c r="AB68" s="22"/>
+      <c r="AC68" s="22"/>
+      <c r="AD68" s="22"/>
+      <c r="AE68" s="22"/>
+      <c r="AF68" s="22"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="34"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5812,56 +5809,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I69" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J69" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="K69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M69" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N69" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q69" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="R69" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="S69" s="25"/>
-      <c r="T69" s="25"/>
-      <c r="U69" s="25"/>
-      <c r="V69" s="25"/>
-      <c r="W69" s="25"/>
-      <c r="X69" s="25"/>
-      <c r="Y69" s="25"/>
-      <c r="Z69" s="25"/>
-      <c r="AA69" s="25"/>
-      <c r="AB69" s="25"/>
-      <c r="AC69" s="25"/>
-      <c r="AD69" s="25"/>
-      <c r="AE69" s="25"/>
-      <c r="AF69" s="25"/>
+      <c r="H69" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I69" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J69" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K69" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L69" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N69" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O69" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="P69" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q69" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="R69" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S69" s="22"/>
+      <c r="T69" s="22"/>
+      <c r="U69" s="22"/>
+      <c r="V69" s="22"/>
+      <c r="W69" s="22"/>
+      <c r="X69" s="22"/>
+      <c r="Y69" s="22"/>
+      <c r="Z69" s="22"/>
+      <c r="AA69" s="22"/>
+      <c r="AB69" s="22"/>
+      <c r="AC69" s="22"/>
+      <c r="AD69" s="22"/>
+      <c r="AE69" s="22"/>
+      <c r="AF69" s="22"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="33" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5879,56 +5876,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I70" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J70" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K70" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L70" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M70" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="O70" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="P70" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q70" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R70" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S70" s="25"/>
-      <c r="T70" s="25"/>
-      <c r="U70" s="25"/>
-      <c r="V70" s="25"/>
-      <c r="W70" s="25"/>
-      <c r="X70" s="25"/>
-      <c r="Y70" s="25"/>
-      <c r="Z70" s="25"/>
-      <c r="AA70" s="25"/>
-      <c r="AB70" s="25"/>
-      <c r="AC70" s="25"/>
-      <c r="AD70" s="25"/>
-      <c r="AE70" s="25"/>
-      <c r="AF70" s="25"/>
+      <c r="H70" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="I70" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J70" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K70" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L70" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="M70" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N70" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O70" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P70" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q70" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="R70" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S70" s="22"/>
+      <c r="T70" s="22"/>
+      <c r="U70" s="22"/>
+      <c r="V70" s="22"/>
+      <c r="W70" s="22"/>
+      <c r="X70" s="22"/>
+      <c r="Y70" s="22"/>
+      <c r="Z70" s="22"/>
+      <c r="AA70" s="22"/>
+      <c r="AB70" s="22"/>
+      <c r="AC70" s="22"/>
+      <c r="AD70" s="22"/>
+      <c r="AE70" s="22"/>
+      <c r="AF70" s="22"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
+      <c r="A71" s="34"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5944,56 +5941,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="I71" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J71" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M71" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="O71" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P71" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q71" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="R71" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="S71" s="25"/>
-      <c r="T71" s="25"/>
-      <c r="U71" s="25"/>
-      <c r="V71" s="25"/>
-      <c r="W71" s="25"/>
-      <c r="X71" s="25"/>
-      <c r="Y71" s="25"/>
-      <c r="Z71" s="25"/>
-      <c r="AA71" s="25"/>
-      <c r="AB71" s="25"/>
-      <c r="AC71" s="25"/>
-      <c r="AD71" s="25"/>
-      <c r="AE71" s="25"/>
-      <c r="AF71" s="25"/>
+      <c r="H71" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I71" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J71" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K71" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L71" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="M71" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N71" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O71" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P71" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q71" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R71" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S71" s="22"/>
+      <c r="T71" s="22"/>
+      <c r="U71" s="22"/>
+      <c r="V71" s="22"/>
+      <c r="W71" s="22"/>
+      <c r="X71" s="22"/>
+      <c r="Y71" s="22"/>
+      <c r="Z71" s="22"/>
+      <c r="AA71" s="22"/>
+      <c r="AB71" s="22"/>
+      <c r="AC71" s="22"/>
+      <c r="AD71" s="22"/>
+      <c r="AE71" s="22"/>
+      <c r="AF71" s="22"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6009,56 +6006,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M72" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q72" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R72" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S72" s="25"/>
-      <c r="T72" s="25"/>
-      <c r="U72" s="25"/>
-      <c r="V72" s="25"/>
-      <c r="W72" s="25"/>
-      <c r="X72" s="25"/>
-      <c r="Y72" s="25"/>
-      <c r="Z72" s="25"/>
-      <c r="AA72" s="25"/>
-      <c r="AB72" s="25"/>
-      <c r="AC72" s="25"/>
-      <c r="AD72" s="25"/>
-      <c r="AE72" s="25"/>
-      <c r="AF72" s="25"/>
+      <c r="H72" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I72" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J72" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K72" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L72" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M72" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N72" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O72" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P72" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q72" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R72" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S72" s="22"/>
+      <c r="T72" s="22"/>
+      <c r="U72" s="22"/>
+      <c r="V72" s="22"/>
+      <c r="W72" s="22"/>
+      <c r="X72" s="22"/>
+      <c r="Y72" s="22"/>
+      <c r="Z72" s="22"/>
+      <c r="AA72" s="22"/>
+      <c r="AB72" s="22"/>
+      <c r="AC72" s="22"/>
+      <c r="AD72" s="22"/>
+      <c r="AE72" s="22"/>
+      <c r="AF72" s="22"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6074,56 +6071,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I73" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L73" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M73" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P73" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="R73" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="S73" s="25"/>
-      <c r="T73" s="25"/>
-      <c r="U73" s="25"/>
-      <c r="V73" s="25"/>
-      <c r="W73" s="25"/>
-      <c r="X73" s="25"/>
-      <c r="Y73" s="25"/>
-      <c r="Z73" s="25"/>
-      <c r="AA73" s="25"/>
-      <c r="AB73" s="25"/>
-      <c r="AC73" s="25"/>
-      <c r="AD73" s="25"/>
-      <c r="AE73" s="25"/>
-      <c r="AF73" s="25"/>
+      <c r="H73" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="I73" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J73" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K73" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L73" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M73" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N73" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O73" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="P73" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q73" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R73" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="S73" s="22"/>
+      <c r="T73" s="22"/>
+      <c r="U73" s="22"/>
+      <c r="V73" s="22"/>
+      <c r="W73" s="22"/>
+      <c r="X73" s="22"/>
+      <c r="Y73" s="22"/>
+      <c r="Z73" s="22"/>
+      <c r="AA73" s="22"/>
+      <c r="AB73" s="22"/>
+      <c r="AC73" s="22"/>
+      <c r="AD73" s="22"/>
+      <c r="AE73" s="22"/>
+      <c r="AF73" s="22"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
+      <c r="A74" s="34"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6139,56 +6136,56 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="I74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="J74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="K74" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="M74" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="N74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="O74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="P74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q74" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="R74" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="S74" s="25"/>
-      <c r="T74" s="25"/>
-      <c r="U74" s="25"/>
-      <c r="V74" s="25"/>
-      <c r="W74" s="25"/>
-      <c r="X74" s="25"/>
-      <c r="Y74" s="25"/>
-      <c r="Z74" s="25"/>
-      <c r="AA74" s="25"/>
-      <c r="AB74" s="25"/>
-      <c r="AC74" s="25"/>
-      <c r="AD74" s="25"/>
-      <c r="AE74" s="25"/>
-      <c r="AF74" s="25"/>
+      <c r="H74" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="I74" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="J74" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K74" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L74" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M74" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N74" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="O74" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="P74" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q74" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="R74" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="S74" s="22"/>
+      <c r="T74" s="22"/>
+      <c r="U74" s="22"/>
+      <c r="V74" s="22"/>
+      <c r="W74" s="22"/>
+      <c r="X74" s="22"/>
+      <c r="Y74" s="22"/>
+      <c r="Z74" s="22"/>
+      <c r="AA74" s="22"/>
+      <c r="AB74" s="22"/>
+      <c r="AC74" s="22"/>
+      <c r="AD74" s="22"/>
+      <c r="AE74" s="22"/>
+      <c r="AF74" s="22"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6204,224 +6201,224 @@
         <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="H75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="K75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="L75" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="M75" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="N75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="O75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P75" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q75" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="R75" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="S75" s="25"/>
-      <c r="T75" s="25"/>
-      <c r="U75" s="25"/>
-      <c r="V75" s="25"/>
-      <c r="W75" s="25"/>
-      <c r="X75" s="25"/>
-      <c r="Y75" s="25"/>
-      <c r="Z75" s="25"/>
-      <c r="AA75" s="25"/>
-      <c r="AB75" s="25"/>
-      <c r="AC75" s="25"/>
-      <c r="AD75" s="25"/>
-      <c r="AE75" s="25"/>
-      <c r="AF75" s="25"/>
+      <c r="H75" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I75" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J75" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K75" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="L75" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="M75" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N75" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="O75" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="P75" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q75" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="R75" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S75" s="22"/>
+      <c r="T75" s="22"/>
+      <c r="U75" s="22"/>
+      <c r="V75" s="22"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="22"/>
+      <c r="Y75" s="22"/>
+      <c r="Z75" s="22"/>
+      <c r="AA75" s="22"/>
+      <c r="AB75" s="22"/>
+      <c r="AC75" s="22"/>
+      <c r="AD75" s="22"/>
+      <c r="AE75" s="22"/>
+      <c r="AF75" s="22"/>
     </row>
     <row r="76" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="27"/>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
-      <c r="D76" s="41" t="s">
+      <c r="A76" s="24"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="42"/>
-      <c r="F76" s="43"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="41"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>5</v>
-      </c>
-      <c r="H76" s="25">
+        <v>16</v>
+      </c>
+      <c r="H76" s="23">
+        <v>179</v>
+      </c>
+      <c r="I76" s="22">
+        <v>222</v>
+      </c>
+      <c r="J76" s="22">
+        <v>186</v>
+      </c>
+      <c r="K76" s="23">
+        <v>162</v>
+      </c>
+      <c r="L76" s="22">
         <v>172</v>
       </c>
-      <c r="I76" s="26">
+      <c r="M76" s="23">
+        <v>185</v>
+      </c>
+      <c r="N76" s="23">
+        <v>201</v>
+      </c>
+      <c r="O76" s="22">
+        <v>169</v>
+      </c>
+      <c r="P76" s="23">
         <v>180</v>
       </c>
-      <c r="J76" s="26">
-        <v>179</v>
-      </c>
-      <c r="K76" s="26">
-        <v>185</v>
-      </c>
-      <c r="L76" s="26">
-        <v>201</v>
-      </c>
-      <c r="M76" s="26">
-        <v>162</v>
-      </c>
-      <c r="N76" s="25">
-        <v>222</v>
-      </c>
-      <c r="O76" s="25">
+      <c r="Q76" s="22">
         <v>197</v>
       </c>
-      <c r="P76" s="25">
-        <v>169</v>
-      </c>
-      <c r="Q76" s="25">
+      <c r="R76" s="22">
         <v>190</v>
       </c>
-      <c r="R76" s="25">
-        <v>186</v>
-      </c>
-      <c r="S76" s="25"/>
-      <c r="T76" s="25"/>
-      <c r="U76" s="25"/>
-      <c r="V76" s="25"/>
-      <c r="W76" s="25"/>
-      <c r="X76" s="25"/>
-      <c r="Y76" s="25"/>
-      <c r="Z76" s="25"/>
-      <c r="AA76" s="25"/>
-      <c r="AB76" s="25"/>
-      <c r="AC76" s="25"/>
-      <c r="AD76" s="25"/>
-      <c r="AE76" s="25"/>
-      <c r="AF76" s="25"/>
+      <c r="S76" s="22"/>
+      <c r="T76" s="22"/>
+      <c r="U76" s="22"/>
+      <c r="V76" s="22"/>
+      <c r="W76" s="22"/>
+      <c r="X76" s="22"/>
+      <c r="Y76" s="22"/>
+      <c r="Z76" s="22"/>
+      <c r="AA76" s="22"/>
+      <c r="AB76" s="22"/>
+      <c r="AC76" s="22"/>
+      <c r="AD76" s="22"/>
+      <c r="AE76" s="22"/>
+      <c r="AF76" s="22"/>
     </row>
     <row r="77" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="27"/>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="44" t="s">
+      <c r="A77" s="24"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="43"/>
-      <c r="H77" s="28">
-        <f t="shared" ref="H77:AF77" si="3">SUM(H78:H81)</f>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="41"/>
+      <c r="H77" s="25">
+        <f>SUM(H78:H81)</f>
         <v>0</v>
       </c>
-      <c r="I77" s="28">
+      <c r="I77" s="25">
+        <f>SUM(I78:I81)</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="25">
+        <f>SUM(J78:J81)</f>
+        <v>0</v>
+      </c>
+      <c r="K77" s="25">
+        <f>SUM(K78:K81)</f>
+        <v>0</v>
+      </c>
+      <c r="L77" s="25">
+        <f>SUM(L78:L81)</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="25">
+        <f>SUM(M78:M81)</f>
+        <v>0</v>
+      </c>
+      <c r="N77" s="25">
+        <f>SUM(N78:N81)</f>
+        <v>0</v>
+      </c>
+      <c r="O77" s="25">
+        <f>SUM(O78:O81)</f>
+        <v>0</v>
+      </c>
+      <c r="P77" s="25">
+        <f>SUM(P78:P81)</f>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="25">
+        <f>SUM(Q78:Q81)</f>
+        <v>0</v>
+      </c>
+      <c r="R77" s="25">
+        <f>SUM(R78:R81)</f>
+        <v>0</v>
+      </c>
+      <c r="S77" s="25">
+        <f t="shared" ref="H77:AF77" si="3">SUM(S78:S81)</f>
+        <v>84</v>
+      </c>
+      <c r="T77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="28">
+        <v>84</v>
+      </c>
+      <c r="U77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="28">
+        <v>84</v>
+      </c>
+      <c r="V77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L77" s="28">
+        <v>84</v>
+      </c>
+      <c r="W77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="28">
+        <v>84</v>
+      </c>
+      <c r="X77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="28">
+        <v>84</v>
+      </c>
+      <c r="Y77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="28">
+        <v>84</v>
+      </c>
+      <c r="Z77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="28">
+        <v>84</v>
+      </c>
+      <c r="AA77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="28">
+        <v>84</v>
+      </c>
+      <c r="AB77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="28">
+        <v>84</v>
+      </c>
+      <c r="AC77" s="25">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S77" s="28">
+        <v>84</v>
+      </c>
+      <c r="AD77" s="25">
         <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="T77" s="28">
+        <v>84</v>
+      </c>
+      <c r="AE77" s="25">
         <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="U77" s="28">
+        <v>84</v>
+      </c>
+      <c r="AF77" s="25">
         <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="V77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="W77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="X77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="Y77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="Z77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="AA77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="AB77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="AC77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="AD77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="AE77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="AF77" s="28">
-        <f t="shared" si="3"/>
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6478,59 +6475,59 @@
       </c>
       <c r="S78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="4"/>
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -7723,6 +7720,10 @@
       <c r="G124" s="1"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H2:R77">
+    <sortCondition descending="1" ref="H3:R3"/>
+    <sortCondition descending="1" ref="H77:R77"/>
+  </sortState>
   <mergeCells count="18">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>

--- a/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
+++ b/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="773" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B65F00F5-2D97-4861-BC01-C7C53CB5B697}"/>
+  <xr:revisionPtr revIDLastSave="775" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73CE2689-A19C-4EFE-8940-9EB7387BD364}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -824,58 +824,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -883,6 +836,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -915,6 +870,51 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1254,15 +1254,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="29">
         <v>1</v>
       </c>
@@ -1340,17 +1340,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="61" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="63"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="27" t="s">
         <v>106</v>
       </c>
@@ -1412,116 +1412,116 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="51"/>
+      <c r="F3" s="34"/>
       <c r="G3" s="19" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <f t="shared" ref="H3:R3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <v>6</v>
+      </c>
+      <c r="I3" s="14">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I3" s="14">
-        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
+      <c r="J3" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K3" s="14">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="J3" s="14">
-        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
+      <c r="L3" s="14">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K3" s="14">
-        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
+      <c r="M3" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="N3" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O3" s="14">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="L3" s="14">
-        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+      <c r="P3" s="14">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="M3" s="14">
-        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
+      <c r="Q3" s="14">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="N3" s="14">
-        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+      <c r="R3" s="14">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="O3" s="14">
-        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
-        <v>2</v>
-      </c>
-      <c r="P3" s="14">
-        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
-        <v>2</v>
-      </c>
-      <c r="Q3" s="14">
-        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R3" s="14">
-        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
-        <v>2</v>
-      </c>
       <c r="S3" s="14">
-        <f t="shared" ref="H3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
+        <f t="shared" ref="S3:AF3" si="1">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
         <v>0</v>
       </c>
       <c r="T3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Y3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Z3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AA3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AB3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AD3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AF3" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="35" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
+        <f t="shared" ref="G4:G51" si="2">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
         <v>L</v>
       </c>
       <c r="H4" s="21" t="s">
@@ -1592,7 +1592,7 @@
       <c r="AF4" s="20"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H5" s="21" t="s">
@@ -1661,7 +1661,7 @@
       <c r="AF5" s="20"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1674,7 +1674,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H6" s="21" t="s">
@@ -1726,7 +1726,7 @@
       <c r="AF6" s="20"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1739,7 +1739,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H7" s="21" t="s">
@@ -1791,7 +1791,7 @@
       <c r="AF7" s="20"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1804,7 +1804,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H8" s="21" t="s">
@@ -1856,7 +1856,7 @@
       <c r="AF8" s="20"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1869,7 +1869,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H9" s="21" t="s">
@@ -1921,7 +1921,7 @@
       <c r="AF9" s="20"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="42" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1940,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H10" s="21" t="s">
@@ -1992,7 +1992,7 @@
       <c r="AF10" s="20"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H11" s="21" t="s">
@@ -2061,7 +2061,7 @@
       <c r="AF11" s="20"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2074,7 +2074,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H12" s="21" t="s">
@@ -2126,7 +2126,7 @@
       <c r="AF12" s="20"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H13" s="21" t="s">
@@ -2191,7 +2191,7 @@
       <c r="AF13" s="20"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2204,7 +2204,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H14" s="21" t="s">
@@ -2256,7 +2256,7 @@
       <c r="AF14" s="20"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="38"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2269,7 +2269,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H15" s="21" t="s">
@@ -2321,7 +2321,7 @@
       <c r="AF15" s="20"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="43" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2340,7 +2340,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="H16" s="21" t="s">
@@ -2392,7 +2392,7 @@
       <c r="AF16" s="20"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2402,11 +2402,15 @@
       <c r="D17" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="E17" s="9">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1</v>
+      </c>
       <c r="G17" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>-</v>
+        <f t="shared" si="2"/>
+        <v>V</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>104</v>
@@ -2457,7 +2461,7 @@
       <c r="AF17" s="20"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2470,7 +2474,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H18" s="21" t="s">
@@ -2522,7 +2526,7 @@
       <c r="AF18" s="20"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2535,7 +2539,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H19" s="21" t="s">
@@ -2587,7 +2591,7 @@
       <c r="AF19" s="20"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2600,7 +2604,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H20" s="21" t="s">
@@ -2652,7 +2656,7 @@
       <c r="AF20" s="20"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="38"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2665,7 +2669,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H21" s="21" t="s">
@@ -2717,7 +2721,7 @@
       <c r="AF21" s="20"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="40" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2736,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="H22" s="21" t="s">
@@ -2788,7 +2792,7 @@
       <c r="AF22" s="20"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2801,7 +2805,7 @@
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H23" s="21" t="s">
@@ -2853,7 +2857,7 @@
       <c r="AF23" s="20"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2866,7 +2870,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H24" s="21" t="s">
@@ -2918,7 +2922,7 @@
       <c r="AF24" s="20"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2931,7 +2935,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H25" s="21" t="s">
@@ -2983,7 +2987,7 @@
       <c r="AF25" s="20"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -2996,7 +3000,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H26" s="21" t="s">
@@ -3048,7 +3052,7 @@
       <c r="AF26" s="20"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="38"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3061,7 +3065,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H27" s="21" t="s">
@@ -3113,7 +3117,7 @@
       <c r="AF27" s="20"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="41" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3128,7 +3132,7 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H28" s="21" t="s">
@@ -3180,7 +3184,7 @@
       <c r="AF28" s="20"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3193,7 +3197,7 @@
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H29" s="21" t="s">
@@ -3245,7 +3249,7 @@
       <c r="AF29" s="20"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3258,7 +3262,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H30" s="21" t="s">
@@ -3310,7 +3314,7 @@
       <c r="AF30" s="20"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="A31" s="36"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3323,7 +3327,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H31" s="21" t="s">
@@ -3375,7 +3379,7 @@
       <c r="AF31" s="20"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="36"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3388,7 +3392,7 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H32" s="21" t="s">
@@ -3440,7 +3444,7 @@
       <c r="AF32" s="20"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="38"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3453,7 +3457,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H33" s="21" t="s">
@@ -3505,7 +3509,7 @@
       <c r="AF33" s="20"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="39" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3520,7 +3524,7 @@
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H34" s="21" t="s">
@@ -3572,7 +3576,7 @@
       <c r="AF34" s="20"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="36"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3585,7 +3589,7 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H35" s="21" t="s">
@@ -3637,7 +3641,7 @@
       <c r="AF35" s="20"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3650,7 +3654,7 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H36" s="21" t="s">
@@ -3702,7 +3706,7 @@
       <c r="AF36" s="20"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3715,7 +3719,7 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H37" s="21" t="s">
@@ -3767,7 +3771,7 @@
       <c r="AF37" s="20"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3780,7 +3784,7 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H38" s="21" t="s">
@@ -3832,7 +3836,7 @@
       <c r="AF38" s="20"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="38"/>
+      <c r="A39" s="37"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3845,7 +3849,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H39" s="21" t="s">
@@ -3897,7 +3901,7 @@
       <c r="AF39" s="20"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="38" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3912,7 +3916,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H40" s="21" t="s">
@@ -3964,7 +3968,7 @@
       <c r="AF40" s="20"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="36"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -3977,7 +3981,7 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H41" s="21" t="s">
@@ -4029,7 +4033,7 @@
       <c r="AF41" s="20"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="36"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4042,7 +4046,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H42" s="21" t="s">
@@ -4094,7 +4098,7 @@
       <c r="AF42" s="20"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="37"/>
+      <c r="A43" s="36"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4107,7 +4111,7 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H43" s="21" t="s">
@@ -4159,7 +4163,7 @@
       <c r="AF43" s="20"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
+      <c r="A44" s="36"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4172,7 +4176,7 @@
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H44" s="21" t="s">
@@ -4224,7 +4228,7 @@
       <c r="AF44" s="20"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="38"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4237,7 +4241,7 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H45" s="21" t="s">
@@ -4289,7 +4293,7 @@
       <c r="AF45" s="20"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="55" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4304,7 +4308,7 @@
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H46" s="21" t="s">
@@ -4356,7 +4360,7 @@
       <c r="AF46" s="20"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4369,7 +4373,7 @@
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H47" s="21" t="s">
@@ -4421,7 +4425,7 @@
       <c r="AF47" s="20"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4434,7 +4438,7 @@
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H48" s="21" t="s">
@@ -4486,7 +4490,7 @@
       <c r="AF48" s="20"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4499,7 +4503,7 @@
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H49" s="21" t="s">
@@ -4551,7 +4555,7 @@
       <c r="AF49" s="20"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="36"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4564,7 +4568,7 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H50" s="21" t="s">
@@ -4616,7 +4620,7 @@
       <c r="AF50" s="20"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="37"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4629,7 +4633,7 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H51" s="21" t="s">
@@ -4681,7 +4685,7 @@
       <c r="AF51" s="20"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="58" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4696,7 +4700,7 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15" t="str">
-        <f t="shared" ref="G52:G75" si="2">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
+        <f t="shared" ref="G52:G75" si="3">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
       <c r="H52" s="23" t="s">
@@ -4748,7 +4752,7 @@
       <c r="AF52" s="22"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="44"/>
+      <c r="A53" s="59"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4761,7 +4765,7 @@
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H53" s="23" t="s">
@@ -4813,7 +4817,7 @@
       <c r="AF53" s="22"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="44"/>
+      <c r="A54" s="59"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4826,7 +4830,7 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H54" s="23" t="s">
@@ -4878,7 +4882,7 @@
       <c r="AF54" s="22"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="44"/>
+      <c r="A55" s="59"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4891,7 +4895,7 @@
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H55" s="23" t="s">
@@ -4944,7 +4948,7 @@
       <c r="AK55" s="28"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="44"/>
+      <c r="A56" s="59"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -4957,7 +4961,7 @@
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H56" s="23" t="s">
@@ -5009,7 +5013,7 @@
       <c r="AF56" s="22"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="45"/>
+      <c r="A57" s="60"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5022,7 +5026,7 @@
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H57" s="23" t="s">
@@ -5074,7 +5078,7 @@
       <c r="AF57" s="22"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="46" t="s">
+      <c r="A58" s="61" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5089,7 +5093,7 @@
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
       <c r="G58" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H58" s="23" t="s">
@@ -5141,7 +5145,7 @@
       <c r="AF58" s="22"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="47"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5154,7 +5158,7 @@
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H59" s="23" t="s">
@@ -5206,7 +5210,7 @@
       <c r="AF59" s="22"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="47"/>
+      <c r="A60" s="62"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5219,7 +5223,7 @@
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H60" s="23" t="s">
@@ -5271,7 +5275,7 @@
       <c r="AF60" s="22"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="47"/>
+      <c r="A61" s="62"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5284,7 +5288,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H61" s="23" t="s">
@@ -5336,7 +5340,7 @@
       <c r="AF61" s="22"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="47"/>
+      <c r="A62" s="62"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5349,7 +5353,7 @@
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H62" s="23" t="s">
@@ -5401,7 +5405,7 @@
       <c r="AF62" s="22"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="48"/>
+      <c r="A63" s="63"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5414,7 +5418,7 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H63" s="23" t="s">
@@ -5466,7 +5470,7 @@
       <c r="AF63" s="22"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="49" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5481,7 +5485,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H64" s="23" t="s">
@@ -5533,7 +5537,7 @@
       <c r="AF64" s="22"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="31"/>
+      <c r="A65" s="50"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5546,7 +5550,7 @@
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H65" s="23" t="s">
@@ -5598,7 +5602,7 @@
       <c r="AF65" s="22"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="31"/>
+      <c r="A66" s="50"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5611,7 +5615,7 @@
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H66" s="23" t="s">
@@ -5663,7 +5667,7 @@
       <c r="AF66" s="22"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="31"/>
+      <c r="A67" s="50"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5676,7 +5680,7 @@
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H67" s="23" t="s">
@@ -5728,7 +5732,7 @@
       <c r="AF67" s="22"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="31"/>
+      <c r="A68" s="50"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5741,7 +5745,7 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H68" s="23" t="s">
@@ -5793,7 +5797,7 @@
       <c r="AF68" s="22"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="32"/>
+      <c r="A69" s="51"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5806,7 +5810,7 @@
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H69" s="23" t="s">
@@ -5858,7 +5862,7 @@
       <c r="AF69" s="22"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="33" t="s">
+      <c r="A70" s="52" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5873,7 +5877,7 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
       <c r="G70" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H70" s="23" t="s">
@@ -5925,7 +5929,7 @@
       <c r="AF70" s="22"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="34"/>
+      <c r="A71" s="53"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5938,7 +5942,7 @@
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
       <c r="G71" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H71" s="23" t="s">
@@ -5990,7 +5994,7 @@
       <c r="AF71" s="22"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="34"/>
+      <c r="A72" s="53"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6003,7 +6007,7 @@
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
       <c r="G72" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H72" s="23" t="s">
@@ -6055,7 +6059,7 @@
       <c r="AF72" s="22"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="34"/>
+      <c r="A73" s="53"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6068,7 +6072,7 @@
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H73" s="23" t="s">
@@ -6120,7 +6124,7 @@
       <c r="AF73" s="22"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="34"/>
+      <c r="A74" s="53"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6133,7 +6137,7 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H74" s="23" t="s">
@@ -6185,7 +6189,7 @@
       <c r="AF74" s="22"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="35"/>
+      <c r="A75" s="54"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6198,7 +6202,7 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="H75" s="23" t="s">
@@ -6253,14 +6257,14 @@
       <c r="A76" s="24"/>
       <c r="B76" s="24"/>
       <c r="C76" s="24"/>
-      <c r="D76" s="39" t="s">
+      <c r="D76" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="40"/>
-      <c r="F76" s="41"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="32"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H76" s="23">
         <v>179</v>
@@ -6314,111 +6318,111 @@
       <c r="A77" s="24"/>
       <c r="B77" s="24"/>
       <c r="C77" s="24"/>
-      <c r="D77" s="42" t="s">
+      <c r="D77" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="40"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="41"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="32"/>
       <c r="H77" s="25">
-        <f>SUM(H78:H81)</f>
+        <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="25">
-        <f>SUM(I78:I81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J77" s="25">
-        <f>SUM(J78:J81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K77" s="25">
-        <f>SUM(K78:K81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L77" s="25">
-        <f>SUM(L78:L81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M77" s="25">
-        <f>SUM(M78:M81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N77" s="25">
-        <f>SUM(N78:N81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O77" s="25">
-        <f>SUM(O78:O81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P77" s="25">
-        <f>SUM(P78:P81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q77" s="25">
-        <f>SUM(Q78:Q81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R77" s="25">
-        <f>SUM(R78:R81)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S77" s="25">
-        <f t="shared" ref="H77:AF77" si="3">SUM(S78:S81)</f>
-        <v>84</v>
+        <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
+        <v>83</v>
       </c>
       <c r="T77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="U77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="V77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="W77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="X77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="Y77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="Z77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="AA77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="AB77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="AC77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="AD77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="AE77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
       <c r="AF77" s="25">
-        <f t="shared" si="3"/>
-        <v>84</v>
+        <f t="shared" si="5"/>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6430,104 +6434,104 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="6">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="4"/>
-        <v>84</v>
+        <f t="shared" si="6"/>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6539,103 +6543,103 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="7">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -6648,103 +6652,103 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="8">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -6757,103 +6761,103 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="9">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -7725,6 +7729,13 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7736,13 +7747,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
+++ b/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="775" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73CE2689-A19C-4EFE-8940-9EB7387BD364}"/>
+  <xr:revisionPtr revIDLastSave="777" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BD54377-7E7B-4C47-B56F-4E31990894CF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -824,11 +824,58 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -836,8 +883,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -870,51 +915,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1254,15 +1254,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="29">
         <v>1</v>
       </c>
@@ -1340,17 +1340,17 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="46" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="63"/>
       <c r="H2" s="27" t="s">
         <v>106</v>
       </c>
@@ -1412,10 +1412,10 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="34"/>
+      <c r="F3" s="51"/>
       <c r="G3" s="19" t="s">
         <v>5</v>
       </c>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="14">
         <f t="shared" si="0"/>
@@ -1441,11 +1441,11 @@
       </c>
       <c r="M3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" s="14">
         <f t="shared" si="0"/>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="R3" s="14">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3" s="14">
         <f t="shared" ref="S3:AF3" si="1">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
@@ -1521,7 +1521,7 @@
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="52" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1592,7 +1592,7 @@
       <c r="AF4" s="20"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1661,7 +1661,7 @@
       <c r="AF5" s="20"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1726,7 +1726,7 @@
       <c r="AF6" s="20"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
+      <c r="A7" s="37"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1791,7 +1791,7 @@
       <c r="AF7" s="20"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="36"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1856,7 +1856,7 @@
       <c r="AF8" s="20"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1921,7 +1921,7 @@
       <c r="AF9" s="20"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="57" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1992,7 +1992,7 @@
       <c r="AF10" s="20"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2061,7 +2061,7 @@
       <c r="AF11" s="20"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2126,7 +2126,7 @@
       <c r="AF12" s="20"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2191,7 +2191,7 @@
       <c r="AF13" s="20"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="AF14" s="20"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2321,7 +2321,7 @@
       <c r="AF15" s="20"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="58" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2392,7 +2392,7 @@
       <c r="AF16" s="20"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2461,7 +2461,7 @@
       <c r="AF17" s="20"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2526,7 +2526,7 @@
       <c r="AF18" s="20"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2591,7 +2591,7 @@
       <c r="AF19" s="20"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2656,7 +2656,7 @@
       <c r="AF20" s="20"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2721,7 +2721,7 @@
       <c r="AF21" s="20"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="55" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2792,7 +2792,7 @@
       <c r="AF22" s="20"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2802,11 +2802,15 @@
       <c r="D23" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
+      <c r="E23" s="10">
+        <v>2</v>
+      </c>
+      <c r="F23" s="10">
+        <v>0</v>
+      </c>
       <c r="G23" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>-</v>
+        <v>L</v>
       </c>
       <c r="H23" s="21" t="s">
         <v>104</v>
@@ -2857,7 +2861,7 @@
       <c r="AF23" s="20"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2922,7 +2926,7 @@
       <c r="AF24" s="20"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="36"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2987,7 +2991,7 @@
       <c r="AF25" s="20"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3052,7 +3056,7 @@
       <c r="AF26" s="20"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
+      <c r="A27" s="38"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3117,7 +3121,7 @@
       <c r="AF27" s="20"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="56" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3184,7 +3188,7 @@
       <c r="AF28" s="20"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3249,7 +3253,7 @@
       <c r="AF29" s="20"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3314,7 +3318,7 @@
       <c r="AF30" s="20"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3379,7 +3383,7 @@
       <c r="AF31" s="20"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3444,7 +3448,7 @@
       <c r="AF32" s="20"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="A33" s="38"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3509,7 +3513,7 @@
       <c r="AF33" s="20"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="39" t="s">
+      <c r="A34" s="54" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3576,7 +3580,7 @@
       <c r="AF34" s="20"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="36"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3641,7 +3645,7 @@
       <c r="AF35" s="20"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3706,7 +3710,7 @@
       <c r="AF36" s="20"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="36"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3771,7 +3775,7 @@
       <c r="AF37" s="20"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="36"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3836,7 +3840,7 @@
       <c r="AF38" s="20"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
+      <c r="A39" s="38"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3901,7 +3905,7 @@
       <c r="AF39" s="20"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="38" t="s">
+      <c r="A40" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3968,7 +3972,7 @@
       <c r="AF40" s="20"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -4033,7 +4037,7 @@
       <c r="AF41" s="20"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="36"/>
+      <c r="A42" s="37"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4098,7 +4102,7 @@
       <c r="AF42" s="20"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="36"/>
+      <c r="A43" s="37"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4163,7 +4167,7 @@
       <c r="AF43" s="20"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="36"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4228,7 +4232,7 @@
       <c r="AF44" s="20"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
+      <c r="A45" s="38"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4293,7 +4297,7 @@
       <c r="AF45" s="20"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="55" t="s">
+      <c r="A46" s="36" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4360,7 +4364,7 @@
       <c r="AF46" s="20"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="36"/>
+      <c r="A47" s="37"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4425,7 +4429,7 @@
       <c r="AF47" s="20"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4490,7 +4494,7 @@
       <c r="AF48" s="20"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="36"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4555,7 +4559,7 @@
       <c r="AF49" s="20"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="36"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4620,7 +4624,7 @@
       <c r="AF50" s="20"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
+      <c r="A51" s="38"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4685,7 +4689,7 @@
       <c r="AF51" s="20"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="58" t="s">
+      <c r="A52" s="43" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4752,7 +4756,7 @@
       <c r="AF52" s="22"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="59"/>
+      <c r="A53" s="44"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4817,7 +4821,7 @@
       <c r="AF53" s="22"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="59"/>
+      <c r="A54" s="44"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4882,7 +4886,7 @@
       <c r="AF54" s="22"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="59"/>
+      <c r="A55" s="44"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4948,7 +4952,7 @@
       <c r="AK55" s="28"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="59"/>
+      <c r="A56" s="44"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -5013,7 +5017,7 @@
       <c r="AF56" s="22"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="60"/>
+      <c r="A57" s="45"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5078,7 +5082,7 @@
       <c r="AF57" s="22"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="61" t="s">
+      <c r="A58" s="46" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5145,7 +5149,7 @@
       <c r="AF58" s="22"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="62"/>
+      <c r="A59" s="47"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5210,7 +5214,7 @@
       <c r="AF59" s="22"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="62"/>
+      <c r="A60" s="47"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5275,7 +5279,7 @@
       <c r="AF60" s="22"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="62"/>
+      <c r="A61" s="47"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5340,7 +5344,7 @@
       <c r="AF61" s="22"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="62"/>
+      <c r="A62" s="47"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5405,7 +5409,7 @@
       <c r="AF62" s="22"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="63"/>
+      <c r="A63" s="48"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5470,7 +5474,7 @@
       <c r="AF63" s="22"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="49" t="s">
+      <c r="A64" s="30" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5537,7 +5541,7 @@
       <c r="AF64" s="22"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="50"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5602,7 +5606,7 @@
       <c r="AF65" s="22"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="50"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5667,7 +5671,7 @@
       <c r="AF66" s="22"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="50"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5732,7 +5736,7 @@
       <c r="AF67" s="22"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="50"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5797,7 +5801,7 @@
       <c r="AF68" s="22"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="51"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5862,7 +5866,7 @@
       <c r="AF69" s="22"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="52" t="s">
+      <c r="A70" s="33" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5929,7 +5933,7 @@
       <c r="AF70" s="22"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="53"/>
+      <c r="A71" s="34"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5994,7 +5998,7 @@
       <c r="AF71" s="22"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="53"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6059,7 +6063,7 @@
       <c r="AF72" s="22"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="53"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6124,7 +6128,7 @@
       <c r="AF73" s="22"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="53"/>
+      <c r="A74" s="34"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6189,7 +6193,7 @@
       <c r="AF74" s="22"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="54"/>
+      <c r="A75" s="35"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6257,14 +6261,14 @@
       <c r="A76" s="24"/>
       <c r="B76" s="24"/>
       <c r="C76" s="24"/>
-      <c r="D76" s="56" t="s">
+      <c r="D76" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="31"/>
-      <c r="F76" s="32"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="41"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H76" s="23">
         <v>179</v>
@@ -6318,12 +6322,12 @@
       <c r="A77" s="24"/>
       <c r="B77" s="24"/>
       <c r="C77" s="24"/>
-      <c r="D77" s="57" t="s">
+      <c r="D77" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="31"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="32"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="41"/>
       <c r="H77" s="25">
         <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
         <v>0</v>
@@ -6370,59 +6374,59 @@
       </c>
       <c r="S77" s="25">
         <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="W77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="X77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Y77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Z77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AA77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AB77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AC77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AD77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AE77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AF77" s="25">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -6479,59 +6483,59 @@
       </c>
       <c r="S78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="V78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="W78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="X78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Y78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Z78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AA78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AB78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AC78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AD78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AE78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AF78" s="3">
         <f t="shared" si="6"/>
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:32" ht="14.4" x14ac:dyDescent="0.3">
@@ -7729,13 +7733,6 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7747,6 +7744,13 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
+++ b/QUINIELA WORLD CUP MEXICO 2026 FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfemex-my.sharepoint.com/personal/david_limon_cfe_mx/Documents/RESPALDO DAVID LIMON/iSE/Python y Power BI/Python/quiniela_mundial_mexico_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="777" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BD54377-7E7B-4C47-B56F-4E31990894CF}"/>
+  <xr:revisionPtr revIDLastSave="778" documentId="8_{5BF2CA42-94C7-4CF1-99FD-A98BD95C2878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A571C74B-7263-4AFD-99DB-F1DBCEC96E9E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -824,58 +824,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -883,6 +836,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -915,6 +870,51 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1254,15 +1254,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="32"/>
       <c r="H1" s="29">
         <v>1</v>
       </c>
@@ -1340,49 +1340,49 @@
       </c>
     </row>
     <row r="2" spans="1:32" ht="140.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="61" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="63"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="27" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="J2" s="26" t="s">
-        <v>114</v>
-      </c>
       <c r="K2" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="M2" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="N2" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="M2" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>108</v>
-      </c>
       <c r="O2" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="P2" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="Q2" s="26" t="s">
+      <c r="R2" s="26" t="s">
         <v>113</v>
-      </c>
-      <c r="R2" s="26" t="s">
-        <v>115</v>
       </c>
       <c r="S2" s="26"/>
       <c r="T2" s="26"/>
@@ -1412,116 +1412,116 @@
       <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="51"/>
+      <c r="F3" s="34"/>
       <c r="G3" s="19" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="14">
-        <f t="shared" ref="H3:R3" si="0">SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
+        <f>SUM(IF(H4=$G$4,1,0)+IF(H5=$G$5,1,0)+IF(H6=$G$6,1,0)+IF(H7=$G$7,1,0)+IF(H8=$G$8,1,0)+IF(H9=$G$9,1,0)+IF(H10=$G$10,1,0)+IF(H11=$G$11,1,0)+IF(H12=$G$12,1,0)+IF(H13=$G$13,1,0)+IF(H14=$G$14,1,0)+IF(H15=$G$15,1,0)+IF(H16=$G$16,1,0)+IF(H17=$G$17,1,0)+IF(H18=$G$18,1,0)+IF(H19=$G$19,1,0)+IF(H20=$G$20,1,0)+IF(H21=$G$21,1,0)+IF(H22=$G$22,1,0)+IF(H23=$G$23,1,0)+IF(H24=$G$24,1,0)+IF(H25=$G$25,1,0)+IF(H26=$G$26,1,0)+IF(H27=$G$27,1,0)+IF(H28=$G$28,1,0)+IF(H29=$G$29,1,0)+IF(H30=$G$30,1,0)+IF(H31=$G$31,1,0)+IF(H32=$G$32,1,0)+IF(H33=$G$33,1,0)+IF(H34=$G$34,1,0)+IF(H35=$G$35,1,0)+IF(H36=$G$36,1,0)+IF(H37=$G$37,1,0)+IF(H38=$G$38,1,0)+IF(H39=$G$39,1,0))</f>
         <v>6</v>
       </c>
       <c r="I3" s="14">
+        <f>SUM(IF(I4=$G$4,1,0)+IF(I5=$G$5,1,0)+IF(I6=$G$6,1,0)+IF(I7=$G$7,1,0)+IF(I8=$G$8,1,0)+IF(I9=$G$9,1,0)+IF(I10=$G$10,1,0)+IF(I11=$G$11,1,0)+IF(I12=$G$12,1,0)+IF(I13=$G$13,1,0)+IF(I14=$G$14,1,0)+IF(I15=$G$15,1,0)+IF(I16=$G$16,1,0)+IF(I17=$G$17,1,0)+IF(I18=$G$18,1,0)+IF(I19=$G$19,1,0)+IF(I20=$G$20,1,0)+IF(I21=$G$21,1,0)+IF(I22=$G$22,1,0)+IF(I23=$G$23,1,0)+IF(I24=$G$24,1,0)+IF(I25=$G$25,1,0)+IF(I26=$G$26,1,0)+IF(I27=$G$27,1,0)+IF(I28=$G$28,1,0)+IF(I29=$G$29,1,0)+IF(I30=$G$30,1,0)+IF(I31=$G$31,1,0)+IF(I32=$G$32,1,0)+IF(I33=$G$33,1,0)+IF(I34=$G$34,1,0)+IF(I35=$G$35,1,0)+IF(I36=$G$36,1,0)+IF(I37=$G$37,1,0)+IF(I38=$G$38,1,0)+IF(I39=$G$39,1,0))</f>
+        <v>6</v>
+      </c>
+      <c r="J3" s="14">
+        <f>SUM(IF(J4=$G$4,1,0)+IF(J5=$G$5,1,0)+IF(J6=$G$6,1,0)+IF(J7=$G$7,1,0)+IF(J8=$G$8,1,0)+IF(J9=$G$9,1,0)+IF(J10=$G$10,1,0)+IF(J11=$G$11,1,0)+IF(J12=$G$12,1,0)+IF(J13=$G$13,1,0)+IF(J14=$G$14,1,0)+IF(J15=$G$15,1,0)+IF(J16=$G$16,1,0)+IF(J17=$G$17,1,0)+IF(J18=$G$18,1,0)+IF(J19=$G$19,1,0)+IF(J20=$G$20,1,0)+IF(J21=$G$21,1,0)+IF(J22=$G$22,1,0)+IF(J23=$G$23,1,0)+IF(J24=$G$24,1,0)+IF(J25=$G$25,1,0)+IF(J26=$G$26,1,0)+IF(J27=$G$27,1,0)+IF(J28=$G$28,1,0)+IF(J29=$G$29,1,0)+IF(J30=$G$30,1,0)+IF(J31=$G$31,1,0)+IF(J32=$G$32,1,0)+IF(J33=$G$33,1,0)+IF(J34=$G$34,1,0)+IF(J35=$G$35,1,0)+IF(J36=$G$36,1,0)+IF(J37=$G$37,1,0)+IF(J38=$G$38,1,0)+IF(J39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="K3" s="14">
+        <f>SUM(IF(K4=$G$4,1,0)+IF(K5=$G$5,1,0)+IF(K6=$G$6,1,0)+IF(K7=$G$7,1,0)+IF(K8=$G$8,1,0)+IF(K9=$G$9,1,0)+IF(K10=$G$10,1,0)+IF(K11=$G$11,1,0)+IF(K12=$G$12,1,0)+IF(K13=$G$13,1,0)+IF(K14=$G$14,1,0)+IF(K15=$G$15,1,0)+IF(K16=$G$16,1,0)+IF(K17=$G$17,1,0)+IF(K18=$G$18,1,0)+IF(K19=$G$19,1,0)+IF(K20=$G$20,1,0)+IF(K21=$G$21,1,0)+IF(K22=$G$22,1,0)+IF(K23=$G$23,1,0)+IF(K24=$G$24,1,0)+IF(K25=$G$25,1,0)+IF(K26=$G$26,1,0)+IF(K27=$G$27,1,0)+IF(K28=$G$28,1,0)+IF(K29=$G$29,1,0)+IF(K30=$G$30,1,0)+IF(K31=$G$31,1,0)+IF(K32=$G$32,1,0)+IF(K33=$G$33,1,0)+IF(K34=$G$34,1,0)+IF(K35=$G$35,1,0)+IF(K36=$G$36,1,0)+IF(K37=$G$37,1,0)+IF(K38=$G$38,1,0)+IF(K39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="L3" s="14">
+        <f>SUM(IF(L4=$G$4,1,0)+IF(L5=$G$5,1,0)+IF(L6=$G$6,1,0)+IF(L7=$G$7,1,0)+IF(L8=$G$8,1,0)+IF(L9=$G$9,1,0)+IF(L10=$G$10,1,0)+IF(L11=$G$11,1,0)+IF(L12=$G$12,1,0)+IF(L13=$G$13,1,0)+IF(L14=$G$14,1,0)+IF(L15=$G$15,1,0)+IF(L16=$G$16,1,0)+IF(L17=$G$17,1,0)+IF(L18=$G$18,1,0)+IF(L19=$G$19,1,0)+IF(L20=$G$20,1,0)+IF(L21=$G$21,1,0)+IF(L22=$G$22,1,0)+IF(L23=$G$23,1,0)+IF(L24=$G$24,1,0)+IF(L25=$G$25,1,0)+IF(L26=$G$26,1,0)+IF(L27=$G$27,1,0)+IF(L28=$G$28,1,0)+IF(L29=$G$29,1,0)+IF(L30=$G$30,1,0)+IF(L31=$G$31,1,0)+IF(L32=$G$32,1,0)+IF(L33=$G$33,1,0)+IF(L34=$G$34,1,0)+IF(L35=$G$35,1,0)+IF(L36=$G$36,1,0)+IF(L37=$G$37,1,0)+IF(L38=$G$38,1,0)+IF(L39=$G$39,1,0))</f>
+        <v>5</v>
+      </c>
+      <c r="M3" s="14">
+        <f>SUM(IF(M4=$G$4,1,0)+IF(M5=$G$5,1,0)+IF(M6=$G$6,1,0)+IF(M7=$G$7,1,0)+IF(M8=$G$8,1,0)+IF(M9=$G$9,1,0)+IF(M10=$G$10,1,0)+IF(M11=$G$11,1,0)+IF(M12=$G$12,1,0)+IF(M13=$G$13,1,0)+IF(M14=$G$14,1,0)+IF(M15=$G$15,1,0)+IF(M16=$G$16,1,0)+IF(M17=$G$17,1,0)+IF(M18=$G$18,1,0)+IF(M19=$G$19,1,0)+IF(M20=$G$20,1,0)+IF(M21=$G$21,1,0)+IF(M22=$G$22,1,0)+IF(M23=$G$23,1,0)+IF(M24=$G$24,1,0)+IF(M25=$G$25,1,0)+IF(M26=$G$26,1,0)+IF(M27=$G$27,1,0)+IF(M28=$G$28,1,0)+IF(M29=$G$29,1,0)+IF(M30=$G$30,1,0)+IF(M31=$G$31,1,0)+IF(M32=$G$32,1,0)+IF(M33=$G$33,1,0)+IF(M34=$G$34,1,0)+IF(M35=$G$35,1,0)+IF(M36=$G$36,1,0)+IF(M37=$G$37,1,0)+IF(M38=$G$38,1,0)+IF(M39=$G$39,1,0))</f>
+        <v>4</v>
+      </c>
+      <c r="N3" s="14">
+        <f>SUM(IF(N4=$G$4,1,0)+IF(N5=$G$5,1,0)+IF(N6=$G$6,1,0)+IF(N7=$G$7,1,0)+IF(N8=$G$8,1,0)+IF(N9=$G$9,1,0)+IF(N10=$G$10,1,0)+IF(N11=$G$11,1,0)+IF(N12=$G$12,1,0)+IF(N13=$G$13,1,0)+IF(N14=$G$14,1,0)+IF(N15=$G$15,1,0)+IF(N16=$G$16,1,0)+IF(N17=$G$17,1,0)+IF(N18=$G$18,1,0)+IF(N19=$G$19,1,0)+IF(N20=$G$20,1,0)+IF(N21=$G$21,1,0)+IF(N22=$G$22,1,0)+IF(N23=$G$23,1,0)+IF(N24=$G$24,1,0)+IF(N25=$G$25,1,0)+IF(N26=$G$26,1,0)+IF(N27=$G$27,1,0)+IF(N28=$G$28,1,0)+IF(N29=$G$29,1,0)+IF(N30=$G$30,1,0)+IF(N31=$G$31,1,0)+IF(N32=$G$32,1,0)+IF(N33=$G$33,1,0)+IF(N34=$G$34,1,0)+IF(N35=$G$35,1,0)+IF(N36=$G$36,1,0)+IF(N37=$G$37,1,0)+IF(N38=$G$38,1,0)+IF(N39=$G$39,1,0))</f>
+        <v>4</v>
+      </c>
+      <c r="O3" s="14">
+        <f>SUM(IF(O4=$G$4,1,0)+IF(O5=$G$5,1,0)+IF(O6=$G$6,1,0)+IF(O7=$G$7,1,0)+IF(O8=$G$8,1,0)+IF(O9=$G$9,1,0)+IF(O10=$G$10,1,0)+IF(O11=$G$11,1,0)+IF(O12=$G$12,1,0)+IF(O13=$G$13,1,0)+IF(O14=$G$14,1,0)+IF(O15=$G$15,1,0)+IF(O16=$G$16,1,0)+IF(O17=$G$17,1,0)+IF(O18=$G$18,1,0)+IF(O19=$G$19,1,0)+IF(O20=$G$20,1,0)+IF(O21=$G$21,1,0)+IF(O22=$G$22,1,0)+IF(O23=$G$23,1,0)+IF(O24=$G$24,1,0)+IF(O25=$G$25,1,0)+IF(O26=$G$26,1,0)+IF(O27=$G$27,1,0)+IF(O28=$G$28,1,0)+IF(O29=$G$29,1,0)+IF(O30=$G$30,1,0)+IF(O31=$G$31,1,0)+IF(O32=$G$32,1,0)+IF(O33=$G$33,1,0)+IF(O34=$G$34,1,0)+IF(O35=$G$35,1,0)+IF(O36=$G$36,1,0)+IF(O37=$G$37,1,0)+IF(O38=$G$38,1,0)+IF(O39=$G$39,1,0))</f>
+        <v>4</v>
+      </c>
+      <c r="P3" s="14">
+        <f>SUM(IF(P4=$G$4,1,0)+IF(P5=$G$5,1,0)+IF(P6=$G$6,1,0)+IF(P7=$G$7,1,0)+IF(P8=$G$8,1,0)+IF(P9=$G$9,1,0)+IF(P10=$G$10,1,0)+IF(P11=$G$11,1,0)+IF(P12=$G$12,1,0)+IF(P13=$G$13,1,0)+IF(P14=$G$14,1,0)+IF(P15=$G$15,1,0)+IF(P16=$G$16,1,0)+IF(P17=$G$17,1,0)+IF(P18=$G$18,1,0)+IF(P19=$G$19,1,0)+IF(P20=$G$20,1,0)+IF(P21=$G$21,1,0)+IF(P22=$G$22,1,0)+IF(P23=$G$23,1,0)+IF(P24=$G$24,1,0)+IF(P25=$G$25,1,0)+IF(P26=$G$26,1,0)+IF(P27=$G$27,1,0)+IF(P28=$G$28,1,0)+IF(P29=$G$29,1,0)+IF(P30=$G$30,1,0)+IF(P31=$G$31,1,0)+IF(P32=$G$32,1,0)+IF(P33=$G$33,1,0)+IF(P34=$G$34,1,0)+IF(P35=$G$35,1,0)+IF(P36=$G$36,1,0)+IF(P37=$G$37,1,0)+IF(P38=$G$38,1,0)+IF(P39=$G$39,1,0))</f>
+        <v>3</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>SUM(IF(Q4=$G$4,1,0)+IF(Q5=$G$5,1,0)+IF(Q6=$G$6,1,0)+IF(Q7=$G$7,1,0)+IF(Q8=$G$8,1,0)+IF(Q9=$G$9,1,0)+IF(Q10=$G$10,1,0)+IF(Q11=$G$11,1,0)+IF(Q12=$G$12,1,0)+IF(Q13=$G$13,1,0)+IF(Q14=$G$14,1,0)+IF(Q15=$G$15,1,0)+IF(Q16=$G$16,1,0)+IF(Q17=$G$17,1,0)+IF(Q18=$G$18,1,0)+IF(Q19=$G$19,1,0)+IF(Q20=$G$20,1,0)+IF(Q21=$G$21,1,0)+IF(Q22=$G$22,1,0)+IF(Q23=$G$23,1,0)+IF(Q24=$G$24,1,0)+IF(Q25=$G$25,1,0)+IF(Q26=$G$26,1,0)+IF(Q27=$G$27,1,0)+IF(Q28=$G$28,1,0)+IF(Q29=$G$29,1,0)+IF(Q30=$G$30,1,0)+IF(Q31=$G$31,1,0)+IF(Q32=$G$32,1,0)+IF(Q33=$G$33,1,0)+IF(Q34=$G$34,1,0)+IF(Q35=$G$35,1,0)+IF(Q36=$G$36,1,0)+IF(Q37=$G$37,1,0)+IF(Q38=$G$38,1,0)+IF(Q39=$G$39,1,0))</f>
+        <v>3</v>
+      </c>
+      <c r="R3" s="14">
+        <f>SUM(IF(R4=$G$4,1,0)+IF(R5=$G$5,1,0)+IF(R6=$G$6,1,0)+IF(R7=$G$7,1,0)+IF(R8=$G$8,1,0)+IF(R9=$G$9,1,0)+IF(R10=$G$10,1,0)+IF(R11=$G$11,1,0)+IF(R12=$G$12,1,0)+IF(R13=$G$13,1,0)+IF(R14=$G$14,1,0)+IF(R15=$G$15,1,0)+IF(R16=$G$16,1,0)+IF(R17=$G$17,1,0)+IF(R18=$G$18,1,0)+IF(R19=$G$19,1,0)+IF(R20=$G$20,1,0)+IF(R21=$G$21,1,0)+IF(R22=$G$22,1,0)+IF(R23=$G$23,1,0)+IF(R24=$G$24,1,0)+IF(R25=$G$25,1,0)+IF(R26=$G$26,1,0)+IF(R27=$G$27,1,0)+IF(R28=$G$28,1,0)+IF(R29=$G$29,1,0)+IF(R30=$G$30,1,0)+IF(R31=$G$31,1,0)+IF(R32=$G$32,1,0)+IF(R33=$G$33,1,0)+IF(R34=$G$34,1,0)+IF(R35=$G$35,1,0)+IF(R36=$G$36,1,0)+IF(R37=$G$37,1,0)+IF(R38=$G$38,1,0)+IF(R39=$G$39,1,0))</f>
+        <v>3</v>
+      </c>
+      <c r="S3" s="14">
+        <f t="shared" ref="S3:AF3" si="0">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="J3" s="14">
+        <v>0</v>
+      </c>
+      <c r="U3" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="K3" s="14">
+        <v>0</v>
+      </c>
+      <c r="V3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="L3" s="14">
+        <v>0</v>
+      </c>
+      <c r="W3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="M3" s="14">
+        <v>0</v>
+      </c>
+      <c r="X3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="14">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="P3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="14">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="Q3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="14">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="R3" s="14">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="S3" s="14">
-        <f t="shared" ref="S3:AF3" si="1">SUM(IF(S4=$G$4,1,0)+IF(S5=$G$5,1,0)+IF(S6=$G$6,1,0)+IF(S7=$G$7,1,0)+IF(S8=$G$8,1,0)+IF(S9=$G$9,1,0)+IF(S10=$G$10,1,0)+IF(S11=$G$11,1,0)+IF(S12=$G$12,1,0)+IF(S13=$G$13,1,0)+IF(S14=$G$14,1,0)+IF(S15=$G$15,1,0)+IF(S16=$G$16,1,0)+IF(S17=$G$17,1,0)+IF(S18=$G$18,1,0)+IF(S19=$G$19,1,0)+IF(S20=$G$20,1,0)+IF(S21=$G$21,1,0)+IF(S22=$G$22,1,0)+IF(S23=$G$23,1,0)+IF(S24=$G$24,1,0)+IF(S25=$G$25,1,0)+IF(S26=$G$26,1,0)+IF(S27=$G$27,1,0)+IF(S28=$G$28,1,0)+IF(S29=$G$29,1,0)+IF(S30=$G$30,1,0)+IF(S31=$G$31,1,0)+IF(S32=$G$32,1,0)+IF(S33=$G$33,1,0)+IF(S34=$G$34,1,0)+IF(S35=$G$35,1,0)+IF(S36=$G$36,1,0)+IF(S37=$G$37,1,0)+IF(S38=$G$38,1,0)+IF(S39=$G$39,1,0))</f>
         <v>0</v>
       </c>
-      <c r="T3" s="14">
-        <f t="shared" si="1"/>
+      <c r="AD3" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U3" s="14">
-        <f t="shared" si="1"/>
+      <c r="AE3" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V3" s="14">
-        <f t="shared" si="1"/>
+      <c r="AF3" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AB3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AF3" s="14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="35" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="7">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="7" t="str">
-        <f t="shared" ref="G4:G51" si="2">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
+        <f t="shared" ref="G4:G51" si="1">IF(E4="","-",IF(E4&gt;F4,"L",IF(E4=F4,"E",IF(E4&lt;F4,"V"))))</f>
         <v>L</v>
       </c>
       <c r="H4" s="21" t="s">
@@ -1555,22 +1555,22 @@
       <c r="K4" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="20" t="s">
+      <c r="L4" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M4" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="21" t="s">
+      <c r="N4" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O4" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="20" t="s">
+      <c r="P4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R4" s="20" t="s">
@@ -1592,7 +1592,7 @@
       <c r="AF4" s="20"/>
     </row>
     <row r="5" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H5" s="21" t="s">
@@ -1624,26 +1624,26 @@
       <c r="K5" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="20" t="s">
+      <c r="L5" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M5" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="21" t="s">
+      <c r="N5" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="P5" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="21" t="s">
         <v>10</v>
       </c>
       <c r="R5" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S5" s="20"/>
       <c r="T5" s="20"/>
@@ -1661,7 +1661,7 @@
       <c r="AF5" s="20"/>
     </row>
     <row r="6" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -1674,37 +1674,37 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" s="20" t="s">
-        <v>46</v>
+        <v>110</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="M6" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="N6" s="21" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O6" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P6" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q6" s="20" t="s">
+      <c r="P6" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R6" s="20" t="s">
@@ -1726,7 +1726,7 @@
       <c r="AF6" s="20"/>
     </row>
     <row r="7" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -1739,38 +1739,38 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K7" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="20" t="s">
-        <v>46</v>
+      <c r="L7" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M7" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="21" t="s">
-        <v>10</v>
+      <c r="N7" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O7" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P7" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q7" s="20" t="s">
-        <v>46</v>
+      <c r="P7" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="R7" s="20" t="s">
         <v>46</v>
@@ -1791,7 +1791,7 @@
       <c r="AF7" s="20"/>
     </row>
     <row r="8" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -1804,37 +1804,37 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>104</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="N8" s="21" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="O8" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="P8" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q8" s="20" t="s">
+      <c r="P8" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R8" s="20" t="s">
@@ -1856,7 +1856,7 @@
       <c r="AF8" s="20"/>
     </row>
     <row r="9" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -1869,41 +1869,41 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H9" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K9" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L9" s="20" t="s">
+      <c r="L9" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M9" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N9" s="21" t="s">
+      <c r="N9" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q9" s="20" t="s">
+      <c r="P9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R9" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S9" s="20"/>
       <c r="T9" s="20"/>
@@ -1921,7 +1921,7 @@
       <c r="AF9" s="20"/>
     </row>
     <row r="10" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="42" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="7">
@@ -1940,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H10" s="21" t="s">
@@ -1953,24 +1953,24 @@
         <v>10</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L10" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="P10" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q10" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P10" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R10" s="20" t="s">
@@ -1992,7 +1992,7 @@
       <c r="AF10" s="20"/>
     </row>
     <row r="11" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -2009,37 +2009,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="L11" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M11" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="N11" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O11" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="P11" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="20" t="s">
+      <c r="P11" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R11" s="20" t="s">
@@ -2061,7 +2061,7 @@
       <c r="AF11" s="20"/>
     </row>
     <row r="12" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -2074,7 +2074,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H12" s="21" t="s">
@@ -2089,23 +2089,23 @@
       <c r="K12" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="20" t="s">
-        <v>46</v>
+      <c r="L12" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M12" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N12" s="21" t="s">
-        <v>10</v>
+      <c r="N12" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="P12" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="20" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="P12" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="R12" s="20" t="s">
         <v>46</v>
@@ -2126,7 +2126,7 @@
       <c r="AF12" s="20"/>
     </row>
     <row r="13" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H13" s="21" t="s">
@@ -2154,22 +2154,22 @@
       <c r="K13" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="20" t="s">
-        <v>46</v>
+      <c r="L13" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M13" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="21" t="s">
-        <v>10</v>
+      <c r="N13" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O13" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P13" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="20" t="s">
+      <c r="P13" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R13" s="20" t="s">
@@ -2191,7 +2191,7 @@
       <c r="AF13" s="20"/>
     </row>
     <row r="14" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -2204,38 +2204,38 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K14" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L14" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="M14" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N14" s="21" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="P14" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q14" s="20" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="P14" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q14" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="R14" s="20" t="s">
         <v>10</v>
@@ -2256,7 +2256,7 @@
       <c r="AF14" s="20"/>
     </row>
     <row r="15" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="38"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -2269,41 +2269,41 @@
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="M15" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="N15" s="21" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="N15" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="P15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q15" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R15" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S15" s="20"/>
       <c r="T15" s="20"/>
@@ -2321,7 +2321,7 @@
       <c r="AF15" s="20"/>
     </row>
     <row r="16" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="43" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="7">
@@ -2340,38 +2340,38 @@
         <v>1</v>
       </c>
       <c r="G16" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>E</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K16" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="20" t="s">
+      <c r="L16" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M16" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N16" s="21" t="s">
+      <c r="N16" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O16" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q16" s="20" t="s">
-        <v>46</v>
+      <c r="P16" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q16" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="R16" s="20" t="s">
         <v>46</v>
@@ -2392,7 +2392,7 @@
       <c r="AF16" s="20"/>
     </row>
     <row r="17" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
       <c r="H17" s="21" t="s">
@@ -2424,22 +2424,22 @@
       <c r="K17" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="20" t="s">
+      <c r="L17" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M17" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N17" s="21" t="s">
+      <c r="N17" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O17" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="P17" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q17" s="20" t="s">
+      <c r="P17" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q17" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R17" s="20" t="s">
@@ -2461,7 +2461,7 @@
       <c r="AF17" s="20"/>
     </row>
     <row r="18" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -2474,7 +2474,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H18" s="21" t="s">
@@ -2489,26 +2489,26 @@
       <c r="K18" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L18" s="20" t="s">
-        <v>104</v>
+      <c r="L18" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M18" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N18" s="21" t="s">
-        <v>10</v>
+      <c r="N18" s="20" t="s">
+        <v>104</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="P18" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q18" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P18" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q18" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R18" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="S18" s="20"/>
       <c r="T18" s="20"/>
@@ -2526,7 +2526,7 @@
       <c r="AF18" s="20"/>
     </row>
     <row r="19" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -2539,7 +2539,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H19" s="21" t="s">
@@ -2554,22 +2554,22 @@
       <c r="K19" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="20" t="s">
+      <c r="L19" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M19" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N19" s="21" t="s">
+      <c r="N19" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O19" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P19" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q19" s="20" t="s">
+      <c r="P19" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R19" s="20" t="s">
@@ -2591,7 +2591,7 @@
       <c r="AF19" s="20"/>
     </row>
     <row r="20" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -2604,7 +2604,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H20" s="21" t="s">
@@ -2617,24 +2617,24 @@
         <v>104</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L20" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M20" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N20" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N20" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O20" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="P20" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q20" s="20" t="s">
+      <c r="P20" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q20" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R20" s="20" t="s">
@@ -2656,7 +2656,7 @@
       <c r="AF20" s="20"/>
     </row>
     <row r="21" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="38"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -2669,7 +2669,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H21" s="21" t="s">
@@ -2684,26 +2684,26 @@
       <c r="K21" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="20" t="s">
+      <c r="L21" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M21" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N21" s="21" t="s">
+      <c r="N21" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q21" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R21" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S21" s="20"/>
       <c r="T21" s="20"/>
@@ -2721,7 +2721,7 @@
       <c r="AF21" s="20"/>
     </row>
     <row r="22" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="40" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="7">
@@ -2740,37 +2740,37 @@
         <v>1</v>
       </c>
       <c r="G22" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H22" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L22" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M22" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N22" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N22" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="P22" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q22" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P22" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R22" s="20" t="s">
@@ -2792,7 +2792,7 @@
       <c r="AF22" s="20"/>
     </row>
     <row r="23" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="7">
         <v>20</v>
       </c>
@@ -2809,41 +2809,41 @@
         <v>0</v>
       </c>
       <c r="G23" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
       <c r="H23" s="21" t="s">
         <v>104</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L23" s="20" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="M23" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N23" s="21" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="N23" s="20" t="s">
+        <v>104</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="P23" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q23" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="P23" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q23" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="R23" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S23" s="20"/>
       <c r="T23" s="20"/>
@@ -2861,7 +2861,7 @@
       <c r="AF23" s="20"/>
     </row>
     <row r="24" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="7">
         <v>21</v>
       </c>
@@ -2874,38 +2874,38 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H24" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I24" s="20" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K24" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L24" s="20" t="s">
-        <v>46</v>
+      <c r="L24" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M24" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N24" s="21" t="s">
-        <v>10</v>
+      <c r="N24" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O24" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P24" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q24" s="20" t="s">
-        <v>46</v>
+      <c r="P24" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q24" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="R24" s="20" t="s">
         <v>46</v>
@@ -2926,7 +2926,7 @@
       <c r="AF24" s="20"/>
     </row>
     <row r="25" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -2939,38 +2939,38 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H25" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I25" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K25" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L25" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="M25" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N25" s="21" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="N25" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="O25" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="P25" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q25" s="20" t="s">
-        <v>10</v>
+      <c r="P25" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="R25" s="20" t="s">
         <v>10</v>
@@ -2991,7 +2991,7 @@
       <c r="AF25" s="20"/>
     </row>
     <row r="26" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -3004,7 +3004,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H26" s="21" t="s">
@@ -3019,26 +3019,26 @@
       <c r="K26" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L26" s="20" t="s">
-        <v>10</v>
+      <c r="L26" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="M26" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N26" s="21" t="s">
-        <v>104</v>
+      <c r="N26" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P26" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q26" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P26" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="21" t="s">
         <v>10</v>
       </c>
       <c r="R26" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="S26" s="20"/>
       <c r="T26" s="20"/>
@@ -3056,7 +3056,7 @@
       <c r="AF26" s="20"/>
     </row>
     <row r="27" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="38"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -3069,41 +3069,41 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I27" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L27" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="M27" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="N27" s="21" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="N27" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P27" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q27" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="P27" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q27" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="R27" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S27" s="20"/>
       <c r="T27" s="20"/>
@@ -3121,7 +3121,7 @@
       <c r="AF27" s="20"/>
     </row>
     <row r="28" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="41" t="s">
         <v>10</v>
       </c>
       <c r="B28" s="7">
@@ -3136,7 +3136,7 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H28" s="21" t="s">
@@ -3151,22 +3151,22 @@
       <c r="K28" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="20" t="s">
+      <c r="L28" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M28" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N28" s="21" t="s">
+      <c r="N28" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O28" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P28" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q28" s="20" t="s">
+      <c r="P28" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R28" s="20" t="s">
@@ -3188,7 +3188,7 @@
       <c r="AF28" s="20"/>
     </row>
     <row r="29" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -3201,38 +3201,38 @@
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H29" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I29" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K29" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L29" s="20" t="s">
-        <v>104</v>
+      <c r="L29" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M29" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N29" s="21" t="s">
-        <v>10</v>
+      <c r="N29" s="20" t="s">
+        <v>104</v>
       </c>
       <c r="O29" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q29" s="20" t="s">
-        <v>10</v>
+      <c r="P29" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="R29" s="20" t="s">
         <v>10</v>
@@ -3253,7 +3253,7 @@
       <c r="AF29" s="20"/>
     </row>
     <row r="30" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -3266,7 +3266,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H30" s="21" t="s">
@@ -3281,22 +3281,22 @@
       <c r="K30" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="20" t="s">
+      <c r="L30" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M30" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N30" s="21" t="s">
+      <c r="N30" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O30" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P30" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q30" s="20" t="s">
+      <c r="P30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R30" s="20" t="s">
@@ -3318,7 +3318,7 @@
       <c r="AF30" s="20"/>
     </row>
     <row r="31" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="A31" s="36"/>
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -3331,7 +3331,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H31" s="21" t="s">
@@ -3346,26 +3346,26 @@
       <c r="K31" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L31" s="20" t="s">
+      <c r="L31" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M31" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N31" s="21" t="s">
+      <c r="N31" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O31" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P31" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q31" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P31" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q31" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R31" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S31" s="20"/>
       <c r="T31" s="20"/>
@@ -3383,7 +3383,7 @@
       <c r="AF31" s="20"/>
     </row>
     <row r="32" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="A32" s="36"/>
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -3396,7 +3396,7 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H32" s="21" t="s">
@@ -3409,28 +3409,28 @@
         <v>104</v>
       </c>
       <c r="K32" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L32" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L32" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M32" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N32" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O32" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="P32" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q32" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="P32" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q32" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="R32" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S32" s="20"/>
       <c r="T32" s="20"/>
@@ -3448,7 +3448,7 @@
       <c r="AF32" s="20"/>
     </row>
     <row r="33" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="38"/>
+      <c r="A33" s="37"/>
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -3461,7 +3461,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H33" s="21" t="s">
@@ -3474,25 +3474,25 @@
         <v>104</v>
       </c>
       <c r="K33" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L33" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="M33" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="N33" s="21" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="N33" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="O33" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="P33" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q33" s="20" t="s">
-        <v>104</v>
+      <c r="P33" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q33" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="R33" s="20" t="s">
         <v>104</v>
@@ -3513,7 +3513,7 @@
       <c r="AF33" s="20"/>
     </row>
     <row r="34" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="39" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="7">
@@ -3528,41 +3528,41 @@
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H34" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K34" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L34" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="L34" s="21" t="s">
         <v>10</v>
       </c>
       <c r="M34" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N34" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N34" s="20" t="s">
         <v>10</v>
       </c>
       <c r="O34" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="P34" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q34" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P34" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R34" s="20" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="S34" s="20"/>
       <c r="T34" s="20"/>
@@ -3580,7 +3580,7 @@
       <c r="AF34" s="20"/>
     </row>
     <row r="35" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
+      <c r="A35" s="36"/>
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -3593,7 +3593,7 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H35" s="21" t="s">
@@ -3608,22 +3608,22 @@
       <c r="K35" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L35" s="20" t="s">
+      <c r="L35" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M35" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N35" s="21" t="s">
+      <c r="N35" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O35" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="P35" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q35" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P35" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R35" s="20" t="s">
@@ -3645,7 +3645,7 @@
       <c r="AF35" s="20"/>
     </row>
     <row r="36" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -3658,7 +3658,7 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H36" s="21" t="s">
@@ -3671,24 +3671,24 @@
         <v>46</v>
       </c>
       <c r="K36" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="L36" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="L36" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M36" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="N36" s="21" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="N36" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O36" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P36" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q36" s="20" t="s">
+      <c r="P36" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q36" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R36" s="20" t="s">
@@ -3710,7 +3710,7 @@
       <c r="AF36" s="20"/>
     </row>
     <row r="37" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
+      <c r="A37" s="36"/>
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -3723,7 +3723,7 @@
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H37" s="21" t="s">
@@ -3738,22 +3738,22 @@
       <c r="K37" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L37" s="20" t="s">
+      <c r="L37" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M37" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N37" s="21" t="s">
+      <c r="N37" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="P37" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q37" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P37" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R37" s="20" t="s">
@@ -3775,7 +3775,7 @@
       <c r="AF37" s="20"/>
     </row>
     <row r="38" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="7">
         <v>35</v>
       </c>
@@ -3788,37 +3788,37 @@
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H38" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I38" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J38" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K38" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L38" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="L38" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M38" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="N38" s="21" t="s">
-        <v>10</v>
+        <v>104</v>
+      </c>
+      <c r="N38" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P38" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q38" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P38" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q38" s="21" t="s">
         <v>10</v>
       </c>
       <c r="R38" s="20" t="s">
@@ -3840,7 +3840,7 @@
       <c r="AF38" s="20"/>
     </row>
     <row r="39" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="38"/>
+      <c r="A39" s="37"/>
       <c r="B39" s="7">
         <v>36</v>
       </c>
@@ -3853,37 +3853,37 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
       <c r="G39" s="12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H39" s="21" t="s">
         <v>104</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K39" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L39" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="L39" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M39" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="N39" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N39" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O39" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="P39" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q39" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P39" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R39" s="20" t="s">
@@ -3905,7 +3905,7 @@
       <c r="AF39" s="20"/>
     </row>
     <row r="40" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="38" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="7">
@@ -3920,7 +3920,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H40" s="21" t="s">
@@ -3935,23 +3935,23 @@
       <c r="K40" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L40" s="20" t="s">
-        <v>10</v>
+      <c r="L40" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="M40" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N40" s="21" t="s">
-        <v>46</v>
+      <c r="N40" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="O40" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P40" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q40" s="20" t="s">
-        <v>46</v>
+      <c r="P40" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q40" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="R40" s="20" t="s">
         <v>46</v>
@@ -3972,7 +3972,7 @@
       <c r="AF40" s="20"/>
     </row>
     <row r="41" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
+      <c r="A41" s="36"/>
       <c r="B41" s="7">
         <v>38</v>
       </c>
@@ -3985,41 +3985,41 @@
       <c r="E41" s="13"/>
       <c r="F41" s="13"/>
       <c r="G41" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H41" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K41" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L41" s="20" t="s">
-        <v>104</v>
+      <c r="L41" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M41" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N41" s="21" t="s">
-        <v>10</v>
+      <c r="N41" s="20" t="s">
+        <v>104</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P41" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q41" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="P41" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q41" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="R41" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S41" s="20"/>
       <c r="T41" s="20"/>
@@ -4037,7 +4037,7 @@
       <c r="AF41" s="20"/>
     </row>
     <row r="42" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
+      <c r="A42" s="36"/>
       <c r="B42" s="7">
         <v>39</v>
       </c>
@@ -4050,37 +4050,37 @@
       <c r="E42" s="13"/>
       <c r="F42" s="13"/>
       <c r="G42" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H42" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K42" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L42" s="20" t="s">
+      <c r="L42" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M42" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N42" s="21" t="s">
+      <c r="N42" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O42" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P42" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q42" s="20" t="s">
+      <c r="P42" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q42" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R42" s="20" t="s">
@@ -4102,7 +4102,7 @@
       <c r="AF42" s="20"/>
     </row>
     <row r="43" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="37"/>
+      <c r="A43" s="36"/>
       <c r="B43" s="7">
         <v>40</v>
       </c>
@@ -4115,41 +4115,41 @@
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H43" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="K43" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L43" s="20" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="L43" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="M43" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N43" s="21" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="N43" s="20" t="s">
+        <v>104</v>
       </c>
       <c r="O43" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="P43" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q43" s="20" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="P43" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q43" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="S43" s="20"/>
       <c r="T43" s="20"/>
@@ -4167,7 +4167,7 @@
       <c r="AF43" s="20"/>
     </row>
     <row r="44" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
+      <c r="A44" s="36"/>
       <c r="B44" s="7">
         <v>41</v>
       </c>
@@ -4180,7 +4180,7 @@
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H44" s="21" t="s">
@@ -4193,24 +4193,24 @@
         <v>104</v>
       </c>
       <c r="K44" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L44" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="L44" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="M44" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="N44" s="21" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="N44" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="O44" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="20" t="s">
+      <c r="P44" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="21" t="s">
         <v>10</v>
       </c>
       <c r="R44" s="20" t="s">
@@ -4232,7 +4232,7 @@
       <c r="AF44" s="20"/>
     </row>
     <row r="45" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="38"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="7">
         <v>42</v>
       </c>
@@ -4245,7 +4245,7 @@
       <c r="E45" s="13"/>
       <c r="F45" s="13"/>
       <c r="G45" s="13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H45" s="21" t="s">
@@ -4260,22 +4260,22 @@
       <c r="K45" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L45" s="20" t="s">
+      <c r="L45" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M45" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N45" s="21" t="s">
+      <c r="N45" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O45" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="P45" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q45" s="20" t="s">
+      <c r="P45" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q45" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R45" s="20" t="s">
@@ -4297,7 +4297,7 @@
       <c r="AF45" s="20"/>
     </row>
     <row r="46" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="55" t="s">
         <v>13</v>
       </c>
       <c r="B46" s="7">
@@ -4312,7 +4312,7 @@
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H46" s="21" t="s">
@@ -4327,22 +4327,22 @@
       <c r="K46" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="20" t="s">
+      <c r="L46" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M46" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N46" s="21" t="s">
+      <c r="N46" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O46" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P46" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q46" s="20" t="s">
+      <c r="P46" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q46" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R46" s="20" t="s">
@@ -4364,7 +4364,7 @@
       <c r="AF46" s="20"/>
     </row>
     <row r="47" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="7">
         <v>44</v>
       </c>
@@ -4377,7 +4377,7 @@
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H47" s="21" t="s">
@@ -4392,26 +4392,26 @@
       <c r="K47" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L47" s="20" t="s">
+      <c r="L47" s="21" t="s">
         <v>104</v>
       </c>
       <c r="M47" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="N47" s="21" t="s">
+      <c r="N47" s="20" t="s">
         <v>104</v>
       </c>
       <c r="O47" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="P47" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q47" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q47" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R47" s="20" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S47" s="20"/>
       <c r="T47" s="20"/>
@@ -4429,7 +4429,7 @@
       <c r="AF47" s="20"/>
     </row>
     <row r="48" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="7">
         <v>45</v>
       </c>
@@ -4442,7 +4442,7 @@
       <c r="E48" s="14"/>
       <c r="F48" s="14"/>
       <c r="G48" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H48" s="21" t="s">
@@ -4457,22 +4457,22 @@
       <c r="K48" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L48" s="20" t="s">
+      <c r="L48" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M48" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N48" s="21" t="s">
+      <c r="N48" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O48" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P48" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q48" s="20" t="s">
+      <c r="P48" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q48" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R48" s="20" t="s">
@@ -4494,7 +4494,7 @@
       <c r="AF48" s="20"/>
     </row>
     <row r="49" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="7">
         <v>46</v>
       </c>
@@ -4507,37 +4507,37 @@
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H49" s="21" t="s">
         <v>46</v>
       </c>
       <c r="I49" s="20" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="J49" s="20" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K49" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="L49" s="20" t="s">
+      <c r="L49" s="21" t="s">
         <v>46</v>
       </c>
       <c r="M49" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="N49" s="21" t="s">
+      <c r="N49" s="20" t="s">
         <v>46</v>
       </c>
       <c r="O49" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="P49" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q49" s="20" t="s">
+      <c r="P49" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q49" s="21" t="s">
         <v>46</v>
       </c>
       <c r="R49" s="20" t="s">
@@ -4559,7 +4559,7 @@
       <c r="AF49" s="20"/>
     </row>
     <row r="50" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
+      <c r="A50" s="36"/>
       <c r="B50" s="7">
         <v>47</v>
       </c>
@@ -4572,7 +4572,7 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H50" s="21" t="s">
@@ -4585,24 +4585,24 @@
         <v>104</v>
       </c>
       <c r="K50" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L50" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="L50" s="21" t="s">
         <v>10</v>
       </c>
       <c r="M50" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="N50" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N50" s="20" t="s">
         <v>10</v>
       </c>
       <c r="O50" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="P50" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q50" s="20" t="s">
+      <c r="P50" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q50" s="21" t="s">
         <v>10</v>
       </c>
       <c r="R50" s="20" t="s">
@@ -4624,7 +4624,7 @@
       <c r="AF50" s="20"/>
     </row>
     <row r="51" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="38"/>
+      <c r="A51" s="37"/>
       <c r="B51" s="7">
         <v>48</v>
       </c>
@@ -4637,7 +4637,7 @@
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
       <c r="H51" s="21" t="s">
@@ -4650,24 +4650,24 @@
         <v>104</v>
       </c>
       <c r="K51" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="L51" s="20" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="L51" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="M51" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="N51" s="21" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="N51" s="20" t="s">
+        <v>104</v>
       </c>
       <c r="O51" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="P51" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q51" s="20" t="s">
+      <c r="P51" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q51" s="21" t="s">
         <v>104</v>
       </c>
       <c r="R51" s="20" t="s">
@@ -4689,7 +4689,7 @@
       <c r="AF51" s="20"/>
     </row>
     <row r="52" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="58" t="s">
         <v>77</v>
       </c>
       <c r="B52" s="7">
@@ -4704,38 +4704,38 @@
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15" t="str">
-        <f t="shared" ref="G52:G75" si="3">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
+        <f t="shared" ref="G52:G75" si="2">IF(E52="","-",IF(E52&gt;F52,"L",IF(E52=F52,"E",IF(E52&lt;F52,"V"))))</f>
         <v>-</v>
       </c>
       <c r="H52" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K52" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L52" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="L52" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M52" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N52" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N52" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O52" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P52" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q52" s="22" t="s">
-        <v>46</v>
+      <c r="P52" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q52" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="R52" s="22" t="s">
         <v>46</v>
@@ -4756,7 +4756,7 @@
       <c r="AF52" s="22"/>
     </row>
     <row r="53" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="44"/>
+      <c r="A53" s="59"/>
       <c r="B53" s="7">
         <v>50</v>
       </c>
@@ -4769,7 +4769,7 @@
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H53" s="23" t="s">
@@ -4784,22 +4784,22 @@
       <c r="K53" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L53" s="22" t="s">
-        <v>104</v>
+      <c r="L53" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M53" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N53" s="23" t="s">
-        <v>46</v>
+      <c r="N53" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="O53" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="P53" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q53" s="22" t="s">
+      <c r="P53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q53" s="23" t="s">
         <v>104</v>
       </c>
       <c r="R53" s="22" t="s">
@@ -4821,7 +4821,7 @@
       <c r="AF53" s="22"/>
     </row>
     <row r="54" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="44"/>
+      <c r="A54" s="59"/>
       <c r="B54" s="7">
         <v>51</v>
       </c>
@@ -4834,7 +4834,7 @@
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
       <c r="G54" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H54" s="23" t="s">
@@ -4849,22 +4849,22 @@
       <c r="K54" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L54" s="22" t="s">
+      <c r="L54" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M54" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N54" s="23" t="s">
+      <c r="N54" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O54" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P54" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q54" s="22" t="s">
+      <c r="P54" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q54" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R54" s="22" t="s">
@@ -4886,7 +4886,7 @@
       <c r="AF54" s="22"/>
     </row>
     <row r="55" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="44"/>
+      <c r="A55" s="59"/>
       <c r="B55" s="7">
         <v>52</v>
       </c>
@@ -4899,7 +4899,7 @@
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
       <c r="G55" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H55" s="23" t="s">
@@ -4912,28 +4912,28 @@
         <v>10</v>
       </c>
       <c r="K55" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L55" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="L55" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M55" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N55" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N55" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O55" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P55" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q55" s="22" t="s">
-        <v>10</v>
+      <c r="P55" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q55" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="R55" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S55" s="22"/>
       <c r="T55" s="22"/>
@@ -4952,7 +4952,7 @@
       <c r="AK55" s="28"/>
     </row>
     <row r="56" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="44"/>
+      <c r="A56" s="59"/>
       <c r="B56" s="7">
         <v>53</v>
       </c>
@@ -4965,38 +4965,38 @@
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H56" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K56" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L56" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="L56" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M56" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="N56" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N56" s="22" t="s">
         <v>104</v>
       </c>
       <c r="O56" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="P56" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q56" s="22" t="s">
-        <v>104</v>
+      <c r="P56" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q56" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="R56" s="22" t="s">
         <v>104</v>
@@ -5017,7 +5017,7 @@
       <c r="AF56" s="22"/>
     </row>
     <row r="57" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="45"/>
+      <c r="A57" s="60"/>
       <c r="B57" s="7">
         <v>54</v>
       </c>
@@ -5030,41 +5030,41 @@
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H57" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J57" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K57" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L57" s="22" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="L57" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M57" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N57" s="23" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="N57" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="O57" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="P57" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q57" s="22" t="s">
+      <c r="P57" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q57" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R57" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S57" s="22"/>
       <c r="T57" s="22"/>
@@ -5082,7 +5082,7 @@
       <c r="AF57" s="22"/>
     </row>
     <row r="58" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="46" t="s">
+      <c r="A58" s="61" t="s">
         <v>78</v>
       </c>
       <c r="B58" s="7">
@@ -5097,37 +5097,37 @@
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
       <c r="G58" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H58" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J58" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K58" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L58" s="22" t="s">
+      <c r="L58" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M58" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N58" s="23" t="s">
+      <c r="N58" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O58" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P58" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q58" s="22" t="s">
+      <c r="P58" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R58" s="22" t="s">
@@ -5149,7 +5149,7 @@
       <c r="AF58" s="22"/>
     </row>
     <row r="59" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="47"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="7">
         <v>56</v>
       </c>
@@ -5162,7 +5162,7 @@
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H59" s="23" t="s">
@@ -5177,26 +5177,26 @@
       <c r="K59" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L59" s="22" t="s">
+      <c r="L59" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M59" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N59" s="23" t="s">
+      <c r="N59" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O59" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="P59" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q59" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="P59" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q59" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="R59" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S59" s="22"/>
       <c r="T59" s="22"/>
@@ -5214,7 +5214,7 @@
       <c r="AF59" s="22"/>
     </row>
     <row r="60" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="47"/>
+      <c r="A60" s="62"/>
       <c r="B60" s="7">
         <v>57</v>
       </c>
@@ -5227,7 +5227,7 @@
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
       <c r="G60" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H60" s="23" t="s">
@@ -5242,22 +5242,22 @@
       <c r="K60" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L60" s="22" t="s">
-        <v>46</v>
+      <c r="L60" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M60" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N60" s="23" t="s">
-        <v>10</v>
+      <c r="N60" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="O60" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P60" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q60" s="22" t="s">
+      <c r="P60" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q60" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R60" s="22" t="s">
@@ -5279,7 +5279,7 @@
       <c r="AF60" s="22"/>
     </row>
     <row r="61" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="47"/>
+      <c r="A61" s="62"/>
       <c r="B61" s="7">
         <v>58</v>
       </c>
@@ -5292,7 +5292,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H61" s="23" t="s">
@@ -5305,28 +5305,28 @@
         <v>104</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="L61" s="22" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="L61" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M61" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N61" s="23" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="N61" s="22" t="s">
+        <v>10</v>
       </c>
       <c r="O61" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="P61" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q61" s="22" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="P61" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q61" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="R61" s="22" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S61" s="22"/>
       <c r="T61" s="22"/>
@@ -5344,7 +5344,7 @@
       <c r="AF61" s="22"/>
     </row>
     <row r="62" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="47"/>
+      <c r="A62" s="62"/>
       <c r="B62" s="7">
         <v>59</v>
       </c>
@@ -5357,41 +5357,41 @@
       <c r="E62" s="16"/>
       <c r="F62" s="16"/>
       <c r="G62" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H62" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="J62" s="22" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K62" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L62" s="22" t="s">
+      <c r="L62" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M62" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N62" s="23" t="s">
+      <c r="N62" s="22" t="s">
         <v>104</v>
       </c>
       <c r="O62" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="P62" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q62" s="22" t="s">
-        <v>104</v>
+      <c r="P62" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q62" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="R62" s="22" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="S62" s="22"/>
       <c r="T62" s="22"/>
@@ -5409,7 +5409,7 @@
       <c r="AF62" s="22"/>
     </row>
     <row r="63" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="48"/>
+      <c r="A63" s="63"/>
       <c r="B63" s="7">
         <v>60</v>
       </c>
@@ -5422,7 +5422,7 @@
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
       <c r="G63" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H63" s="23" t="s">
@@ -5437,22 +5437,22 @@
       <c r="K63" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L63" s="22" t="s">
+      <c r="L63" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M63" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N63" s="23" t="s">
+      <c r="N63" s="22" t="s">
         <v>104</v>
       </c>
       <c r="O63" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="P63" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q63" s="22" t="s">
+      <c r="P63" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q63" s="23" t="s">
         <v>104</v>
       </c>
       <c r="R63" s="22" t="s">
@@ -5474,7 +5474,7 @@
       <c r="AF63" s="22"/>
     </row>
     <row r="64" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="49" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="7">
@@ -5489,7 +5489,7 @@
       <c r="E64" s="17"/>
       <c r="F64" s="17"/>
       <c r="G64" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H64" s="23" t="s">
@@ -5504,22 +5504,22 @@
       <c r="K64" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L64" s="22" t="s">
+      <c r="L64" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M64" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N64" s="23" t="s">
+      <c r="N64" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O64" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P64" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q64" s="22" t="s">
+      <c r="P64" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q64" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R64" s="22" t="s">
@@ -5541,7 +5541,7 @@
       <c r="AF64" s="22"/>
     </row>
     <row r="65" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="31"/>
+      <c r="A65" s="50"/>
       <c r="B65" s="7">
         <v>62</v>
       </c>
@@ -5554,7 +5554,7 @@
       <c r="E65" s="17"/>
       <c r="F65" s="17"/>
       <c r="G65" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H65" s="23" t="s">
@@ -5569,22 +5569,22 @@
       <c r="K65" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L65" s="22" t="s">
+      <c r="L65" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M65" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N65" s="23" t="s">
+      <c r="N65" s="22" t="s">
         <v>104</v>
       </c>
       <c r="O65" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="P65" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q65" s="22" t="s">
+      <c r="P65" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q65" s="23" t="s">
         <v>104</v>
       </c>
       <c r="R65" s="22" t="s">
@@ -5606,7 +5606,7 @@
       <c r="AF65" s="22"/>
     </row>
     <row r="66" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="31"/>
+      <c r="A66" s="50"/>
       <c r="B66" s="7">
         <v>63</v>
       </c>
@@ -5619,7 +5619,7 @@
       <c r="E66" s="17"/>
       <c r="F66" s="17"/>
       <c r="G66" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H66" s="23" t="s">
@@ -5634,22 +5634,22 @@
       <c r="K66" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L66" s="22" t="s">
+      <c r="L66" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M66" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N66" s="23" t="s">
+      <c r="N66" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O66" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P66" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q66" s="22" t="s">
+      <c r="P66" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q66" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R66" s="22" t="s">
@@ -5671,7 +5671,7 @@
       <c r="AF66" s="22"/>
     </row>
     <row r="67" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="31"/>
+      <c r="A67" s="50"/>
       <c r="B67" s="7">
         <v>64</v>
       </c>
@@ -5684,37 +5684,37 @@
       <c r="E67" s="17"/>
       <c r="F67" s="17"/>
       <c r="G67" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H67" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I67" s="22" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="J67" s="22" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="K67" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L67" s="22" t="s">
+      <c r="L67" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M67" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N67" s="23" t="s">
+      <c r="N67" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O67" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P67" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q67" s="22" t="s">
+      <c r="P67" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q67" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R67" s="22" t="s">
@@ -5736,7 +5736,7 @@
       <c r="AF67" s="22"/>
     </row>
     <row r="68" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="31"/>
+      <c r="A68" s="50"/>
       <c r="B68" s="7">
         <v>65</v>
       </c>
@@ -5749,38 +5749,38 @@
       <c r="E68" s="17"/>
       <c r="F68" s="17"/>
       <c r="G68" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H68" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J68" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K68" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L68" s="22" t="s">
-        <v>104</v>
+      <c r="L68" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M68" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N68" s="23" t="s">
-        <v>10</v>
+      <c r="N68" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="O68" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="P68" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q68" s="22" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="P68" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q68" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="R68" s="22" t="s">
         <v>104</v>
@@ -5801,7 +5801,7 @@
       <c r="AF68" s="22"/>
     </row>
     <row r="69" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="32"/>
+      <c r="A69" s="51"/>
       <c r="B69" s="7">
         <v>66</v>
       </c>
@@ -5814,38 +5814,38 @@
       <c r="E69" s="17"/>
       <c r="F69" s="17"/>
       <c r="G69" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H69" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I69" s="22" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="J69" s="22" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K69" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L69" s="22" t="s">
-        <v>10</v>
+      <c r="L69" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M69" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N69" s="23" t="s">
-        <v>104</v>
+      <c r="N69" s="22" t="s">
+        <v>10</v>
       </c>
       <c r="O69" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="P69" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q69" s="22" t="s">
-        <v>10</v>
+      <c r="P69" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q69" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="R69" s="22" t="s">
         <v>10</v>
@@ -5866,7 +5866,7 @@
       <c r="AF69" s="22"/>
     </row>
     <row r="70" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="33" t="s">
+      <c r="A70" s="52" t="s">
         <v>46</v>
       </c>
       <c r="B70" s="7">
@@ -5881,41 +5881,41 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
       <c r="G70" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H70" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I70" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J70" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K70" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L70" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="L70" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M70" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N70" s="23" t="s">
-        <v>46</v>
+        <v>104</v>
+      </c>
+      <c r="N70" s="22" t="s">
+        <v>10</v>
       </c>
       <c r="O70" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P70" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q70" s="22" t="s">
-        <v>10</v>
+      <c r="P70" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q70" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="R70" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="S70" s="22"/>
       <c r="T70" s="22"/>
@@ -5933,7 +5933,7 @@
       <c r="AF70" s="22"/>
     </row>
     <row r="71" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="34"/>
+      <c r="A71" s="53"/>
       <c r="B71" s="7">
         <v>68</v>
       </c>
@@ -5946,41 +5946,41 @@
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
       <c r="G71" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H71" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J71" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K71" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L71" s="22" t="s">
-        <v>10</v>
+      <c r="L71" s="23" t="s">
+        <v>104</v>
       </c>
       <c r="M71" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N71" s="23" t="s">
-        <v>104</v>
+      <c r="N71" s="22" t="s">
+        <v>10</v>
       </c>
       <c r="O71" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="P71" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q71" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="P71" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q71" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="R71" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="S71" s="22"/>
       <c r="T71" s="22"/>
@@ -5998,7 +5998,7 @@
       <c r="AF71" s="22"/>
     </row>
     <row r="72" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="34"/>
+      <c r="A72" s="53"/>
       <c r="B72" s="7">
         <v>69</v>
       </c>
@@ -6011,37 +6011,37 @@
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
       <c r="G72" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H72" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I72" s="22" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="J72" s="22" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="K72" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L72" s="22" t="s">
+      <c r="L72" s="23" t="s">
         <v>46</v>
       </c>
       <c r="M72" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N72" s="23" t="s">
+      <c r="N72" s="22" t="s">
         <v>46</v>
       </c>
       <c r="O72" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="P72" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q72" s="22" t="s">
+      <c r="P72" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q72" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R72" s="22" t="s">
@@ -6063,7 +6063,7 @@
       <c r="AF72" s="22"/>
     </row>
     <row r="73" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="34"/>
+      <c r="A73" s="53"/>
       <c r="B73" s="7">
         <v>70</v>
       </c>
@@ -6076,7 +6076,7 @@
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
       <c r="G73" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H73" s="23" t="s">
@@ -6091,23 +6091,23 @@
       <c r="K73" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="L73" s="22" t="s">
-        <v>104</v>
+      <c r="L73" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="M73" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="N73" s="23" t="s">
-        <v>46</v>
+      <c r="N73" s="22" t="s">
+        <v>104</v>
       </c>
       <c r="O73" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="P73" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q73" s="22" t="s">
-        <v>104</v>
+        <v>104</v>
+      </c>
+      <c r="P73" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q73" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="R73" s="22" t="s">
         <v>104</v>
@@ -6128,7 +6128,7 @@
       <c r="AF73" s="22"/>
     </row>
     <row r="74" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="34"/>
+      <c r="A74" s="53"/>
       <c r="B74" s="7">
         <v>71</v>
       </c>
@@ -6141,37 +6141,37 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
       <c r="G74" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H74" s="23" t="s">
         <v>104</v>
       </c>
       <c r="I74" s="22" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="J74" s="22" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="K74" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="L74" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="L74" s="23" t="s">
         <v>104</v>
       </c>
       <c r="M74" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="N74" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="N74" s="22" t="s">
         <v>104</v>
       </c>
       <c r="O74" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="P74" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q74" s="22" t="s">
+      <c r="P74" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q74" s="23" t="s">
         <v>104</v>
       </c>
       <c r="R74" s="22" t="s">
@@ -6193,7 +6193,7 @@
       <c r="AF74" s="22"/>
     </row>
     <row r="75" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="35"/>
+      <c r="A75" s="54"/>
       <c r="B75" s="7">
         <v>72</v>
       </c>
@@ -6206,37 +6206,37 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
       <c r="G75" s="18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H75" s="23" t="s">
         <v>46</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="J75" s="22" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="L75" s="22" t="s">
-        <v>46</v>
+      <c r="L75" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="M75" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="N75" s="23" t="s">
-        <v>10</v>
+      <c r="N75" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="O75" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="P75" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q75" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P75" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q75" s="23" t="s">
         <v>46</v>
       </c>
       <c r="R75" s="22" t="s">
@@ -6261,11 +6261,11 @@
       <c r="A76" s="24"/>
       <c r="B76" s="24"/>
       <c r="C76" s="24"/>
-      <c r="D76" s="39" t="s">
+      <c r="D76" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="E76" s="40"/>
-      <c r="F76" s="41"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="32"/>
       <c r="G76" s="2">
         <f>SUM(E4:F75)</f>
         <v>19</v>
@@ -6274,34 +6274,34 @@
         <v>179</v>
       </c>
       <c r="I76" s="22">
+        <v>186</v>
+      </c>
+      <c r="J76" s="22">
         <v>222</v>
       </c>
-      <c r="J76" s="22">
-        <v>186</v>
-      </c>
       <c r="K76" s="23">
+        <v>185</v>
+      </c>
+      <c r="L76" s="23">
+        <v>201</v>
+      </c>
+      <c r="M76" s="23">
         <v>162</v>
       </c>
-      <c r="L76" s="22">
+      <c r="N76" s="22">
         <v>172</v>
       </c>
-      <c r="M76" s="23">
-        <v>185</v>
-      </c>
-      <c r="N76" s="23">
-        <v>201</v>
-      </c>
       <c r="O76" s="22">
+        <v>190</v>
+      </c>
+      <c r="P76" s="22">
         <v>169</v>
       </c>
-      <c r="P76" s="23">
+      <c r="Q76" s="23">
         <v>180</v>
       </c>
-      <c r="Q76" s="22">
+      <c r="R76" s="22">
         <v>197</v>
-      </c>
-      <c r="R76" s="22">
-        <v>190</v>
       </c>
       <c r="S76" s="22"/>
       <c r="T76" s="22"/>
@@ -6322,110 +6322,110 @@
       <c r="A77" s="24"/>
       <c r="B77" s="24"/>
       <c r="C77" s="24"/>
-      <c r="D77" s="42" t="s">
+      <c r="D77" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="40"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="41"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="32"/>
       <c r="H77" s="25">
-        <f t="shared" ref="H77:R77" si="4">SUM(H78:H81)</f>
+        <f>SUM(H78:H81)</f>
         <v>0</v>
       </c>
       <c r="I77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(I78:I81)</f>
         <v>0</v>
       </c>
       <c r="J77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(J78:J81)</f>
         <v>0</v>
       </c>
       <c r="K77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(K78:K81)</f>
         <v>0</v>
       </c>
       <c r="L77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(L78:L81)</f>
         <v>0</v>
       </c>
       <c r="M77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(M78:M81)</f>
         <v>0</v>
       </c>
       <c r="N77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(N78:N81)</f>
         <v>0</v>
       </c>
       <c r="O77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(O78:O81)</f>
         <v>0</v>
       </c>
       <c r="P77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(P78:P81)</f>
         <v>0</v>
       </c>
       <c r="Q77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(Q78:Q81)</f>
         <v>0</v>
       </c>
       <c r="R77" s="25">
-        <f t="shared" si="4"/>
+        <f>SUM(R78:R81)</f>
         <v>0</v>
       </c>
       <c r="S77" s="25">
-        <f t="shared" ref="S77:AF77" si="5">SUM(S78:S81)</f>
+        <f t="shared" ref="S77:AF77" si="3">SUM(S78:S81)</f>
         <v>81</v>
       </c>
       <c r="T77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="U77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="V77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="W77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="X77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="Y77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="Z77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AA77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AB77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AC77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AD77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AE77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
       <c r="AF77" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>81</v>
       </c>
     </row>
@@ -6438,103 +6438,103 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3">
-        <f t="shared" ref="H78:AF78" si="6">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H78:AF78" si="4">IF(H76=$G$76,100,IF($G$76-H76=1,99,IF($G$76-H76=-1,99,IF($G$76-H76=2,98,IF($G$76-H76=-2,98,IF($G$76-H76=3,97,IF($G$76-H76=-3,97,IF($G$76-H76=4,96,IF($G$76-H76=-4,96,IF($G$76-H76=5,95,IF($G$76-H76=-5,95,IF($G$76-H76=6,94,IF($G$76-H76=-6,94,IF($G$76-H76=7,93,IF($G$76-H76=-7,93,IF($G$76-H76=8,92,IF($G$76-H76=-8,92,IF($G$76-H76=9,91,IF($G$76-H76=-9,91,IF($G$76-H76=10,90,IF($G$76-H76=-10,90,IF($G$76-H76=11,89,IF($G$76-H76=-11,89,IF($G$76-H76=12,88,IF($G$76-H76=-12,88,IF($G$76-H76=13,87,IF($G$76-H76=-13,87,IF($G$76-H76=14,86,IF($G$76-H76=-14,86,IF($G$76-H76=15,85,IF($G$76-H76=-15,85,IF($G$76-H76=16,84,IF($G$76-H76=-16,84,IF($G$76-H76=17,83,IF($G$76-H76=-17,83,IF($G$76-H76=18,82,IF($G$76-H76=-18,82,IF($G$76-H76=19,81,IF($G$76-H76=-19,81,IF($G$76-H76=20,80,IF($G$76-H76=-20,80,IF($G$76-H76=21,79,IF($G$76-H76=-21,79,IF($G$76-H76=22,78,IF($G$76-H76=-22,78,IF($G$76-H76=23,77,IF($G$76-H76=-23,77,IF($G$76-H76=24,76,IF($G$76-H76=-24,76,IF($G$76-H76=25,75,IF($G$76-H76=-25,75,IF($G$76-H76=26,74,IF($G$76-H76=-26,74,IF($G$76-H76=27,73,IF($G$76-H76=-27,73,IF($G$76-H76=28,72,IF($G$76-H76=-28,72,IF($G$76-H76=29,71,IF($G$76-H76=-29,71,IF($G$76-H76=30,70,IF($G$76-H76=-30,70,IF($G$76-H76=31,69,IF($G$76-H76=-31,69,IF($G$76-H76=32,68,IF($G$76-H76=-32,68,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="T78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="X78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="Y78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="Z78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="AA78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="AB78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="AC78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="AD78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="AE78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="AF78" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
     </row>
@@ -6547,103 +6547,103 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
       <c r="H79" s="3">
-        <f t="shared" ref="H79:AF79" si="7">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H79:AF79" si="5">IF($G$76-H76=33,67,IF($G$76-H76=-33,67,IF($G$76-H76=34,66,IF($G$76-H76=-34,66,IF($G$76-H76=35,65,IF($G$76-H76=-35,65,IF($G$76-H76=36,64,IF($G$76-H76=-36,64,IF($G$76-H76=37,63,IF($G$76-H76=-37,63,IF($G$76-H76=38,62,IF($G$76-H76=-38,62,IF($G$76-H76=39,61,IF($G$76-H76=-39,61,IF($G$76-H76=40,60,IF($G$76-H76=-40,60,IF($G$76-H76=41,59,IF($G$76-H76=-41,59,IF($G$76-H76=42,58,IF($G$76-H76=-42,58,IF($G$76-H76=43,57,IF($G$76-H76=-43,57,IF($G$76-H76=44,56,IF($G$76-H76=-44,56,IF($G$76-H76=45,55,IF($G$76-H76=-45,55,IF($G$76-H76=46,54,IF($G$76-H76=-46,54,IF($G$76-H76=47,53,IF($G$76-H76=-47,53,IF($G$76-H76=48,52,IF($G$76-H76=-48,52,IF($G$76-H76=49,51,IF($G$76-H76=-49,51,IF($G$76-H76=50,50,IF($G$76-H76=-50,50,IF($G$76-H76=51,49,IF($G$76-H76=-51,49,IF($G$76-H76=52,48,IF($G$76-H76=-52,48,IF($G$76-H76=53,47,IF($G$76-H76=-53,47,IF($G$76-H76=54,46,IF($G$76-H76=-54,46,IF($G$76-H76=55,45,IF($G$76-H76=-55,45,IF($G$76-H76=56,44,IF($G$76-H76=-56,44,IF($G$76-H76=57,43,IF($G$76-H76=-57,43,IF($G$76-H76=58,42,IF($G$76-H76=-58,42,IF($G$76-H76=59,41,IF($G$76-H76=-59,41,IF($G$76-H76=60,40,IF($G$76-H76=-60,40,IF($G$76-H76=61,39,IF($G$76-H76=-61,39,IF($G$76-H76=62,38,IF($G$76-H76=-62,38,IF($G$76-H76=63,37,IF($G$76-H76=-63,37,IF($G$76-H76=64,36,IF($G$76-H76=-64,36,IF($G$76-H76=65,35,0)))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF79" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -6656,103 +6656,103 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
       <c r="H80" s="3">
-        <f t="shared" ref="H80:AF80" si="8">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
+        <f t="shared" ref="H80:AF80" si="6">IF($G$76-H76=-65,35,IF($G$76-H76=66,34,IF($G$76-H76=-66,34,IF($G$76-H76=67,33,IF($G$76-H76=-67,33,IF($G$76-H76=68,32,IF($G$76-H76=-68,32,IF($G$76-H76=69,31,IF($G$76-H76=-69,31,IF($G$76-H76=70,30,IF($G$76-H76=-70,30,IF($G$76-H76=71,29,IF($G$76-H76=-71,29,IF($G$76-H76=72,28,IF($G$76-H76=-72,28,IF($G$76-H76=73,27,IF($G$76-H76=-73,27,IF($G$76-H76=74,26,IF($G$76-H76=-74,26,IF($G$76-H76=75,25,IF($G$76-H76=-75,25,IF($G$76-H76=76,24,IF($G$76-H76=-76,24,IF($G$76-H76=77,23,IF($G$76-H76=-77,23,IF($G$76-H76=78,22,IF($G$76-H76=-78,22,IF($G$76-H76=79,21,IF($G$76-H76=-79,21,IF($G$76-H76=80,20,IF($G$76-H76=-80,20,IF($G$76-H76=81,19,IF($G$76-H76=-81,19,IF($G$76-H76=82,18,IF($G$76-H76=-82,18,IF($G$76-H76=83,17,IF($G$76-H76=-83,17,IF($G$76-H76=84,16,IF($G$76-H76=-84,16,IF($G$76-H76=85,15,IF($G$76-H76=-85,15,IF($G$76-H76=86,14,IF($G$76-H76=-86,14,IF($G$76-H76=87,13,IF($G$76-H76=-87,13,IF($G$76-H76=88,12,IF($G$76-H76=-88,12,IF($G$76-H76=89,11,IF($G$76-H76=-89,11,IF($G$76-H76=90,10,IF($G$76-H76=-90,10,IF($G$76-H76=91,9,IF($G$76-H76=-91,9,IF($G$76-H76=92,8,IF($G$76-H76=-92,8,IF($G$76-H76=93,7,IF($G$76-H76=-93,7,IF($G$76-H76=94,6,IF($G$76-H76=-94,6,IF($G$76-H76=95,5,IF($G$76-H76=-95,5,IF($G$76-H76=96,4,0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</f>
         <v>0</v>
       </c>
       <c r="I80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF80" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -6765,103 +6765,103 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
       <c r="H81" s="3">
-        <f t="shared" ref="H81:AF81" si="9">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
+        <f t="shared" ref="H81:AF81" si="7">IF($G$76-H76=-96,4,IF($G$76-H76=97,3,IF($G$76-H76=-97,3,IF($G$76-H76=98,2,IF($G$76-H76=-98,2,IF($G$76-H76=99,1,IF($G$76-H76=-99,1,IF($G$76-H76=100,0,IF($G$76-H76=-100,0,0)))))))))</f>
         <v>0</v>
       </c>
       <c r="I81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF81" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7733,6 +7733,13 @@
     <sortCondition descending="1" ref="H77:R77"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A58:A63"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="A4:A9"/>
@@ -7744,13 +7751,6 @@
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A58:A63"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:AF3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
